--- a/replication-package/Code/LinearCF_v3/CF_results_revision_5.xlsx
+++ b/replication-package/Code/LinearCF_v3/CF_results_revision_5.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1477" uniqueCount="844">
   <si>
     <t>Var1</t>
   </si>
@@ -2552,7 +2552,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -2591,7 +2591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2614,46 +2614,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>633</v>
+        <v>739</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>725</v>
+        <v>831</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>726</v>
+        <v>832</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>727</v>
+        <v>833</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>728</v>
+        <v>834</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>729</v>
+        <v>835</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>730</v>
+        <v>836</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>731</v>
+        <v>837</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>732</v>
+        <v>838</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>733</v>
+        <v>839</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>734</v>
+        <v>840</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>735</v>
+        <v>841</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>736</v>
+        <v>842</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>737</v>
+        <v>843</v>
       </c>
       <c r="O1" s="0" t="s">
         <v>738</v>
@@ -2661,34 +2661,34 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>634</v>
+        <v>740</v>
       </c>
       <c r="B2" s="0">
-        <v>0.78149579333799934</v>
+        <v>0.78149579344971631</v>
       </c>
       <c r="C2" s="0">
         <v>0.00099664659340659308</v>
       </c>
       <c r="D2" s="0">
-        <v>3.5378916704941782e-06</v>
+        <v>3.5354229930806629e-06</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>2.8024036750922554e-06</v>
+        <v>2.8058208969585993e-06</v>
       </c>
       <c r="G2" s="0">
-        <v>4.2046000047237523e-08</v>
+        <v>4.0991444581573049e-08</v>
       </c>
       <c r="H2" s="0">
-        <v>1.9688352051835616e-15</v>
+        <v>2.125560679066466e-15</v>
       </c>
       <c r="I2" s="0">
-        <v>6.9348020030556075e-07</v>
+        <v>6.8864789866280695e-07</v>
       </c>
       <c r="J2" s="0">
-        <v>-3.8206919710699729e-11</v>
+        <v>-3.7249247877116872e-11</v>
       </c>
       <c r="K2" s="0">
         <v>0</v>
@@ -2703,39 +2703,39 @@
         <v>1</v>
       </c>
       <c r="O2" s="0">
-        <v>0.000161517395390834</v>
+        <v>0.0001615173953669049</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>635</v>
+        <v>741</v>
       </c>
       <c r="B3" s="0">
-        <v>0.89377294262467666</v>
+        <v>0.89377294242544958</v>
       </c>
       <c r="C3" s="0">
         <v>0.0059910226373626405</v>
       </c>
       <c r="D3" s="0">
-        <v>3.8777001351310622e-05</v>
+        <v>3.8801427061201618e-05</v>
       </c>
       <c r="E3" s="0">
-        <v>5.6092878156187332e-05</v>
+        <v>5.6092878307398962e-05</v>
       </c>
       <c r="F3" s="0">
-        <v>-1.3968239703674863e-05</v>
+        <v>-1.3973016805833319e-05</v>
       </c>
       <c r="G3" s="0">
-        <v>3.4620437808640691e-07</v>
+        <v>3.385398088449474e-07</v>
       </c>
       <c r="H3" s="0">
-        <v>1.3758659853197611e-21</v>
+        <v>-5.2101779443252176e-21</v>
       </c>
       <c r="I3" s="0">
-        <v>-3.6935263708971714e-06</v>
+        <v>-3.6566661211339192e-06</v>
       </c>
       <c r="J3" s="0">
-        <v>-3.1510839108271637e-10</v>
+        <v>-3.0812807504803857e-10</v>
       </c>
       <c r="K3" s="0">
         <v>1</v>
@@ -2750,39 +2750,39 @@
         <v>0</v>
       </c>
       <c r="O3" s="0">
-        <v>0.019175251780907576</v>
+        <v>0.019175251785082156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>636</v>
+        <v>742</v>
       </c>
       <c r="B4" s="0">
-        <v>0.58038968102602051</v>
+        <v>0.58038968104253585</v>
       </c>
       <c r="C4" s="0">
         <v>0.024877143296703302</v>
       </c>
       <c r="D4" s="0">
-        <v>3.136248973002982e-05</v>
+        <v>3.138200248478357e-05</v>
       </c>
       <c r="E4" s="0">
-        <v>4.527008604012679e-05</v>
+        <v>4.5270085987693838e-05</v>
       </c>
       <c r="F4" s="0">
-        <v>-1.1073871230043286e-05</v>
+        <v>-1.1078639728205837e-05</v>
       </c>
       <c r="G4" s="0">
-        <v>2.35086106962992e-07</v>
+        <v>2.2992435239124864e-07</v>
       </c>
       <c r="H4" s="0">
-        <v>6.1231052779929697e-20</v>
+        <v>-3.5554644858162557e-20</v>
       </c>
       <c r="I4" s="0">
-        <v>-3.0685972439638024e-06</v>
+        <v>-3.0391588836476749e-06</v>
       </c>
       <c r="J4" s="0">
-        <v>-2.1394305293604814e-10</v>
+        <v>-2.0924344796923629e-10</v>
       </c>
       <c r="K4" s="0">
         <v>1</v>
@@ -2797,39 +2797,39 @@
         <v>0</v>
       </c>
       <c r="O4" s="0">
-        <v>0.0058489659841263414</v>
+        <v>0.0058489659839294954</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>637</v>
+        <v>743</v>
       </c>
       <c r="B5" s="0">
-        <v>0.49684304335047907</v>
+        <v>0.49684304334618173</v>
       </c>
       <c r="C5" s="0">
         <v>0.028964137692307681</v>
       </c>
       <c r="D5" s="0">
-        <v>5.5804754025743641e-05</v>
+        <v>5.5850298266950359e-05</v>
       </c>
       <c r="E5" s="0">
-        <v>9.6405943030097204e-05</v>
+        <v>9.640594304440149e-05</v>
       </c>
       <c r="F5" s="0">
-        <v>-3.2176389140139842e-05</v>
+        <v>-3.220049553154273e-05</v>
       </c>
       <c r="G5" s="0">
-        <v>4.7387539834058336e-07</v>
+        <v>4.634879446710666e-07</v>
       </c>
       <c r="H5" s="0">
-        <v>-3.4540597775017659e-20</v>
+        <v>-1.6404750360277116e-19</v>
       </c>
       <c r="I5" s="0">
-        <v>-8.8982440320396524e-06</v>
+        <v>-8.8182154172884918e-06</v>
       </c>
       <c r="J5" s="0">
-        <v>-4.3123051461828126e-10</v>
+        <v>-4.2177329081110628e-10</v>
       </c>
       <c r="K5" s="0">
         <v>1</v>
@@ -2844,39 +2844,39 @@
         <v>0</v>
       </c>
       <c r="O5" s="0">
-        <v>0.01112286546973147</v>
+        <v>0.011122865469769845</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>638</v>
+        <v>744</v>
       </c>
       <c r="B6" s="0">
-        <v>0.83894268763452251</v>
+        <v>0.83894268773261005</v>
       </c>
       <c r="C6" s="0">
         <v>0.00056924747252747249</v>
       </c>
       <c r="D6" s="0">
-        <v>1.7724947166103133e-05</v>
+        <v>1.7729814667702624e-05</v>
       </c>
       <c r="E6" s="0">
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>1.9963104224019093e-05</v>
+        <v>1.9950298375975735e-05</v>
       </c>
       <c r="G6" s="0">
-        <v>9.4980934998509524e-08</v>
+        <v>9.2546631959595274e-08</v>
       </c>
       <c r="H6" s="0">
-        <v>5.6038487762414983e-19</v>
+        <v>5.6873756324934291e-19</v>
       </c>
       <c r="I6" s="0">
-        <v>-2.3330516506031475e-06</v>
+        <v>-2.312946210911117e-06</v>
       </c>
       <c r="J6" s="0">
-        <v>-8.6342311882204491e-11</v>
+        <v>-8.4129322158533256e-11</v>
       </c>
       <c r="K6" s="0">
         <v>0</v>
@@ -2891,39 +2891,39 @@
         <v>0</v>
       </c>
       <c r="O6" s="0">
-        <v>9.0512945147590499e-05</v>
+        <v>9.0512945136537302e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>639</v>
+        <v>745</v>
       </c>
       <c r="B7" s="0">
-        <v>0.9085352004413042</v>
+        <v>0.908535200552539</v>
       </c>
       <c r="C7" s="0">
         <v>0.0064199401098901073</v>
       </c>
       <c r="D7" s="0">
-        <v>3.3669661799565791e-05</v>
+        <v>3.364831487222061e-05</v>
       </c>
       <c r="E7" s="0">
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>3.1707851594667661e-05</v>
+        <v>3.1707032223443043e-05</v>
       </c>
       <c r="G7" s="0">
-        <v>1.3778576001882702e-07</v>
+        <v>1.3418914459323239e-07</v>
       </c>
       <c r="H7" s="0">
-        <v>8.9801790107580611e-21</v>
+        <v>-1.1146388832270831e-20</v>
       </c>
       <c r="I7" s="0">
-        <v>1.8241497787022852e-06</v>
+        <v>1.8072155658131127e-06</v>
       </c>
       <c r="J7" s="0">
-        <v>-1.2533382299108145e-10</v>
+        <v>-1.220616287676865e-10</v>
       </c>
       <c r="K7" s="0">
         <v>0</v>
@@ -2938,39 +2938,39 @@
         <v>0</v>
       </c>
       <c r="O7" s="0">
-        <v>0.0012336762862563782</v>
+        <v>0.001233676286098921</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>640</v>
+        <v>746</v>
       </c>
       <c r="B8" s="0">
-        <v>0.8389707174230655</v>
+        <v>0.83897071741063856</v>
       </c>
       <c r="C8" s="0">
         <v>0.0071889561538461526</v>
       </c>
       <c r="D8" s="0">
-        <v>2.4482395341677374e-05</v>
+        <v>2.4506741936018731e-05</v>
       </c>
       <c r="E8" s="0">
-        <v>4.8116484804233987e-05</v>
+        <v>4.8116484526700938e-05</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.8508802823186358e-05</v>
+        <v>-1.8526002182075404e-05</v>
       </c>
       <c r="G8" s="0">
-        <v>2.1018843685490098e-07</v>
+        <v>2.0559261599622715e-07</v>
       </c>
       <c r="H8" s="0">
-        <v>-4.8119286803635357e-19</v>
+        <v>-8.8732384012015876e-19</v>
       </c>
       <c r="I8" s="0">
-        <v>-5.3352838056689714e-06</v>
+        <v>-5.2891459376960823e-06</v>
       </c>
       <c r="J8" s="0">
-        <v>-1.9127055570391084e-10</v>
+        <v>-1.8708690605967688e-10</v>
       </c>
       <c r="K8" s="0">
         <v>0</v>
@@ -2985,39 +2985,39 @@
         <v>0</v>
       </c>
       <c r="O8" s="0">
-        <v>0.0011134296221103025</v>
+        <v>0.001113429622121006</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>641</v>
+        <v>747</v>
       </c>
       <c r="B9" s="0">
-        <v>0.85359648677539157</v>
+        <v>0.85359648674592037</v>
       </c>
       <c r="C9" s="0">
         <v>0.0014056876923076917</v>
       </c>
       <c r="D9" s="0">
-        <v>0.0001131715902305964</v>
+        <v>0.00011282405600522115</v>
       </c>
       <c r="E9" s="0">
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>5.1166948509609598e-05</v>
+        <v>5.1281177193386143e-05</v>
       </c>
       <c r="G9" s="0">
-        <v>2.4501781875108866e-07</v>
+        <v>2.3928229212645234e-07</v>
       </c>
       <c r="H9" s="0">
-        <v>9.8876041423280702e-20</v>
+        <v>1.0024235643695668e-19</v>
       </c>
       <c r="I9" s="0">
-        <v>6.1759846781565442e-05</v>
+        <v>6.1303814180067054e-05</v>
       </c>
       <c r="J9" s="0">
-        <v>-2.2287932981948817e-10</v>
+        <v>-2.1766035859533545e-10</v>
       </c>
       <c r="K9" s="0">
         <v>0</v>
@@ -3032,39 +3032,39 @@
         <v>0</v>
       </c>
       <c r="O9" s="0">
-        <v>0.00027864583459222329</v>
+        <v>0.00027864583460039514</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>642</v>
+        <v>748</v>
       </c>
       <c r="B10" s="0">
-        <v>0.93573023505403186</v>
+        <v>0.93573023509885622</v>
       </c>
       <c r="C10" s="0">
         <v>0.0019589672527472535</v>
       </c>
       <c r="D10" s="0">
-        <v>3.9628673452383846e-05</v>
+        <v>3.9589599851635835e-05</v>
       </c>
       <c r="E10" s="0">
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>3.1948362701539518e-05</v>
+        <v>3.1973356927922413e-05</v>
       </c>
       <c r="G10" s="0">
-        <v>1.6939833404591357e-07</v>
+        <v>1.6516674398881952e-07</v>
       </c>
       <c r="H10" s="0">
-        <v>3.4179159918891019e-22</v>
+        <v>-3.8853751185165931e-21</v>
       </c>
       <c r="I10" s="0">
-        <v>7.5110665074307337e-06</v>
+        <v>7.4512264204969233e-06</v>
       </c>
       <c r="J10" s="0">
-        <v>-1.5409063231911949e-10</v>
+        <v>-1.5024077231652345e-10</v>
       </c>
       <c r="K10" s="0">
         <v>0</v>
@@ -3079,39 +3079,39 @@
         <v>0</v>
       </c>
       <c r="O10" s="0">
-        <v>0.031269923852035232</v>
+        <v>0.031269923850374727</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>643</v>
+        <v>749</v>
       </c>
       <c r="B11" s="0">
-        <v>0.76744161783916032</v>
+        <v>0.76744161778897346</v>
       </c>
       <c r="C11" s="0">
         <v>0.0097142418681318687</v>
       </c>
       <c r="D11" s="0">
-        <v>4.8529088534708972e-05</v>
+        <v>4.856391018285594e-05</v>
       </c>
       <c r="E11" s="0">
-        <v>8.330731102493227e-05</v>
+        <v>8.3307311031725258e-05</v>
       </c>
       <c r="F11" s="0">
-        <v>-2.789060382258562e-05</v>
+        <v>-2.7912122967860666e-05</v>
       </c>
       <c r="G11" s="0">
-        <v>5.3463577129471811e-07</v>
+        <v>5.2270683617646842e-07</v>
       </c>
       <c r="H11" s="0">
-        <v>-6.0808238596351462e-21</v>
+        <v>-2.6181107745197751e-20</v>
       </c>
       <c r="I11" s="0">
-        <v>-7.4217678282963349e-06</v>
+        <v>-7.353508970053763e-06</v>
       </c>
       <c r="J11" s="0">
-        <v>-4.8661063605542112e-10</v>
+        <v>-4.7574713133123343e-10</v>
       </c>
       <c r="K11" s="0">
         <v>1</v>
@@ -3126,39 +3126,39 @@
         <v>0</v>
       </c>
       <c r="O11" s="0">
-        <v>0.024946383482634157</v>
+        <v>0.024946383484135828</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>644</v>
+        <v>750</v>
       </c>
       <c r="B12" s="0">
-        <v>0.64522645358968622</v>
+        <v>0.64522645365168074</v>
       </c>
       <c r="C12" s="0">
         <v>0.014572179450549456</v>
       </c>
       <c r="D12" s="0">
-        <v>3.9509096050493192e-05</v>
+        <v>3.9516657974319803e-05</v>
       </c>
       <c r="E12" s="0">
-        <v>3.9161728526384605e-05</v>
+        <v>3.916172851490636e-05</v>
       </c>
       <c r="F12" s="0">
-        <v>-2.2771554133643969e-08</v>
+        <v>-1.4460874544795266e-08</v>
       </c>
       <c r="G12" s="0">
-        <v>2.5813735196007472e-07</v>
+        <v>2.5237370598733037e-07</v>
       </c>
       <c r="H12" s="0">
-        <v>-9.0423125477123068e-21</v>
+        <v>-6.4105083868296943e-20</v>
       </c>
       <c r="I12" s="0">
-        <v>1.1223662436671538e-07</v>
+        <v>1.1724627892016378e-07</v>
       </c>
       <c r="J12" s="0">
-        <v>-2.3489808454938854e-10</v>
+        <v>-2.2965094919120577e-10</v>
       </c>
       <c r="K12" s="0">
         <v>1</v>
@@ -3173,39 +3173,39 @@
         <v>0</v>
       </c>
       <c r="O12" s="0">
-        <v>0.007433872138042228</v>
+        <v>0.007433872137289319</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>645</v>
+        <v>751</v>
       </c>
       <c r="B13" s="0">
-        <v>0.82012382005816176</v>
+        <v>0.82012381999086181</v>
       </c>
       <c r="C13" s="0">
         <v>0.041016255714285729</v>
       </c>
       <c r="D13" s="0">
-        <v>9.1901528611756472e-05</v>
+        <v>9.175006478765779e-05</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>6.548333313547157e-05</v>
+        <v>6.5547319066883402e-05</v>
       </c>
       <c r="G13" s="0">
-        <v>3.1023306351150127e-07</v>
+        <v>3.0254469232444208e-07</v>
       </c>
       <c r="H13" s="0">
-        <v>1.3001852228412135e-20</v>
+        <v>-6.6262897544297192e-21</v>
       </c>
       <c r="I13" s="0">
-        <v>2.6108244573634587e-05</v>
+        <v>2.5900476195157338e-05</v>
       </c>
       <c r="J13" s="0">
-        <v>-2.8216086120073816e-10</v>
+        <v>-2.7516670738573622e-10</v>
       </c>
       <c r="K13" s="0">
         <v>0</v>
@@ -3220,39 +3220,39 @@
         <v>0</v>
       </c>
       <c r="O13" s="0">
-        <v>0.0028304275862942774</v>
+        <v>0.0028304275865118291</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>646</v>
+        <v>752</v>
       </c>
       <c r="B14" s="0">
-        <v>0.92530677364875635</v>
+        <v>0.92530677364918812</v>
       </c>
       <c r="C14" s="0">
         <v>0.045989524065934054</v>
       </c>
       <c r="D14" s="0">
-        <v>2.9767608945274056e-05</v>
+        <v>2.9743461540968997e-05</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>2.5535217611334807e-05</v>
+        <v>2.5547914620479577e-05</v>
       </c>
       <c r="G14" s="0">
-        <v>1.0873353067712138e-07</v>
+        <v>1.0598121516948092e-07</v>
       </c>
       <c r="H14" s="0">
-        <v>-6.2623176361883402e-23</v>
+        <v>-7.8340968147078914e-21</v>
       </c>
       <c r="I14" s="0">
-        <v>4.123756695306085e-06</v>
+        <v>4.0896620934833708e-06</v>
       </c>
       <c r="J14" s="0">
-        <v>-9.8892043957633487e-11</v>
+        <v>-9.6388163424241519e-11</v>
       </c>
       <c r="K14" s="0">
         <v>0</v>
@@ -3267,39 +3267,39 @@
         <v>0</v>
       </c>
       <c r="O14" s="0">
-        <v>0.20318992999815097</v>
+        <v>0.20318992999699975</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>647</v>
+        <v>753</v>
       </c>
       <c r="B15" s="0">
-        <v>0.9079149677423094</v>
+        <v>0.9079149677510141</v>
       </c>
       <c r="C15" s="0">
         <v>0.00061881285714285729</v>
       </c>
       <c r="D15" s="0">
-        <v>0.0001382102124167299</v>
+        <v>0.00013787963894244888</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <v>8.3600351782705097e-05</v>
+        <v>8.3702050963299423e-05</v>
       </c>
       <c r="G15" s="0">
-        <v>6.7210209111169734e-07</v>
+        <v>6.5578869768055837e-07</v>
       </c>
       <c r="H15" s="0">
-        <v>4.7016047218193094e-20</v>
+        <v>3.2775884982789397e-20</v>
       </c>
       <c r="I15" s="0">
-        <v>5.3938370081562954e-05</v>
+        <v>5.3522395970040773e-05</v>
       </c>
       <c r="J15" s="0">
-        <v>-6.1153864989934052e-10</v>
+        <v>-5.9668857191102955e-10</v>
       </c>
       <c r="K15" s="0">
         <v>0</v>
@@ -3314,39 +3314,39 @@
         <v>0</v>
       </c>
       <c r="O15" s="0">
-        <v>0.00027236908705401071</v>
+        <v>0.00027236908704998322</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>648</v>
+        <v>754</v>
       </c>
       <c r="B16" s="0">
-        <v>0.90982261977488854</v>
+        <v>0.90982261985644763</v>
       </c>
       <c r="C16" s="0">
         <v>0.0010574215384615388</v>
       </c>
       <c r="D16" s="0">
-        <v>9.410554002566162e-05</v>
+        <v>9.3963617261293953e-05</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <v>6.8698949810244979e-05</v>
+        <v>6.8764502963016404e-05</v>
       </c>
       <c r="G16" s="0">
-        <v>4.7346159719493751e-07</v>
+        <v>4.6174960701096714e-07</v>
       </c>
       <c r="H16" s="0">
-        <v>3.1261746509128363e-20</v>
+        <v>6.2125724148998798e-21</v>
       </c>
       <c r="I16" s="0">
-        <v>2.4933559357064648e-05</v>
+        <v>2.4737784770840421e-05</v>
       </c>
       <c r="J16" s="0">
-        <v>-4.3073884297347722e-10</v>
+        <v>-4.2007957384504403e-10</v>
       </c>
       <c r="K16" s="0">
         <v>0</v>
@@ -3361,39 +3361,39 @@
         <v>0</v>
       </c>
       <c r="O16" s="0">
-        <v>0.00033576085877726582</v>
+        <v>0.00033576085874542156</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>649</v>
+        <v>755</v>
       </c>
       <c r="B17" s="0">
-        <v>0.7924154816897645</v>
+        <v>0.79241548245486415</v>
       </c>
       <c r="C17" s="0">
         <v>0.0013863102197802196</v>
       </c>
       <c r="D17" s="0">
-        <v>0.00011939905729595247</v>
+        <v>0.00011930713082843225</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <v>0.0001017910660077459</v>
+        <v>0.00010185016431875234</v>
       </c>
       <c r="G17" s="0">
-        <v>4.8784566345656374e-07</v>
+        <v>4.7551261133889963e-07</v>
       </c>
       <c r="H17" s="0">
-        <v>1.8509319192705241e-20</v>
+        <v>7.4108974288538521e-21</v>
       </c>
       <c r="I17" s="0">
-        <v>1.7120589333343619e-05</v>
+        <v>1.6981886387181016e-05</v>
       </c>
       <c r="J17" s="0">
-        <v>-4.4370859362670933e-10</v>
+        <v>-4.3248884001203364e-10</v>
       </c>
       <c r="K17" s="0">
         <v>0</v>
@@ -3408,39 +3408,39 @@
         <v>0</v>
       </c>
       <c r="O17" s="0">
-        <v>0.0016809314053617423</v>
+        <v>0.0016809314037300159</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>650</v>
+        <v>756</v>
       </c>
       <c r="B18" s="0">
-        <v>0.82169818775600156</v>
+        <v>0.82169818838093611</v>
       </c>
       <c r="C18" s="0">
         <v>0.0015645810989010991</v>
       </c>
       <c r="D18" s="0">
-        <v>4.7486616824928346e-05</v>
+        <v>4.7438783007102674e-05</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <v>4.0044602872017626e-05</v>
+        <v>4.0061545481187327e-05</v>
       </c>
       <c r="G18" s="0">
-        <v>1.4355253727914297e-07</v>
+        <v>1.398938884164368e-07</v>
       </c>
       <c r="H18" s="0">
-        <v>3.3069384410309778e-20</v>
+        <v>2.4137121589333148e-20</v>
       </c>
       <c r="I18" s="0">
-        <v>7.2985919497078241e-06</v>
+        <v>7.2374708437147967e-06</v>
       </c>
       <c r="J18" s="0">
-        <v>-1.3053407627978367e-10</v>
+        <v>-1.2720621591125712e-10</v>
       </c>
       <c r="K18" s="0">
         <v>0</v>
@@ -3455,39 +3455,39 @@
         <v>0</v>
       </c>
       <c r="O18" s="0">
-        <v>0.00056200465729003876</v>
+        <v>0.00056200465685968964</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>651</v>
+        <v>757</v>
       </c>
       <c r="B19" s="0">
-        <v>0.74945301207952264</v>
+        <v>0.74945301184209867</v>
       </c>
       <c r="C19" s="0">
         <v>0.0035383113186813198</v>
       </c>
       <c r="D19" s="0">
-        <v>2.5493794132045542e-05</v>
+        <v>2.5508041084946226e-05</v>
       </c>
       <c r="E19" s="0">
-        <v>6.3640208230779577e-05</v>
+        <v>6.3640208300538108e-05</v>
       </c>
       <c r="F19" s="0">
-        <v>-3.451129320698893e-05</v>
+        <v>-3.4527694291789354e-05</v>
       </c>
       <c r="G19" s="0">
-        <v>3.0459593882615888e-07</v>
+        <v>2.9794658465313174e-07</v>
       </c>
       <c r="H19" s="0">
-        <v>-1.6713476928293082e-18</v>
+        <v>-1.6699445357759873e-18</v>
       </c>
       <c r="I19" s="0">
-        <v>-3.9394396536370218e-06</v>
+        <v>-3.9021483851181543e-06</v>
       </c>
       <c r="J19" s="0">
-        <v>-2.7717693256805443e-10</v>
+        <v>-2.7112333583774977e-10</v>
       </c>
       <c r="K19" s="0">
         <v>1</v>
@@ -3502,39 +3502,39 @@
         <v>0</v>
       </c>
       <c r="O19" s="0">
-        <v>0.00030151334493098151</v>
+        <v>0.00030151334502493223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>652</v>
+        <v>758</v>
       </c>
       <c r="B20" s="0">
-        <v>0.67062566720905337</v>
+        <v>0.6706256672362465</v>
       </c>
       <c r="C20" s="0">
         <v>0.013227400879120874</v>
       </c>
       <c r="D20" s="0">
-        <v>3.8450676871503243e-05</v>
+        <v>3.8508803434316755e-05</v>
       </c>
       <c r="E20" s="0">
-        <v>0.00010053981715883349</v>
+        <v>0.00010053981719394424</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.8297531699323941e-05</v>
+        <v>-4.8349358546930909e-05</v>
       </c>
       <c r="G20" s="0">
-        <v>4.0829240667937707e-07</v>
+        <v>3.9937704680957916e-07</v>
       </c>
       <c r="H20" s="0">
-        <v>2.2351993308451077e-20</v>
+        <v>-2.6219155524955266e-20</v>
       </c>
       <c r="I20" s="0">
-        <v>-1.4199529481621376e-05</v>
+        <v>-1.408066886211984e-05</v>
       </c>
       <c r="J20" s="0">
-        <v>-3.7151306431725505e-10</v>
+        <v>-3.6339738629120085e-10</v>
       </c>
       <c r="K20" s="0">
         <v>0</v>
@@ -3549,39 +3549,39 @@
         <v>0</v>
       </c>
       <c r="O20" s="0">
-        <v>0.0046807748638005384</v>
+        <v>0.0046807748635864016</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>653</v>
+        <v>759</v>
       </c>
       <c r="B21" s="0">
-        <v>0.72714244584911225</v>
+        <v>0.72714244585210863</v>
       </c>
       <c r="C21" s="0">
         <v>0.020689979230769231</v>
       </c>
       <c r="D21" s="0">
-        <v>4.8882346619400097e-05</v>
+        <v>4.8918563129615965e-05</v>
       </c>
       <c r="E21" s="0">
-        <v>7.8949506548336201e-05</v>
+        <v>7.8949506544632011e-05</v>
       </c>
       <c r="F21" s="0">
-        <v>-2.3654105915257146e-05</v>
+        <v>-2.3671133381418599e-05</v>
       </c>
       <c r="G21" s="0">
-        <v>3.8950298428250339e-07</v>
+        <v>3.8096100509163953e-07</v>
       </c>
       <c r="H21" s="0">
-        <v>8.4210202465454044e-21</v>
+        <v>-1.5818144539132807e-19</v>
       </c>
       <c r="I21" s="0">
-        <v>-6.8022025398680036e-06</v>
+        <v>-6.740424358010717e-06</v>
       </c>
       <c r="J21" s="0">
-        <v>-3.5445809346563696e-10</v>
+        <v>-3.4668067821139317e-10</v>
       </c>
       <c r="K21" s="0">
         <v>1</v>
@@ -3596,39 +3596,39 @@
         <v>0</v>
       </c>
       <c r="O21" s="0">
-        <v>0.063034478811684391</v>
+        <v>0.063034478811096931</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>654</v>
+        <v>760</v>
       </c>
       <c r="B22" s="0">
-        <v>0.6896356885712891</v>
+        <v>0.68963568877976777</v>
       </c>
       <c r="C22" s="0">
         <v>0.035353695054945039</v>
       </c>
       <c r="D22" s="0">
-        <v>2.9759960063147116e-05</v>
+        <v>2.9782637852873605e-05</v>
       </c>
       <c r="E22" s="0">
-        <v>5.0143784421009414e-05</v>
+        <v>5.0143784441965768e-05</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.6342450228314121e-05</v>
+        <v>-1.6353469102873748e-05</v>
       </c>
       <c r="G22" s="0">
-        <v>2.5705241648671219e-07</v>
+        <v>2.5141581315421454e-07</v>
       </c>
       <c r="H22" s="0">
-        <v>2.0035263837222149e-21</v>
+        <v>-5.6238424782118471e-20</v>
       </c>
       <c r="I22" s="0">
-        <v>-4.2981926122729137e-06</v>
+        <v>-4.2588644978390034e-06</v>
       </c>
       <c r="J22" s="0">
-        <v>-2.3393376197789145e-10</v>
+        <v>-2.2880153357081697e-10</v>
       </c>
       <c r="K22" s="0">
         <v>1</v>
@@ -3643,39 +3643,39 @@
         <v>0</v>
       </c>
       <c r="O22" s="0">
-        <v>0.0054146667783116593</v>
+        <v>0.0054146667766466379</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>655</v>
+        <v>761</v>
       </c>
       <c r="B23" s="0">
-        <v>0.81607049181438751</v>
+        <v>0.81607049158119394</v>
       </c>
       <c r="C23" s="0">
         <v>0.00058346373626373617</v>
       </c>
       <c r="D23" s="0">
-        <v>9.9456023349242601e-05</v>
+        <v>9.940890324955792e-05</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
       </c>
       <c r="F23" s="0">
-        <v>9.116493879599149e-05</v>
+        <v>9.1192310291646168e-05</v>
       </c>
       <c r="G23" s="0">
-        <v>4.0700721994587858e-07</v>
+        <v>3.9649594465552037e-07</v>
       </c>
       <c r="H23" s="0">
-        <v>3.2128127588003461e-20</v>
+        <v>9.2772251172019475e-21</v>
       </c>
       <c r="I23" s="0">
-        <v>7.88444750201664e-06</v>
+        <v>7.8204576203762985e-06</v>
       </c>
       <c r="J23" s="0">
-        <v>-3.7016871143845387e-10</v>
+        <v>-3.6060712007535372e-10</v>
       </c>
       <c r="K23" s="0">
         <v>0</v>
@@ -3690,39 +3690,39 @@
         <v>0</v>
       </c>
       <c r="O23" s="0">
-        <v>0.00058677680589867734</v>
+        <v>0.00058677680606329902</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>656</v>
+        <v>762</v>
       </c>
       <c r="B24" s="0">
-        <v>0.83693409514047812</v>
+        <v>0.83693409451307599</v>
       </c>
       <c r="C24" s="0">
         <v>0.00077550758241758219</v>
       </c>
       <c r="D24" s="0">
-        <v>0.00011357762425406135</v>
+        <v>0.00011338625394747186</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>7.933617602112247e-05</v>
+        <v>7.9421670131862705e-05</v>
       </c>
       <c r="G24" s="0">
-        <v>4.24618521359168e-07</v>
+        <v>4.1414210931258248e-07</v>
       </c>
       <c r="H24" s="0">
-        <v>4.911759740633145e-20</v>
+        <v>3.7350597991878035e-20</v>
       </c>
       <c r="I24" s="0">
-        <v>3.3817215967530085e-05</v>
+        <v>3.3550818429401177e-05</v>
       </c>
       <c r="J24" s="0">
-        <v>-3.8625595041483999e-10</v>
+        <v>-3.7672310464962862e-10</v>
       </c>
       <c r="K24" s="0">
         <v>0</v>
@@ -3737,39 +3737,39 @@
         <v>0</v>
       </c>
       <c r="O24" s="0">
-        <v>0.00072234289962918663</v>
+        <v>0.00072234290016693053</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>657</v>
+        <v>763</v>
       </c>
       <c r="B25" s="0">
-        <v>0.87863421383823914</v>
+        <v>0.87863421325276381</v>
       </c>
       <c r="C25" s="0">
         <v>0.00163550934065934</v>
       </c>
       <c r="D25" s="0">
-        <v>6.8279207356167503e-05</v>
+        <v>6.8223849344302138e-05</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
       </c>
       <c r="F25" s="0">
-        <v>5.814835434639939e-05</v>
+        <v>5.8180156083640223e-05</v>
       </c>
       <c r="G25" s="0">
-        <v>2.8201211574842716e-07</v>
+        <v>2.7484467094602933e-07</v>
       </c>
       <c r="H25" s="0">
-        <v>-6.0731212617548161e-20</v>
+        <v>-2.2964486128587201e-19</v>
       </c>
       <c r="I25" s="0">
-        <v>9.8490974030884381e-06</v>
+        <v>9.7690985778804226e-06</v>
       </c>
       <c r="J25" s="0">
-        <v>-2.5650906869216766e-10</v>
+        <v>-2.4998816430583817e-10</v>
       </c>
       <c r="K25" s="0">
         <v>0</v>
@@ -3784,39 +3784,39 @@
         <v>0</v>
       </c>
       <c r="O25" s="0">
-        <v>0.0023118952260676247</v>
+        <v>0.0023118952275961299</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>658</v>
+        <v>764</v>
       </c>
       <c r="B26" s="0">
-        <v>0.81001725405564173</v>
+        <v>0.8100172540067323</v>
       </c>
       <c r="C26" s="0">
         <v>0.01328132923076923</v>
       </c>
       <c r="D26" s="0">
-        <v>2.9524757829087522e-05</v>
+        <v>2.9550725768782437e-05</v>
       </c>
       <c r="E26" s="0">
-        <v>5.9378452703179745e-05</v>
+        <v>5.9378452696773967e-05</v>
       </c>
       <c r="F26" s="0">
-        <v>-2.4164107637880828e-05</v>
+        <v>-2.4184640411913225e-05</v>
       </c>
       <c r="G26" s="0">
-        <v>2.9697944544973829e-07</v>
+        <v>2.904616129857484e-07</v>
       </c>
       <c r="H26" s="0">
-        <v>-1.7655839615402114e-20</v>
+        <v>-7.8568234006894772e-20</v>
       </c>
       <c r="I26" s="0">
-        <v>-5.9862964133213797e-06</v>
+        <v>-5.9332837953787755e-06</v>
       </c>
       <c r="J26" s="0">
-        <v>-2.7026833973639965e-10</v>
+        <v>-2.6433368519875148e-10</v>
       </c>
       <c r="K26" s="0">
         <v>1</v>
@@ -3831,39 +3831,39 @@
         <v>0</v>
       </c>
       <c r="O26" s="0">
-        <v>0.02226083189033868</v>
+        <v>0.022260831891567068</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>659</v>
+        <v>765</v>
       </c>
       <c r="B27" s="0">
-        <v>0.57923297511811345</v>
+        <v>0.57923297472173718</v>
       </c>
       <c r="C27" s="0">
         <v>0.014742598461538463</v>
       </c>
       <c r="D27" s="0">
-        <v>8.039736329020892e-05</v>
+        <v>8.0480749508106514e-05</v>
       </c>
       <c r="E27" s="0">
-        <v>0.00018925866947844326</v>
+        <v>0.00018925866941563467</v>
       </c>
       <c r="F27" s="0">
-        <v>-8.8400000973341478e-05</v>
+        <v>-8.8482117465162432e-05</v>
       </c>
       <c r="G27" s="0">
-        <v>6.9816961779282532e-07</v>
+        <v>6.8296689447113501e-07</v>
       </c>
       <c r="H27" s="0">
-        <v>6.3514483618932129e-20</v>
+        <v>-4.9630956241280695e-21</v>
       </c>
       <c r="I27" s="0">
-        <v>-2.1158839617675227e-05</v>
+        <v>-2.0978147959269384e-05</v>
       </c>
       <c r="J27" s="0">
-        <v>-6.3521501052522258e-10</v>
+        <v>-6.2137756747266825e-10</v>
       </c>
       <c r="K27" s="0">
         <v>0</v>
@@ -3878,39 +3878,39 @@
         <v>0</v>
       </c>
       <c r="O27" s="0">
-        <v>0.00042356892264797563</v>
+        <v>0.00042356892293562683</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>660</v>
+        <v>766</v>
       </c>
       <c r="B28" s="0">
-        <v>0.88645176910926837</v>
+        <v>0.88645176921665325</v>
       </c>
       <c r="C28" s="0">
         <v>0.00056269538461538424</v>
       </c>
       <c r="D28" s="0">
-        <v>0.00011336813086471956</v>
+        <v>0.00011317042913267155</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>7.9360891190784484e-05</v>
+        <v>7.9439894337674917e-05</v>
       </c>
       <c r="G28" s="0">
-        <v>5.1568363707410218e-07</v>
+        <v>5.0294592170058149e-07</v>
       </c>
       <c r="H28" s="0">
-        <v>2.667321611146074e-19</v>
+        <v>1.7586783244224844e-19</v>
       </c>
       <c r="I28" s="0">
-        <v>3.3492025181715915e-05</v>
+        <v>3.3228046425811228e-05</v>
       </c>
       <c r="J28" s="0">
-        <v>-4.6914485520016666e-10</v>
+        <v>-4.5755251535306227e-10</v>
       </c>
       <c r="K28" s="0">
         <v>0</v>
@@ -3925,39 +3925,39 @@
         <v>0</v>
       </c>
       <c r="O28" s="0">
-        <v>8.0551217088880911e-05</v>
+        <v>8.0551217078704115e-05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>661</v>
+        <v>767</v>
       </c>
       <c r="B29" s="0">
-        <v>0.68710694899702685</v>
+        <v>0.68710694951369455</v>
       </c>
       <c r="C29" s="0">
         <v>0.016124222307692306</v>
       </c>
       <c r="D29" s="0">
-        <v>7.8581164955533728e-05</v>
+        <v>7.8634617020582989e-05</v>
       </c>
       <c r="E29" s="0">
-        <v>0.00012799179861964398</v>
+        <v>0.00012799179871744997</v>
       </c>
       <c r="F29" s="0">
-        <v>-3.9249997143795813e-05</v>
+        <v>-3.9280670297044029e-05</v>
       </c>
       <c r="G29" s="0">
-        <v>5.4860189094401007e-07</v>
+        <v>5.3658792545681176e-07</v>
       </c>
       <c r="H29" s="0">
-        <v>-1.038329844754597e-20</v>
+        <v>-5.4803255830037175e-20</v>
       </c>
       <c r="I29" s="0">
-        <v>-1.0708739214576689e-05</v>
+        <v>-1.0612611065676383e-05</v>
       </c>
       <c r="J29" s="0">
-        <v>-4.9919668175170569e-10</v>
+        <v>-4.8825960332474412e-10</v>
       </c>
       <c r="K29" s="0">
         <v>1</v>
@@ -3972,39 +3972,39 @@
         <v>0</v>
       </c>
       <c r="O29" s="0">
-        <v>0.003834419254901042</v>
+        <v>0.0038344192519978279</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>662</v>
+        <v>768</v>
       </c>
       <c r="B30" s="0">
-        <v>0.77759445748602507</v>
+        <v>0.77759445751360423</v>
       </c>
       <c r="C30" s="0">
         <v>0.014526590109890108</v>
       </c>
       <c r="D30" s="0">
-        <v>3.1236256344977536e-05</v>
+        <v>3.1260874102468631e-05</v>
       </c>
       <c r="E30" s="0">
-        <v>5.405171856976819e-05</v>
+        <v>5.4051718498037184e-05</v>
       </c>
       <c r="F30" s="0">
-        <v>-1.8060674278515733e-05</v>
+        <v>-1.8075141498184699e-05</v>
       </c>
       <c r="G30" s="0">
-        <v>2.5988141125691013e-07</v>
+        <v>2.5419369962708454e-07</v>
       </c>
       <c r="H30" s="0">
-        <v>2.4674628790192807e-20</v>
+        <v>-3.4461274691516871e-20</v>
       </c>
       <c r="I30" s="0">
-        <v>-5.0144328544869073e-06</v>
+        <v>-4.9696652726988279e-06</v>
       </c>
       <c r="J30" s="0">
-        <v>-2.3650304494820151e-10</v>
+        <v>-2.3132431207587711e-10</v>
       </c>
       <c r="K30" s="0">
         <v>1</v>
@@ -4019,39 +4019,39 @@
         <v>0</v>
       </c>
       <c r="O30" s="0">
-        <v>0.03483656235656777</v>
+        <v>0.034836562355151077</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>663</v>
+        <v>769</v>
       </c>
       <c r="B31" s="0">
-        <v>0.91705560397319819</v>
+        <v>0.91705560400373709</v>
       </c>
       <c r="C31" s="0">
         <v>0.0023755154945054946</v>
       </c>
       <c r="D31" s="0">
-        <v>0.00010567072799046875</v>
+        <v>0.00010543645792803074</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>
       </c>
       <c r="F31" s="0">
-        <v>6.5301608567785145e-05</v>
+        <v>6.5384364506783436e-05</v>
       </c>
       <c r="G31" s="0">
-        <v>4.6863706459366679e-07</v>
+        <v>4.5731100103072351e-07</v>
       </c>
       <c r="H31" s="0">
-        <v>7.6004074491030812e-20</v>
+        <v>6.9606686014824838e-20</v>
       </c>
       <c r="I31" s="0">
-        <v>3.9900908721494402e-05</v>
+        <v>3.9595198475195246e-05</v>
       </c>
       <c r="J31" s="0">
-        <v>-4.2636340453621217e-10</v>
+        <v>-4.1605497873135628e-10</v>
       </c>
       <c r="K31" s="0">
         <v>0</v>
@@ -4066,39 +4066,39 @@
         <v>0</v>
       </c>
       <c r="O31" s="0">
-        <v>0.00031365805056520634</v>
+        <v>0.0003136580505531305</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>664</v>
+        <v>770</v>
       </c>
       <c r="B32" s="0">
-        <v>0.76611404182693987</v>
+        <v>0.76611404182759835</v>
       </c>
       <c r="C32" s="0">
         <v>0.013309501648351648</v>
       </c>
       <c r="D32" s="0">
-        <v>3.0046298138349186e-05</v>
+        <v>3.0070749049865186e-05</v>
       </c>
       <c r="E32" s="0">
-        <v>5.6876094731229577e-05</v>
+        <v>5.6876094738498522e-05</v>
       </c>
       <c r="F32" s="0">
-        <v>-2.1765305463159791e-05</v>
+        <v>-2.1782547288409527e-05</v>
       </c>
       <c r="G32" s="0">
-        <v>2.9398479957646472e-07</v>
+        <v>2.8752983753404239e-07</v>
       </c>
       <c r="H32" s="0">
-        <v>-2.3013034901401152e-20</v>
+        <v>-9.3870980770393065e-20</v>
       </c>
       <c r="I32" s="0">
-        <v>-5.358208389466769e-06</v>
+        <v>-5.3100665751998995e-06</v>
       </c>
       <c r="J32" s="0">
-        <v>-2.6753983027260849e-10</v>
+        <v>-2.6166255785830525e-10</v>
       </c>
       <c r="K32" s="0">
         <v>1</v>
@@ -4113,39 +4113,39 @@
         <v>0</v>
       </c>
       <c r="O32" s="0">
-        <v>0.035179202987826438</v>
+        <v>0.035179202987613303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
-        <v>665</v>
+        <v>771</v>
       </c>
       <c r="B33" s="0">
-        <v>0.81210548499654189</v>
+        <v>0.81210548491603707</v>
       </c>
       <c r="C33" s="0">
         <v>0.00021664318681318683</v>
       </c>
       <c r="D33" s="0">
-        <v>7.3304835627677501e-05</v>
+        <v>7.3240756842559175e-05</v>
       </c>
       <c r="E33" s="0">
         <v>0</v>
       </c>
       <c r="F33" s="0">
-        <v>6.0287482834733499e-05</v>
+        <v>6.0332758007390699e-05</v>
       </c>
       <c r="G33" s="0">
-        <v>3.2745919131758148e-07</v>
+        <v>3.1936554913241939e-07</v>
       </c>
       <c r="H33" s="0">
-        <v>2.5262541783038437e-19</v>
+        <v>-1.4235129069282196e-18</v>
       </c>
       <c r="I33" s="0">
-        <v>1.2690191429633743e-05</v>
+        <v>1.2588923751159853e-05</v>
       </c>
       <c r="J33" s="0">
-        <v>-2.9782800757499432e-10</v>
+        <v>-2.9046512237450664e-10</v>
       </c>
       <c r="K33" s="0">
         <v>0</v>
@@ -4160,39 +4160,39 @@
         <v>0</v>
       </c>
       <c r="O33" s="0">
-        <v>0.00013725457694788287</v>
+        <v>0.00013725457696077547</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>666</v>
+        <v>772</v>
       </c>
       <c r="B34" s="0">
-        <v>0.78938339089885556</v>
+        <v>0.78938339007987779</v>
       </c>
       <c r="C34" s="0">
         <v>0.00026451241758241754</v>
       </c>
       <c r="D34" s="0">
-        <v>0.00023715626992408539</v>
+        <v>0.00023673552200075698</v>
       </c>
       <c r="E34" s="0">
         <v>0</v>
       </c>
       <c r="F34" s="0">
-        <v>0.0001674665856703103</v>
+        <v>0.00016761793665953049</v>
       </c>
       <c r="G34" s="0">
-        <v>1.1454546020891747e-06</v>
+        <v>1.1170580758367471e-06</v>
       </c>
       <c r="H34" s="0">
-        <v>3.9912880501364333e-19</v>
+        <v>3.945071249857744e-19</v>
       </c>
       <c r="I34" s="0">
-        <v>6.8545271654995863e-05</v>
+        <v>6.8001543428626129e-05</v>
       </c>
       <c r="J34" s="0">
-        <v>-1.0420033103372825e-09</v>
+        <v>-1.0161632367803805e-09</v>
       </c>
       <c r="K34" s="0">
         <v>0</v>
@@ -4207,39 +4207,39 @@
         <v>0</v>
       </c>
       <c r="O34" s="0">
-        <v>5.1795788117306884e-05</v>
+        <v>5.1795788170775229e-05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>667</v>
+        <v>773</v>
       </c>
       <c r="B35" s="0">
-        <v>0.72881785879860883</v>
+        <v>0.7288178584438606</v>
       </c>
       <c r="C35" s="0">
-        <v>0.0032344040659340666</v>
+        <v>0.0036720769230769229</v>
       </c>
       <c r="D35" s="0">
-        <v>3.1164100720828455e-05</v>
+        <v>3.1187021677915456e-05</v>
       </c>
       <c r="E35" s="0">
-        <v>8.4520767128244727e-05</v>
+        <v>8.4520767161502588e-05</v>
       </c>
       <c r="F35" s="0">
-        <v>-4.5823335655633325e-05</v>
+        <v>-4.586172341564763e-05</v>
       </c>
       <c r="G35" s="0">
-        <v>3.465844490647587e-07</v>
+        <v>3.3902340936278808e-07</v>
       </c>
       <c r="H35" s="0">
-        <v>-3.5467544036045714e-17</v>
+        <v>-3.5604202780715287e-17</v>
       </c>
       <c r="I35" s="0">
-        <v>-7.8795998408405237e-06</v>
+        <v>-7.8107370003818416e-06</v>
       </c>
       <c r="J35" s="0">
-        <v>-3.153599717146537e-10</v>
+        <v>-3.0847688484413873e-10</v>
       </c>
       <c r="K35" s="0">
         <v>1</v>
@@ -4254,39 +4254,39 @@
         <v>0</v>
       </c>
       <c r="O35" s="0">
-        <v>0.0028041018716778812</v>
+        <v>0.0028041018730281838</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>668</v>
+        <v>774</v>
       </c>
       <c r="B36" s="0">
-        <v>0.82119446195065471</v>
+        <v>0.82119446191327083</v>
       </c>
       <c r="C36" s="0">
         <v>0.0020271178021978027</v>
       </c>
       <c r="D36" s="0">
-        <v>6.5065490825406429e-05</v>
+        <v>6.5030650853769418e-05</v>
       </c>
       <c r="E36" s="0">
         <v>0</v>
       </c>
       <c r="F36" s="0">
-        <v>5.93904719371898e-05</v>
+        <v>5.9406610003786653e-05</v>
       </c>
       <c r="G36" s="0">
-        <v>2.1264528307085288e-07</v>
+        <v>2.0715161852187433e-07</v>
       </c>
       <c r="H36" s="0">
-        <v>3.3890874508085794e-20</v>
+        <v>2.5101037159291913e-20</v>
       </c>
       <c r="I36" s="0">
-        <v>5.4625669874608687e-06</v>
+        <v>5.4170776169023547e-06</v>
       </c>
       <c r="J36" s="0">
-        <v>-1.93382315126263e-10</v>
+        <v>-1.8838544148979319e-10</v>
       </c>
       <c r="K36" s="0">
         <v>0</v>
@@ -4301,39 +4301,39 @@
         <v>0</v>
       </c>
       <c r="O36" s="0">
-        <v>0.00051322943500789432</v>
+        <v>0.00051322943502859011</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>669</v>
+        <v>775</v>
       </c>
       <c r="B37" s="0">
-        <v>0.81316977794823553</v>
+        <v>0.81316977808894941</v>
       </c>
       <c r="C37" s="0">
         <v>0.0069718854945054936</v>
       </c>
       <c r="D37" s="0">
-        <v>6.7224588726293682e-07</v>
+        <v>6.6937479738015162e-07</v>
       </c>
       <c r="E37" s="0">
         <v>0</v>
       </c>
       <c r="F37" s="0">
-        <v>6.1056099384431417e-07</v>
+        <v>6.087244037841021e-07</v>
       </c>
       <c r="G37" s="0">
-        <v>4.2277201952292702e-08</v>
+        <v>4.122696022648038e-08</v>
       </c>
       <c r="H37" s="0">
-        <v>-5.6116137950586154e-21</v>
+        <v>-3.3537657357821093e-20</v>
       </c>
       <c r="I37" s="0">
-        <v>1.944610425718479e-08</v>
+        <v>1.9460892302132682e-08</v>
       </c>
       <c r="J37" s="0">
-        <v>-3.8412790849224454e-11</v>
+        <v>-3.7458932530010468e-11</v>
       </c>
       <c r="K37" s="0">
         <v>0</v>
@@ -4348,39 +4348,39 @@
         <v>1</v>
       </c>
       <c r="O37" s="0">
-        <v>0.00094672210297341906</v>
+        <v>0.00094672210280467254</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>670</v>
+        <v>776</v>
       </c>
       <c r="B38" s="0">
-        <v>0.50886706745243537</v>
+        <v>0.50886706740239385</v>
       </c>
       <c r="C38" s="0">
         <v>0.0054763300000000023</v>
       </c>
       <c r="D38" s="0">
-        <v>6.3115385394699086e-05</v>
+        <v>6.3175254686169944e-05</v>
       </c>
       <c r="E38" s="0">
-        <v>0.00013362581415844163</v>
+        <v>0.00013362581434950394</v>
       </c>
       <c r="F38" s="0">
-        <v>-5.7167812741375858e-05</v>
+        <v>-5.7216901530663384e-05</v>
       </c>
       <c r="G38" s="0">
-        <v>6.0557552452158194e-07</v>
+        <v>5.9231753196598707e-07</v>
       </c>
       <c r="H38" s="0">
-        <v>-2.8622844532201652e-20</v>
+        <v>-1.4893276659388109e-19</v>
       </c>
       <c r="I38" s="0">
-        <v>-1.3947640506920904e-05</v>
+        <v>-1.3825436694200799e-05</v>
       </c>
       <c r="J38" s="0">
-        <v>-5.5103996733322374e-10</v>
+        <v>-5.3897043564762599e-10</v>
       </c>
       <c r="K38" s="0">
         <v>0</v>
@@ -4395,39 +4395,39 @@
         <v>0</v>
       </c>
       <c r="O38" s="0">
-        <v>0.0025855130876362596</v>
+        <v>0.0025855130878770739</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>671</v>
+        <v>777</v>
       </c>
       <c r="B39" s="0">
-        <v>0.89510413373288555</v>
+        <v>0.89510413362604568</v>
       </c>
       <c r="C39" s="0">
         <v>0.00085353087912087876</v>
       </c>
       <c r="D39" s="0">
-        <v>7.5932450195967979e-05</v>
+        <v>7.5780413320849805e-05</v>
       </c>
       <c r="E39" s="0">
         <v>0</v>
       </c>
       <c r="F39" s="0">
-        <v>4.9102939363580551e-05</v>
+        <v>4.916366581072905e-05</v>
       </c>
       <c r="G39" s="0">
-        <v>2.3599395570158814e-07</v>
+        <v>2.3024146825840697e-07</v>
       </c>
       <c r="H39" s="0">
-        <v>-1.7223194512853772e-21</v>
+        <v>-1.6792627277578625e-20</v>
       </c>
       <c r="I39" s="0">
-        <v>2.659373153422713e-05</v>
+        <v>2.6386715465666626e-05</v>
       </c>
       <c r="J39" s="0">
-        <v>-2.1465754128764886e-10</v>
+        <v>-2.0942380425989894e-10</v>
       </c>
       <c r="K39" s="0">
         <v>0</v>
@@ -4442,39 +4442,39 @@
         <v>0</v>
       </c>
       <c r="O39" s="0">
-        <v>0.010571392712096167</v>
+        <v>0.010571392713303009</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>672</v>
+        <v>778</v>
       </c>
       <c r="B40" s="0">
-        <v>0.90975405657355435</v>
+        <v>0.90975405654482888</v>
       </c>
       <c r="C40" s="0">
         <v>0.00085380681318681306</v>
       </c>
       <c r="D40" s="0">
-        <v>3.8060981236082497e-05</v>
+        <v>3.8022589950045856e-05</v>
       </c>
       <c r="E40" s="0">
         <v>0</v>
       </c>
       <c r="F40" s="0">
-        <v>3.0943012135166473e-05</v>
+        <v>3.0964597108786451e-05</v>
       </c>
       <c r="G40" s="0">
-        <v>1.4213373365985839e-07</v>
+        <v>1.3856848616908648e-07</v>
       </c>
       <c r="H40" s="0">
-        <v>3.0409968611406518e-22</v>
+        <v>-1.9489307689593433e-20</v>
       </c>
       <c r="I40" s="0">
-        <v>6.9759646406041558e-06</v>
+        <v>6.9195503850410952e-06</v>
       </c>
       <c r="J40" s="0">
-        <v>-1.2927334798993223e-10</v>
+        <v>-1.2602995075687958e-10</v>
       </c>
       <c r="K40" s="0">
         <v>0</v>
@@ -4489,39 +4489,39 @@
         <v>0</v>
       </c>
       <c r="O40" s="0">
-        <v>0.025289094401765438</v>
+        <v>0.025289094402432471</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>673</v>
+        <v>779</v>
       </c>
       <c r="B41" s="0">
-        <v>0.44492538831216377</v>
+        <v>0.44492538831376283</v>
       </c>
       <c r="C41" s="0">
         <v>0.014438330329670323</v>
       </c>
       <c r="D41" s="0">
-        <v>3.2934860639947289e-05</v>
+        <v>3.2972741690455487e-05</v>
       </c>
       <c r="E41" s="0">
-        <v>7.7541363087191696e-05</v>
+        <v>7.7541363004633319e-05</v>
       </c>
       <c r="F41" s="0">
-        <v>-3.6551064709201752e-05</v>
+        <v>-3.6579846724866026e-05</v>
       </c>
       <c r="G41" s="0">
-        <v>4.3983436663902738e-07</v>
+        <v>4.3010528071348847e-07</v>
       </c>
       <c r="H41" s="0">
-        <v>-8.6510860597061163e-21</v>
+        <v>-7.4622337814632632e-20</v>
       </c>
       <c r="I41" s="0">
-        <v>-8.4948718407344725e-06</v>
+        <v>-8.4184884644190793e-06</v>
       </c>
       <c r="J41" s="0">
-        <v>-4.0026394720203598e-10</v>
+        <v>-3.9140560613940424e-10</v>
       </c>
       <c r="K41" s="0">
         <v>1</v>
@@ -4536,39 +4536,39 @@
         <v>0</v>
       </c>
       <c r="O41" s="0">
-        <v>0.0038241531909349773</v>
+        <v>0.0038241531909013523</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>674</v>
+        <v>780</v>
       </c>
       <c r="B42" s="0">
-        <v>0.7810362480761236</v>
+        <v>0.78103624807029925</v>
       </c>
       <c r="C42" s="0">
         <v>0.024008800989010985</v>
       </c>
       <c r="D42" s="0">
-        <v>3.4321972835234427e-05</v>
+        <v>3.4348655891190586e-05</v>
       </c>
       <c r="E42" s="0">
-        <v>5.9699103720211536e-05</v>
+        <v>5.969910373525125e-05</v>
       </c>
       <c r="F42" s="0">
-        <v>-2.0279200042881406e-05</v>
+        <v>-2.0294622292681753e-05</v>
       </c>
       <c r="G42" s="0">
-        <v>2.8826859125210548e-07</v>
+        <v>2.8196538422849642e-07</v>
       </c>
       <c r="H42" s="0">
-        <v>4.2361830005926584e-19</v>
+        <v>3.339345550908042e-19</v>
       </c>
       <c r="I42" s="0">
-        <v>-5.3859370987574102e-06</v>
+        <v>-5.3375343398910358e-06</v>
       </c>
       <c r="J42" s="0">
-        <v>-2.6233459082218303e-10</v>
+        <v>-2.5659571670508328e-10</v>
       </c>
       <c r="K42" s="0">
         <v>1</v>
@@ -4583,39 +4583,39 @@
         <v>0</v>
       </c>
       <c r="O42" s="0">
-        <v>0.031128519631731071</v>
+        <v>0.031128519631801362</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>675</v>
+        <v>781</v>
       </c>
       <c r="B43" s="0">
-        <v>0.80091288434131924</v>
+        <v>0.80091288431717012</v>
       </c>
       <c r="C43" s="0">
         <v>0.0032003447252747256</v>
       </c>
       <c r="D43" s="0">
-        <v>2.4807712455843329e-05</v>
+        <v>2.4826467814389141e-05</v>
       </c>
       <c r="E43" s="0">
         <v>0</v>
       </c>
       <c r="F43" s="0">
-        <v>2.6747496824652402e-05</v>
+        <v>2.6751462867391288e-05</v>
       </c>
       <c r="G43" s="0">
-        <v>1.2977247067462801e-07</v>
+        <v>1.2648431328461679e-07</v>
       </c>
       <c r="H43" s="0">
-        <v>-4.7795145152824188e-20</v>
+        <v>-5.3181246342707424e-19</v>
       </c>
       <c r="I43" s="0">
-        <v>-2.0694388558026718e-06</v>
+        <v>-2.0513643723664001e-06</v>
       </c>
       <c r="J43" s="0">
-        <v>-1.1798368098136862e-10</v>
+        <v>-1.1499391983190772e-10</v>
       </c>
       <c r="K43" s="0">
         <v>0</v>
@@ -4630,39 +4630,39 @@
         <v>0</v>
       </c>
       <c r="O43" s="0">
-        <v>0.00046492619136151951</v>
+        <v>0.00046492619137312075</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>676</v>
+        <v>782</v>
       </c>
       <c r="B44" s="0">
-        <v>0.90903772064705446</v>
+        <v>0.90903772062833732</v>
       </c>
       <c r="C44" s="0">
         <v>0.0063659247252747251</v>
       </c>
       <c r="D44" s="0">
-        <v>3.9184338458737175e-05</v>
+        <v>3.9211670036849939e-05</v>
       </c>
       <c r="E44" s="0">
-        <v>6.6398648110830625e-05</v>
+        <v>6.6398648115475998e-05</v>
       </c>
       <c r="F44" s="0">
-        <v>-2.1855781190353639e-05</v>
+        <v>-2.1872588160037187e-05</v>
       </c>
       <c r="G44" s="0">
-        <v>3.9291194860015536e-07</v>
+        <v>3.8420163827773932e-07</v>
       </c>
       <c r="H44" s="0">
-        <v>2.9955954207882046e-22</v>
+        <v>-4.1824365403162895e-21</v>
       </c>
       <c r="I44" s="0">
-        <v>-5.7510828479053275e-06</v>
+        <v>-5.6982419248453575e-06</v>
       </c>
       <c r="J44" s="0">
-        <v>-3.5756243463889797e-10</v>
+        <v>-3.4963202124979511e-10</v>
       </c>
       <c r="K44" s="0">
         <v>1</v>
@@ -4677,39 +4677,39 @@
         <v>0</v>
       </c>
       <c r="O44" s="0">
-        <v>0.076894676798214281</v>
+        <v>0.076894676799397765</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>677</v>
+        <v>783</v>
       </c>
       <c r="B45" s="0">
-        <v>0.7750744033095478</v>
+        <v>0.77507440361489521</v>
       </c>
       <c r="C45" s="0">
         <v>0.003136649120879121</v>
       </c>
       <c r="D45" s="0">
-        <v>7.6105760585178203e-05</v>
+        <v>7.6059202731699969e-05</v>
       </c>
       <c r="E45" s="0">
         <v>0</v>
       </c>
       <c r="F45" s="0">
-        <v>7.0933820351523792e-05</v>
+        <v>7.0937765139218587e-05</v>
       </c>
       <c r="G45" s="0">
-        <v>2.8672253270193482e-07</v>
+        <v>2.7930928251205748e-07</v>
       </c>
       <c r="H45" s="0">
-        <v>8.154647968582397e-20</v>
+        <v>5.3102449828254335e-20</v>
       </c>
       <c r="I45" s="0">
-        <v>4.8854784582854209e-06</v>
+        <v>4.8423823240224144e-06</v>
       </c>
       <c r="J45" s="0">
-        <v>-2.6075733302590251e-10</v>
+        <v>-2.5401405314292121e-10</v>
       </c>
       <c r="K45" s="0">
         <v>0</v>
@@ -4724,39 +4724,39 @@
         <v>0</v>
       </c>
       <c r="O45" s="0">
-        <v>0.00041514320006591802</v>
+        <v>0.00041514319990021024</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>678</v>
+        <v>784</v>
       </c>
       <c r="B46" s="0">
-        <v>0.7446650776949254</v>
+        <v>0.74466507764501477</v>
       </c>
       <c r="C46" s="0">
         <v>0.00077207417582417627</v>
       </c>
       <c r="D46" s="0">
-        <v>3.9195445744178527e-05</v>
+        <v>3.921480043749046e-05</v>
       </c>
       <c r="E46" s="0">
         <v>0</v>
       </c>
       <c r="F46" s="0">
-        <v>4.3142071518316932e-05</v>
+        <v>4.3136819440625071e-05</v>
       </c>
       <c r="G46" s="0">
-        <v>2.9314749008016992e-07</v>
+        <v>2.8585223080811498e-07</v>
       </c>
       <c r="H46" s="0">
-        <v>1.0965641790101372e-18</v>
+        <v>1.8765241883670734e-19</v>
       </c>
       <c r="I46" s="0">
-        <v>-4.2395066701721439e-06</v>
+        <v>-4.2076112756412638e-06</v>
       </c>
       <c r="J46" s="0">
-        <v>-2.6659404752825741e-10</v>
+        <v>-2.5995830165006844e-10</v>
       </c>
       <c r="K46" s="0">
         <v>0</v>
@@ -4771,39 +4771,39 @@
         <v>0</v>
       </c>
       <c r="O46" s="0">
-        <v>8.2022055859693263e-05</v>
+        <v>8.2022055864764266e-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>679</v>
+        <v>785</v>
       </c>
       <c r="B47" s="0">
-        <v>0.86309745266608595</v>
+        <v>0.86309745266543925</v>
       </c>
       <c r="C47" s="0">
         <v>0.0020190452747252739</v>
       </c>
       <c r="D47" s="0">
-        <v>2.6283951146517036e-05</v>
+        <v>2.6284587909520011e-05</v>
       </c>
       <c r="E47" s="0">
         <v>0</v>
       </c>
       <c r="F47" s="0">
-        <v>2.9742880747172226e-05</v>
+        <v>2.971995930966555e-05</v>
       </c>
       <c r="G47" s="0">
-        <v>1.2763742521396534e-07</v>
+        <v>1.2428410989223497e-07</v>
       </c>
       <c r="H47" s="0">
-        <v>1.2190626529108005e-19</v>
+        <v>1.2575478443824829e-19</v>
       </c>
       <c r="I47" s="0">
-        <v>-3.5864509329854248e-06</v>
+        <v>-3.5595424678598024e-06</v>
       </c>
       <c r="J47" s="0">
-        <v>-1.1609288385319358e-10</v>
+        <v>-1.1304217809703093e-10</v>
       </c>
       <c r="K47" s="0">
         <v>0</v>
@@ -4818,39 +4818,39 @@
         <v>0</v>
       </c>
       <c r="O47" s="0">
-        <v>0.00018338592866790613</v>
+        <v>0.00018338592866709005</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>680</v>
+        <v>786</v>
       </c>
       <c r="B48" s="0">
-        <v>0.83203566382320415</v>
+        <v>0.83203566378564087</v>
       </c>
       <c r="C48" s="0">
         <v>0.0070545008791208785</v>
       </c>
       <c r="D48" s="0">
-        <v>1.8122980228956009e-05</v>
+        <v>1.8103586501677939e-05</v>
       </c>
       <c r="E48" s="0">
-        <v>1.2360467702452213e-06</v>
+        <v>1.23604676137642e-06</v>
       </c>
       <c r="F48" s="0">
-        <v>1.2284310151977034e-05</v>
+        <v>1.2301258698754286e-05</v>
       </c>
       <c r="G48" s="0">
-        <v>1.2099272208446126e-07</v>
+        <v>1.1800845504123936e-07</v>
       </c>
       <c r="H48" s="0">
-        <v>-6.3207852733032194e-22</v>
+        <v>-9.4162284013091034e-21</v>
       </c>
       <c r="I48" s="0">
-        <v>4.4817405948909019e-06</v>
+        <v>4.4483798832131038e-06</v>
       </c>
       <c r="J48" s="0">
-        <v>-1.1001024160926825e-10</v>
+        <v>-1.0729670710183775e-10</v>
       </c>
       <c r="K48" s="0">
         <v>1</v>
@@ -4865,39 +4865,39 @@
         <v>0</v>
       </c>
       <c r="O48" s="0">
-        <v>0.02946827626869614</v>
+        <v>0.029468276269873309</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>681</v>
+        <v>787</v>
       </c>
       <c r="B49" s="0">
-        <v>0.90455694835793987</v>
+        <v>0.90455694697840028</v>
       </c>
       <c r="C49" s="0">
         <v>0.0029544837362637352</v>
       </c>
       <c r="D49" s="0">
-        <v>2.9893893470323747e-05</v>
+        <v>2.9816930681365569e-05</v>
       </c>
       <c r="E49" s="0">
         <v>0</v>
       </c>
       <c r="F49" s="0">
-        <v>1.4804337912157112e-05</v>
+        <v>1.4841480446474067e-05</v>
       </c>
       <c r="G49" s="0">
-        <v>6.2267694426683292e-08</v>
+        <v>6.0767172141295054e-08</v>
       </c>
       <c r="H49" s="0">
-        <v>2.2093547003720456e-19</v>
+        <v>2.2970975486823304e-19</v>
       </c>
       <c r="I49" s="0">
-        <v>1.5027344503271388e-05</v>
+        <v>1.4914738336977996e-05</v>
       </c>
       <c r="J49" s="0">
-        <v>-5.6639531655633944e-11</v>
+        <v>-5.5274228019969889e-11</v>
       </c>
       <c r="K49" s="0">
         <v>0</v>
@@ -4912,39 +4912,39 @@
         <v>0</v>
       </c>
       <c r="O49" s="0">
-        <v>8.2005880420495377e-05</v>
+        <v>8.2005880545136167e-05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>682</v>
+        <v>788</v>
       </c>
       <c r="B50" s="0">
-        <v>0.71137118377682762</v>
+        <v>0.71137118352994644</v>
       </c>
       <c r="C50" s="0">
         <v>0.0036961735164835192</v>
       </c>
       <c r="D50" s="0">
-        <v>3.8154186178899955e-05</v>
+        <v>3.8163522536919028e-05</v>
       </c>
       <c r="E50" s="0">
         <v>0</v>
       </c>
       <c r="F50" s="0">
-        <v>4.218578345501157e-05</v>
+        <v>4.2163529326708268e-05</v>
       </c>
       <c r="G50" s="0">
-        <v>1.7824218131318057e-07</v>
+        <v>1.7366916505575905e-07</v>
       </c>
       <c r="H50" s="0">
-        <v>-2.2948225379829338e-19</v>
+        <v>-7.0842493604193697e-19</v>
       </c>
       <c r="I50" s="0">
-        <v>-4.2096774204054606e-06</v>
+        <v>-4.1735180751585531e-06</v>
       </c>
       <c r="J50" s="0">
-        <v>-1.6203701910551661e-10</v>
+        <v>-1.5787968573733848e-10</v>
       </c>
       <c r="K50" s="0">
         <v>0</v>
@@ -4959,39 +4959,39 @@
         <v>0</v>
       </c>
       <c r="O50" s="0">
-        <v>0.00040432953049755418</v>
+        <v>0.00040432953063577456</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>683</v>
+        <v>789</v>
       </c>
       <c r="B51" s="0">
-        <v>0.84693045303058656</v>
+        <v>0.84693045321762972</v>
       </c>
       <c r="C51" s="0">
         <v>0.00097700439560439588</v>
       </c>
       <c r="D51" s="0">
-        <v>0.00011064639064934876</v>
+        <v>0.0001104789711332796</v>
       </c>
       <c r="E51" s="0">
         <v>0</v>
       </c>
       <c r="F51" s="0">
-        <v>8.358930016672637e-05</v>
+        <v>8.3648953687046377e-05</v>
       </c>
       <c r="G51" s="0">
-        <v>4.4587088654914151e-07</v>
+        <v>4.3465394961501492e-07</v>
       </c>
       <c r="H51" s="0">
-        <v>2.4885892817129055e-20</v>
+        <v>1.2752954198925811e-21</v>
       </c>
       <c r="I51" s="0">
-        <v>2.6611625190139574e-05</v>
+        <v>2.6395758883849513e-05</v>
       </c>
       <c r="J51" s="0">
-        <v>-4.0559406634533136e-10</v>
+        <v>-3.953872313106413e-10</v>
       </c>
       <c r="K51" s="0">
         <v>0</v>
@@ -5006,39 +5006,39 @@
         <v>0</v>
       </c>
       <c r="O51" s="0">
-        <v>0.00048602528453063718</v>
+        <v>0.00048602528442077243</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>684</v>
+        <v>790</v>
       </c>
       <c r="B52" s="0">
-        <v>0.49467206477960474</v>
+        <v>0.4946720646314165</v>
       </c>
       <c r="C52" s="0">
         <v>0.0095371454945054959</v>
       </c>
       <c r="D52" s="0">
-        <v>0.00017292360374529577</v>
+        <v>0.00017307155427490569</v>
       </c>
       <c r="E52" s="0">
-        <v>0.00036468477100178899</v>
+        <v>0.00036468477097110114</v>
       </c>
       <c r="F52" s="0">
-        <v>-0.00015696698683727005</v>
+        <v>-0.00015710147857884229</v>
       </c>
       <c r="G52" s="0">
-        <v>1.1073280295144267e-06</v>
+        <v>1.0833213307160187e-06</v>
       </c>
       <c r="H52" s="0">
-        <v>5.104003540935617e-20</v>
+        <v>-9.9078036044423633e-20</v>
       </c>
       <c r="I52" s="0">
-        <v>-3.5900501166817578e-05</v>
+        <v>-3.5594074010313095e-05</v>
       </c>
       <c r="J52" s="0">
-        <v>-1.0072819200778035e-09</v>
+        <v>-9.854377559863044e-10</v>
       </c>
       <c r="K52" s="0">
         <v>0</v>
@@ -5053,39 +5053,39 @@
         <v>0</v>
       </c>
       <c r="O52" s="0">
-        <v>0.00057760531180212906</v>
+        <v>0.00057760531197215831</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>685</v>
+        <v>791</v>
       </c>
       <c r="B53" s="0">
-        <v>0.72938748485475291</v>
+        <v>0.72938748481945315</v>
       </c>
       <c r="C53" s="0">
         <v>0.042665651648351621</v>
       </c>
       <c r="D53" s="0">
-        <v>3.593664866188388e-06</v>
+        <v>3.591606995269382e-06</v>
       </c>
       <c r="E53" s="0">
-        <v>4.730273530725303e-06</v>
+        <v>4.7302735307826861e-06</v>
       </c>
       <c r="F53" s="0">
-        <v>-1.716672452166895e-06</v>
+        <v>-1.7144305858522705e-06</v>
       </c>
       <c r="G53" s="0">
-        <v>2.4718427698112601e-08</v>
+        <v>2.4174964546853264e-08</v>
       </c>
       <c r="H53" s="0">
-        <v>1.8603003868480281e-20</v>
+        <v>1.1559405331303827e-20</v>
       </c>
       <c r="I53" s="0">
-        <v>5.5536785536808736e-07</v>
+        <v>5.5161108609778955e-07</v>
       </c>
       <c r="J53" s="0">
-        <v>-2.2495436238664408e-11</v>
+        <v>-2.2000305688021682e-11</v>
       </c>
       <c r="K53" s="0">
         <v>1</v>
@@ -5100,39 +5100,39 @@
         <v>0</v>
       </c>
       <c r="O53" s="0">
-        <v>0.0019935594219699739</v>
+        <v>0.0019935594220560904</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>686</v>
+        <v>792</v>
       </c>
       <c r="B54" s="0">
-        <v>0.67528287593361136</v>
+        <v>0.67528287597857872</v>
       </c>
       <c r="C54" s="0">
         <v>0.011126930109890108</v>
       </c>
       <c r="D54" s="0">
-        <v>6.5845958781702188e-05</v>
+        <v>6.5900654128878263e-05</v>
       </c>
       <c r="E54" s="0">
-        <v>0.0001287915728259045</v>
+        <v>0.00012879157283448081</v>
       </c>
       <c r="F54" s="0">
-        <v>-5.1152093150734312e-05</v>
+        <v>-5.1193734443211857e-05</v>
       </c>
       <c r="G54" s="0">
-        <v>4.5733015347055847e-07</v>
+        <v>4.4739590849567164e-07</v>
       </c>
       <c r="H54" s="0">
-        <v>8.4198190369412772e-20</v>
+        <v>4.3897837404782305e-20</v>
       </c>
       <c r="I54" s="0">
-        <v>-1.2250434940119976e-05</v>
+        <v>-1.2144173106361899e-05</v>
       </c>
       <c r="J54" s="0">
-        <v>-4.1610681866899942e-10</v>
+        <v>-4.0706452450845561e-10</v>
       </c>
       <c r="K54" s="0">
         <v>0</v>
@@ -5147,39 +5147,39 @@
         <v>0</v>
       </c>
       <c r="O54" s="0">
-        <v>0.00039214223466139237</v>
+        <v>0.00039214223463324057</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>687</v>
+        <v>793</v>
       </c>
       <c r="B55" s="0">
-        <v>0.82399881399324948</v>
+        <v>0.82399881515213313</v>
       </c>
       <c r="C55" s="0">
         <v>0.0021432036263736242</v>
       </c>
       <c r="D55" s="0">
-        <v>0.0001236892459103695</v>
+        <v>0.00012356747082240655</v>
       </c>
       <c r="E55" s="0">
         <v>0</v>
       </c>
       <c r="F55" s="0">
-        <v>0.00010078319049816373</v>
+        <v>0.00010085421442712853</v>
       </c>
       <c r="G55" s="0">
-        <v>4.8800815112698342e-07</v>
+        <v>4.7571896093090346e-07</v>
       </c>
       <c r="H55" s="0">
-        <v>-2.3904148956297576e-20</v>
+        <v>-1.4061710328125173e-19</v>
       </c>
       <c r="I55" s="0">
-        <v>2.2418491110450814e-05</v>
+        <v>2.2237970104347552e-05</v>
       </c>
       <c r="J55" s="0">
-        <v>-4.4384937199670911e-10</v>
+        <v>-4.3267000028815862e-10</v>
       </c>
       <c r="K55" s="0">
         <v>0</v>
@@ -5194,39 +5194,39 @@
         <v>0</v>
       </c>
       <c r="O55" s="0">
-        <v>0.0010977995799803574</v>
+        <v>0.001097799578430689</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>688</v>
+        <v>794</v>
       </c>
       <c r="B56" s="0">
-        <v>0.86070956564543077</v>
+        <v>0.86070956641605478</v>
       </c>
       <c r="C56" s="0">
         <v>0.0025875605494505485</v>
       </c>
       <c r="D56" s="0">
-        <v>0.00010289269156103691</v>
+        <v>0.00010277622830773896</v>
       </c>
       <c r="E56" s="0">
         <v>0</v>
       </c>
       <c r="F56" s="0">
-        <v>8.2280293088134117e-05</v>
+        <v>8.2337585620734653e-05</v>
       </c>
       <c r="G56" s="0">
-        <v>4.7182888416302752e-07</v>
+        <v>4.5992070040923169e-07</v>
       </c>
       <c r="H56" s="0">
-        <v>1.2013527945100521e-19</v>
+        <v>9.7985575214264691e-20</v>
       </c>
       <c r="I56" s="0">
-        <v>2.014099879808041e-05</v>
+        <v>1.9979140360025309e-05</v>
       </c>
       <c r="J56" s="0">
-        <v>-4.2920934075754355e-10</v>
+        <v>-4.1837343033135723e-10</v>
       </c>
       <c r="K56" s="0">
         <v>0</v>
@@ -5241,39 +5241,39 @@
         <v>0</v>
       </c>
       <c r="O56" s="0">
-        <v>0.00013968742466329505</v>
+        <v>0.00013968742453750169</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>689</v>
+        <v>795</v>
       </c>
       <c r="B57" s="0">
-        <v>0.69541698665151885</v>
+        <v>0.69541698652824135</v>
       </c>
       <c r="C57" s="0">
         <v>0.000901488571428571</v>
       </c>
       <c r="D57" s="0">
-        <v>4.540132322794372e-05</v>
+        <v>4.5342988475199534e-05</v>
       </c>
       <c r="E57" s="0">
         <v>0</v>
       </c>
       <c r="F57" s="0">
-        <v>3.7482905971332573e-05</v>
+        <v>3.7494482395662462e-05</v>
       </c>
       <c r="G57" s="0">
-        <v>1.3749360642931995e-07</v>
+        <v>1.3402905741715609e-07</v>
       </c>
       <c r="H57" s="0">
-        <v>3.6414165506556674e-22</v>
+        <v>-1.6495583395907131e-20</v>
       </c>
       <c r="I57" s="0">
-        <v>7.7810486419644701e-06</v>
+        <v>7.71459886460294e-06</v>
       </c>
       <c r="J57" s="0">
-        <v>-1.2499178264227344e-10</v>
+        <v>-1.2184248300745081e-10</v>
       </c>
       <c r="K57" s="0">
         <v>0</v>
@@ -5288,39 +5288,39 @@
         <v>0</v>
       </c>
       <c r="O57" s="0">
-        <v>0.010095025458343371</v>
+        <v>0.010095025460080445</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>690</v>
+        <v>796</v>
       </c>
       <c r="B58" s="0">
-        <v>0.7353386346117512</v>
+        <v>0.73533863539090405</v>
       </c>
       <c r="C58" s="0">
         <v>0.0019742773626373628</v>
       </c>
       <c r="D58" s="0">
-        <v>-1.6235823328625748e-06</v>
+        <v>-1.6352172388742747e-06</v>
       </c>
       <c r="E58" s="0">
         <v>0</v>
       </c>
       <c r="F58" s="0">
-        <v>-4.6728861872053849e-07</v>
+        <v>-4.8456374984315702e-07</v>
       </c>
       <c r="G58" s="0">
-        <v>1.5999330763951665e-07</v>
+        <v>1.5606695102105239e-07</v>
       </c>
       <c r="H58" s="0">
-        <v>-2.8290814424927179e-19</v>
+        <v>-8.6672293974315117e-19</v>
       </c>
       <c r="I58" s="0">
-        <v>-1.3161416449454627e-06</v>
+        <v>-1.3065786300565508e-06</v>
       </c>
       <c r="J58" s="0">
-        <v>-1.4537683580729212e-10</v>
+        <v>-1.4180999475247326e-10</v>
       </c>
       <c r="K58" s="0">
         <v>0</v>
@@ -5335,39 +5335,39 @@
         <v>1</v>
       </c>
       <c r="O58" s="0">
-        <v>0.00021816876483759178</v>
+        <v>0.00021816876460528943</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>691</v>
+        <v>797</v>
       </c>
       <c r="B59" s="0">
-        <v>0.90477592581094413</v>
+        <v>0.90477592597111112</v>
       </c>
       <c r="C59" s="0">
         <v>0.00093552098901098846</v>
       </c>
       <c r="D59" s="0">
-        <v>1.4660677211567457e-05</v>
+        <v>1.4665443687056445e-05</v>
       </c>
       <c r="E59" s="0">
         <v>0</v>
       </c>
       <c r="F59" s="0">
-        <v>1.6820619915617505e-05</v>
+        <v>1.6810403532495549e-05</v>
       </c>
       <c r="G59" s="0">
-        <v>1.4036779187861792e-07</v>
+        <v>1.3684175790924137e-07</v>
       </c>
       <c r="H59" s="0">
-        <v>1.3907578722849114e-19</v>
+        <v>1.2933621913756872e-19</v>
       </c>
       <c r="I59" s="0">
-        <v>-2.300182873892154e-06</v>
+        <v>-2.281677187538256e-06</v>
       </c>
       <c r="J59" s="0">
-        <v>-1.2762203665094837e-10</v>
+        <v>-1.2441581021872973e-10</v>
       </c>
       <c r="K59" s="0">
         <v>0</v>
@@ -5382,39 +5382,39 @@
         <v>0</v>
       </c>
       <c r="O59" s="0">
-        <v>0.00014052339499340369</v>
+        <v>0.00014052339496779703</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>692</v>
+        <v>798</v>
       </c>
       <c r="B60" s="0">
-        <v>0.5924146013925119</v>
+        <v>0.5924146020926212</v>
       </c>
       <c r="C60" s="0">
         <v>0.0079997632967032974</v>
       </c>
       <c r="D60" s="0">
-        <v>5.7707349704594765e-05</v>
+        <v>5.7732418851165891e-05</v>
       </c>
       <c r="E60" s="0">
-        <v>7.6145747081994762e-05</v>
+        <v>7.6145747225165732e-05</v>
       </c>
       <c r="F60" s="0">
-        <v>-1.5257910597290584e-05</v>
+        <v>-1.5260542182212581e-05</v>
       </c>
       <c r="G60" s="0">
-        <v>4.0886630144667188e-07</v>
+        <v>3.9988884030991998e-07</v>
       </c>
       <c r="H60" s="0">
-        <v>2.3840442943081332e-20</v>
+        <v>-1.0360925618675387e-19</v>
       </c>
       <c r="I60" s="0">
-        <v>-3.5889809879275867e-06</v>
+        <v>-3.5523111128728301e-06</v>
       </c>
       <c r="J60" s="0">
-        <v>-3.7209362852122889e-10</v>
+        <v>-3.6391922424573896e-10</v>
       </c>
       <c r="K60" s="0">
         <v>1</v>
@@ -5429,39 +5429,39 @@
         <v>0</v>
       </c>
       <c r="O60" s="0">
-        <v>0.00011269003381088796</v>
+        <v>0.00011269003367712617</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>693</v>
+        <v>799</v>
       </c>
       <c r="B61" s="0">
-        <v>0.6326412571748784</v>
+        <v>0.63264125648709901</v>
       </c>
       <c r="C61" s="0">
         <v>0.0010330782417582412</v>
       </c>
       <c r="D61" s="0">
-        <v>0.00017244670027794217</v>
+        <v>0.00017235092230747298</v>
       </c>
       <c r="E61" s="0">
         <v>0</v>
       </c>
       <c r="F61" s="0">
-        <v>0.0001624553328292611</v>
+        <v>0.00016245978518293516</v>
       </c>
       <c r="G61" s="0">
-        <v>6.2494592117370504e-07</v>
+        <v>6.086805584579475e-07</v>
       </c>
       <c r="H61" s="0">
-        <v>2.5011994434767831e-19</v>
+        <v>2.4037646756124422e-19</v>
       </c>
       <c r="I61" s="0">
-        <v>9.3669898653752663e-06</v>
+        <v>9.2830101094750881e-06</v>
       </c>
       <c r="J61" s="0">
-        <v>-5.6833786815483917e-10</v>
+        <v>-5.5354339546038935e-10</v>
       </c>
       <c r="K61" s="0">
         <v>0</v>
@@ -5476,39 +5476,39 @@
         <v>0</v>
       </c>
       <c r="O61" s="0">
-        <v>0.00011756905896135267</v>
+        <v>0.00011756905908855727</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>694</v>
+        <v>800</v>
       </c>
       <c r="B62" s="0">
-        <v>0.86580262765809413</v>
+        <v>0.86580262795585761</v>
       </c>
       <c r="C62" s="0">
         <v>0.00086934967032967052</v>
       </c>
       <c r="D62" s="0">
-        <v>6.0228815324464301e-05</v>
+        <v>6.0178200983880159e-05</v>
       </c>
       <c r="E62" s="0">
         <v>0</v>
       </c>
       <c r="F62" s="0">
-        <v>5.2464460033158185e-05</v>
+        <v>5.2483036607991797e-05</v>
       </c>
       <c r="G62" s="0">
-        <v>2.0239233569776234e-07</v>
+        <v>1.9718552251099832e-07</v>
       </c>
       <c r="H62" s="0">
-        <v>2.0340030596567027e-19</v>
+        <v>2.0746045906991859e-19</v>
       </c>
       <c r="I62" s="0">
-        <v>7.5621470311268186e-06</v>
+        <v>7.4981581923686504e-06</v>
       </c>
       <c r="J62" s="0">
-        <v>-1.8407551866829458e-10</v>
+        <v>-1.7933899149423082e-10</v>
       </c>
       <c r="K62" s="0">
         <v>0</v>
@@ -5523,39 +5523,39 @@
         <v>0</v>
       </c>
       <c r="O62" s="0">
-        <v>8.3920602650843802e-05</v>
+        <v>8.3920602621545841e-05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>695</v>
+        <v>801</v>
       </c>
       <c r="B63" s="0">
-        <v>0.8595158467241002</v>
+        <v>0.85951584381059909</v>
       </c>
       <c r="C63" s="0">
         <v>0.00042814329670329667</v>
       </c>
       <c r="D63" s="0">
-        <v>7.6322258710365012e-05</v>
+        <v>7.6276994892622387e-05</v>
       </c>
       <c r="E63" s="0">
         <v>0</v>
       </c>
       <c r="F63" s="0">
-        <v>6.8545756756197842e-05</v>
+        <v>6.8570639739343859e-05</v>
       </c>
       <c r="G63" s="0">
-        <v>4.0979079672305358e-07</v>
+        <v>3.9937911046131645e-07</v>
       </c>
       <c r="H63" s="0">
-        <v>5.4315490640145064e-19</v>
+        <v>5.6380216119113187e-19</v>
       </c>
       <c r="I63" s="0">
-        <v>7.3670838989086283e-06</v>
+        <v>7.3073393115935603e-06</v>
       </c>
       <c r="J63" s="0">
-        <v>-3.727414650542675e-10</v>
+        <v>-3.6326877691321142e-10</v>
       </c>
       <c r="K63" s="0">
         <v>0</v>
@@ -5570,39 +5570,39 @@
         <v>0</v>
       </c>
       <c r="O63" s="0">
-        <v>6.837789804211467e-05</v>
+        <v>6.8377896674541678e-05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>696</v>
+        <v>802</v>
       </c>
       <c r="B64" s="0">
-        <v>0.81176465893378724</v>
+        <v>0.81176465883274429</v>
       </c>
       <c r="C64" s="0">
         <v>0.00080047703296703314</v>
       </c>
       <c r="D64" s="0">
-        <v>4.6064134655237405e-05</v>
+        <v>4.606009853808423e-05</v>
       </c>
       <c r="E64" s="0">
         <v>0</v>
       </c>
       <c r="F64" s="0">
-        <v>4.6932027128015929e-05</v>
+        <v>4.6924009626817206e-05</v>
       </c>
       <c r="G64" s="0">
-        <v>1.6765500071522589e-07</v>
+        <v>1.6325963357649389e-07</v>
       </c>
       <c r="H64" s="0">
-        <v>1.4378661696601724e-19</v>
+        <v>1.4678434362212352e-19</v>
       </c>
       <c r="I64" s="0">
-        <v>-1.0353950070645209e-06</v>
+        <v>-1.0270222540429155e-06</v>
       </c>
       <c r="J64" s="0">
-        <v>-1.5246642937323988e-10</v>
+        <v>-1.48468266701518e-10</v>
       </c>
       <c r="K64" s="0">
         <v>0</v>
@@ -5617,39 +5617,39 @@
         <v>0</v>
       </c>
       <c r="O64" s="0">
-        <v>0.0001358101323412518</v>
+        <v>0.00013581013235745037</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>697</v>
+        <v>803</v>
       </c>
       <c r="B65" s="0">
-        <v>0.51366240636625837</v>
+        <v>0.513662406380895</v>
       </c>
       <c r="C65" s="0">
         <v>0.031474542747252747</v>
       </c>
       <c r="D65" s="0">
-        <v>7.2711963170313257e-05</v>
+        <v>7.2785159675776197e-05</v>
       </c>
       <c r="E65" s="0">
-        <v>0.00014371162889811439</v>
+        <v>0.00014371162870346985</v>
       </c>
       <c r="F65" s="0">
-        <v>-5.6304001845315155e-05</v>
+        <v>-5.6351117409397725e-05</v>
       </c>
       <c r="G65" s="0">
-        <v>6.8388693176427238e-07</v>
+        <v>6.68896796008652e-07</v>
       </c>
       <c r="H65" s="0">
-        <v>-2.9404818234127911e-20</v>
+        <v>-1.8920536124489803e-19</v>
       </c>
       <c r="I65" s="0">
-        <v>-1.5378928505474348e-05</v>
+        <v>-1.5243639752168013e-05</v>
       </c>
       <c r="J65" s="0">
-        <v>-6.2230877587420843e-10</v>
+        <v>-6.0866213637984226e-10</v>
       </c>
       <c r="K65" s="0">
         <v>1</v>
@@ -5664,39 +5664,39 @@
         <v>0</v>
       </c>
       <c r="O65" s="0">
-        <v>0.014517901053880984</v>
+        <v>0.014517901053391818</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>698</v>
+        <v>804</v>
       </c>
       <c r="B66" s="0">
-        <v>0.73207782933897247</v>
+        <v>0.73207782910962793</v>
       </c>
       <c r="C66" s="0">
         <v>0.02713582912087913</v>
       </c>
       <c r="D66" s="0">
-        <v>2.0941904352249315e-05</v>
+        <v>2.0972482215811656e-05</v>
       </c>
       <c r="E66" s="0">
-        <v>4.6988642928115428e-05</v>
+        <v>4.698864291522957e-05</v>
       </c>
       <c r="F66" s="0">
-        <v>-1.9618010276857538e-05</v>
+        <v>-1.9638546982500405e-05</v>
       </c>
       <c r="G66" s="0">
-        <v>2.8982478907027376e-07</v>
+        <v>2.833770361693189e-07</v>
       </c>
       <c r="H66" s="0">
-        <v>-1.861902017423763e-20</v>
+        <v>-5.4952912500824176e-20</v>
       </c>
       <c r="I66" s="0">
-        <v>-6.7182893378686148e-06</v>
+        <v>-6.6607328733276854e-06</v>
       </c>
       <c r="J66" s="0">
-        <v>-2.6375021021475878e-10</v>
+        <v>-2.5787975908806988e-10</v>
       </c>
       <c r="K66" s="0">
         <v>1</v>
@@ -5711,39 +5711,39 @@
         <v>0</v>
       </c>
       <c r="O66" s="0">
-        <v>0.0043554452115005656</v>
+        <v>0.0043554452128423899</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>699</v>
+        <v>805</v>
       </c>
       <c r="B67" s="0">
-        <v>0.89534124640643975</v>
+        <v>0.89534124680275695</v>
       </c>
       <c r="C67" s="0">
         <v>0.0013432845054945051</v>
       </c>
       <c r="D67" s="0">
-        <v>2.1239638560337075e-05</v>
+        <v>2.123044879002903e-05</v>
       </c>
       <c r="E67" s="0">
         <v>0</v>
       </c>
       <c r="F67" s="0">
-        <v>1.775909198352736e-05</v>
+        <v>1.7777825584862372e-05</v>
       </c>
       <c r="G67" s="0">
-        <v>8.9895104451172661e-08</v>
+        <v>8.7652865455745387e-08</v>
       </c>
       <c r="H67" s="0">
-        <v>1.0920674269039645e-19</v>
+        <v>1.0278784234637735e-19</v>
       </c>
       <c r="I67" s="0">
-        <v>3.3907332290406154e-06</v>
+        <v>3.3650500568040874e-06</v>
       </c>
       <c r="J67" s="0">
-        <v>-8.1756682181808839e-11</v>
+        <v>-7.9717093277614537e-11</v>
       </c>
       <c r="K67" s="0">
         <v>0</v>
@@ -5758,39 +5758,39 @@
         <v>0</v>
       </c>
       <c r="O67" s="0">
-        <v>0.00025149688795199192</v>
+        <v>0.00025149688783936087</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>700</v>
+        <v>806</v>
       </c>
       <c r="B68" s="0">
-        <v>0.85790778853671634</v>
+        <v>0.85790778857774874</v>
       </c>
       <c r="C68" s="0">
         <v>0.0087388856043956065</v>
       </c>
       <c r="D68" s="0">
-        <v>3.2444877511546306e-05</v>
+        <v>3.2464842472741715e-05</v>
       </c>
       <c r="E68" s="0">
-        <v>4.7671099826719466e-05</v>
+        <v>4.7671099836999478e-05</v>
       </c>
       <c r="F68" s="0">
-        <v>-1.2248077195659606e-05</v>
+        <v>-1.225378055814644e-05</v>
       </c>
       <c r="G68" s="0">
-        <v>2.907692107778115e-07</v>
+        <v>2.8433587953613358e-07</v>
       </c>
       <c r="H68" s="0">
-        <v>1.6648266991428774e-20</v>
+        <v>4.9359753568226793e-21</v>
       </c>
       <c r="I68" s="0">
-        <v>-3.2686496776805241e-06</v>
+        <v>-3.236553891993907e-06</v>
       </c>
       <c r="J68" s="0">
-        <v>-2.6465261085847384e-10</v>
+        <v>-2.5879365355552711e-10</v>
       </c>
       <c r="K68" s="0">
         <v>1</v>
@@ -5805,39 +5805,39 @@
         <v>0</v>
       </c>
       <c r="O68" s="0">
-        <v>0.0029252432597083543</v>
+        <v>0.0029252432595532358</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>701</v>
+        <v>807</v>
       </c>
       <c r="B69" s="0">
-        <v>0.95464010071692817</v>
+        <v>0.95464010084555717</v>
       </c>
       <c r="C69" s="0">
         <v>0.0028873060439560442</v>
       </c>
       <c r="D69" s="0">
-        <v>3.2380308021031267e-05</v>
+        <v>3.2326794394048198e-05</v>
       </c>
       <c r="E69" s="0">
         <v>0</v>
       </c>
       <c r="F69" s="0">
-        <v>2.2428010291431433e-05</v>
+        <v>2.2454047211274565e-05</v>
       </c>
       <c r="G69" s="0">
-        <v>1.2216843595488973e-07</v>
+        <v>1.1917675870260198e-07</v>
       </c>
       <c r="H69" s="0">
-        <v>1.8353197256296392e-21</v>
+        <v>-2.3897487036222976e-20</v>
       </c>
       <c r="I69" s="0">
-        <v>9.8302404295887315e-06</v>
+        <v>9.7536788374264359e-06</v>
       </c>
       <c r="J69" s="0">
-        <v>-1.1113594378915701e-10</v>
+        <v>-1.0841335538043463e-10</v>
       </c>
       <c r="K69" s="0">
         <v>0</v>
@@ -5852,39 +5852,39 @@
         <v>0</v>
       </c>
       <c r="O69" s="0">
-        <v>0.0030477757506563001</v>
+        <v>0.0030477757502297949</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>702</v>
+        <v>808</v>
       </c>
       <c r="B70" s="0">
-        <v>0.89451288314659461</v>
+        <v>0.89451288332467105</v>
       </c>
       <c r="C70" s="0">
         <v>0.0016293460439560444</v>
       </c>
       <c r="D70" s="0">
-        <v>3.1359312077179863e-05</v>
+        <v>3.1329933785871595e-05</v>
       </c>
       <c r="E70" s="0">
         <v>0</v>
       </c>
       <c r="F70" s="0">
-        <v>2.5879476882123994e-05</v>
+        <v>2.5896566942573164e-05</v>
       </c>
       <c r="G70" s="0">
-        <v>1.3529121859975024e-07</v>
+        <v>1.3190274458610584e-07</v>
       </c>
       <c r="H70" s="0">
-        <v>1.5675723345126579e-20</v>
+        <v>1.1112639493369968e-20</v>
       </c>
       <c r="I70" s="0">
-        <v>5.3446670212774833e-06</v>
+        <v>5.3015840613787227e-06</v>
       </c>
       <c r="J70" s="0">
-        <v>-1.2304482138093294e-10</v>
+        <v>-1.1996266640782816e-10</v>
       </c>
       <c r="K70" s="0">
         <v>0</v>
@@ -5899,39 +5899,39 @@
         <v>0</v>
       </c>
       <c r="O70" s="0">
-        <v>0.002118748904830681</v>
+        <v>0.0021187489043978723</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>703</v>
+        <v>809</v>
       </c>
       <c r="B71" s="0">
-        <v>0.77033451438176059</v>
+        <v>0.77033451440743295</v>
       </c>
       <c r="C71" s="0">
         <v>0.0077156657142857131</v>
       </c>
       <c r="D71" s="0">
-        <v>2.5315286614753297e-05</v>
+        <v>2.534386175973023e-05</v>
       </c>
       <c r="E71" s="0">
-        <v>6.4379166487608965e-05</v>
+        <v>6.4379166417257797e-05</v>
       </c>
       <c r="F71" s="0">
-        <v>-3.2087941846456952e-05</v>
+        <v>-3.2116204768825311e-05</v>
       </c>
       <c r="G71" s="0">
-        <v>2.8569589171306436e-07</v>
+        <v>2.7945435047788538e-07</v>
       </c>
       <c r="H71" s="0">
-        <v>-4.0517330654186344e-20</v>
+        <v>-1.0315328528360057e-19</v>
       </c>
       <c r="I71" s="0">
-        <v>-7.2613739454067955e-06</v>
+        <v>-7.1982999489543491e-06</v>
       </c>
       <c r="J71" s="0">
-        <v>-2.5997270494474003e-10</v>
+        <v>-2.5429022568834541e-10</v>
       </c>
       <c r="K71" s="0">
         <v>0</v>
@@ -5946,39 +5946,39 @@
         <v>0</v>
       </c>
       <c r="O71" s="0">
-        <v>0.0077983599051876873</v>
+        <v>0.0077983599048872497</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>704</v>
+        <v>810</v>
       </c>
       <c r="B72" s="0">
-        <v>0.73572122186635847</v>
+        <v>0.73572122196632761</v>
       </c>
       <c r="C72" s="0">
         <v>0.0086889267032967087</v>
       </c>
       <c r="D72" s="0">
-        <v>1.7075888334005394e-05</v>
+        <v>1.7085322407591096e-05</v>
       </c>
       <c r="E72" s="0">
-        <v>3.0217815680652784e-05</v>
+        <v>3.0217815711520617e-05</v>
       </c>
       <c r="F72" s="0">
-        <v>-1.1336577750940506e-05</v>
+        <v>-1.1342561291649639e-05</v>
       </c>
       <c r="G72" s="0">
-        <v>1.4951842467846133e-07</v>
+        <v>1.4625114391598891e-07</v>
       </c>
       <c r="H72" s="0">
-        <v>-1.6622258524439077e-20</v>
+        <v>-7.3139980213810917e-20</v>
       </c>
       <c r="I72" s="0">
-        <v>-1.9547319498212076e-06</v>
+        <v>-1.9360500603937459e-06</v>
       </c>
       <c r="J72" s="0">
-        <v>-1.3607056412180991e-10</v>
+        <v>-1.3309580205051393e-10</v>
       </c>
       <c r="K72" s="0">
         <v>1</v>
@@ -5993,39 +5993,39 @@
         <v>0</v>
       </c>
       <c r="O72" s="0">
-        <v>0.0029645956569198367</v>
+        <v>0.0029645956565015966</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>705</v>
+        <v>811</v>
       </c>
       <c r="B73" s="0">
-        <v>0.92181455249908772</v>
+        <v>0.92181455249366417</v>
       </c>
       <c r="C73" s="0">
         <v>0.0018244775824175833</v>
       </c>
       <c r="D73" s="0">
-        <v>2.9402754414879048e-05</v>
+        <v>2.9354638959313455e-05</v>
       </c>
       <c r="E73" s="0">
         <v>0</v>
       </c>
       <c r="F73" s="0">
-        <v>1.8905622336368605e-05</v>
+        <v>1.8938322577613398e-05</v>
       </c>
       <c r="G73" s="0">
-        <v>9.4366621270501297e-08</v>
+        <v>9.2074754108455134e-08</v>
       </c>
       <c r="H73" s="0">
-        <v>5.8891370631220361e-20</v>
+        <v>5.8813892673290507e-20</v>
       </c>
       <c r="I73" s="0">
-        <v>1.0402851300724454e-05</v>
+        <v>1.0324325385298498e-05</v>
       </c>
       <c r="J73" s="0">
-        <v>-8.5843484572942262e-11</v>
+        <v>-8.375770695535792e-11</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
@@ -6040,39 +6040,39 @@
         <v>0</v>
       </c>
       <c r="O73" s="0">
-        <v>0.00044382107578206829</v>
+        <v>0.00044382107578237208</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>706</v>
+        <v>812</v>
       </c>
       <c r="B74" s="0">
-        <v>0.73423441253282196</v>
+        <v>0.73423441261182676</v>
       </c>
       <c r="C74" s="0">
         <v>0.0044086571428571452</v>
       </c>
       <c r="D74" s="0">
-        <v>3.9034334561682861e-05</v>
+        <v>3.9070991534636647e-05</v>
       </c>
       <c r="E74" s="0">
-        <v>9.7740847544907652e-05</v>
+        <v>9.7740846482694373e-05</v>
       </c>
       <c r="F74" s="0">
-        <v>-4.8162914647352944e-05</v>
+        <v>-4.8210977499139182e-05</v>
       </c>
       <c r="G74" s="0">
-        <v>3.8816943535427458e-07</v>
+        <v>3.7969460939046432e-07</v>
       </c>
       <c r="H74" s="0">
-        <v>-2.9782113426296933e-19</v>
+        <v>-7.6324303051634958e-19</v>
       </c>
       <c r="I74" s="0">
-        <v>-1.0931414576785144e-05</v>
+        <v>-1.08382265785228e-05</v>
       </c>
       <c r="J74" s="0">
-        <v>-3.5319444067933865e-10</v>
+        <v>-3.4547978544363113e-10</v>
       </c>
       <c r="K74" s="0">
         <v>0</v>
@@ -6087,39 +6087,39 @@
         <v>0</v>
       </c>
       <c r="O74" s="0">
-        <v>0.0026580027974908646</v>
+        <v>0.0026580027971910398</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>707</v>
+        <v>813</v>
       </c>
       <c r="B75" s="0">
-        <v>0.92231284420417559</v>
+        <v>0.92231284426437354</v>
       </c>
       <c r="C75" s="0">
         <v>0.0026681046153846167</v>
       </c>
       <c r="D75" s="0">
-        <v>7.8303493141271862e-05</v>
+        <v>7.8134174757845735e-05</v>
       </c>
       <c r="E75" s="0">
         <v>0</v>
       </c>
       <c r="F75" s="0">
-        <v>4.9728197175203569e-05</v>
+        <v>4.9786094191415444e-05</v>
       </c>
       <c r="G75" s="0">
-        <v>2.9428855420098109e-07</v>
+        <v>2.8711283107758232e-07</v>
       </c>
       <c r="H75" s="0">
-        <v>-4.072474352499994e-21</v>
+        <v>-6.9869236074821226e-20</v>
       </c>
       <c r="I75" s="0">
-        <v>2.8281275120543445e-05</v>
+        <v>2.8061228914423354e-05</v>
       </c>
       <c r="J75" s="0">
-        <v>-2.677086761296364e-10</v>
+        <v>-2.6117907057533339e-10</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
@@ -6134,39 +6134,39 @@
         <v>0</v>
       </c>
       <c r="O75" s="0">
-        <v>0.023141687450785379</v>
+        <v>0.023141687449154638</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>708</v>
+        <v>814</v>
       </c>
       <c r="B76" s="0">
-        <v>0.84619531662321068</v>
+        <v>0.84619531649712187</v>
       </c>
       <c r="C76" s="0">
         <v>0.00020541626373626369</v>
       </c>
       <c r="D76" s="0">
-        <v>5.4186991819931247e-06</v>
+        <v>5.4351147863781417e-06</v>
       </c>
       <c r="E76" s="0">
         <v>0</v>
       </c>
       <c r="F76" s="0">
-        <v>1.1351876855806938e-05</v>
+        <v>1.1319065333053091e-05</v>
       </c>
       <c r="G76" s="0">
-        <v>1.012200125261958e-07</v>
+        <v>9.8609786366901703e-08</v>
       </c>
       <c r="H76" s="0">
-        <v>7.1774232783551627e-19</v>
+        <v>7.4588950929480806e-19</v>
       </c>
       <c r="I76" s="0">
-        <v>-6.0343056660201916e-06</v>
+        <v>-5.9824706857242659e-06</v>
       </c>
       <c r="J76" s="0">
-        <v>-9.2020320534702408e-11</v>
+        <v>-8.9647318331537878e-11</v>
       </c>
       <c r="K76" s="0">
         <v>0</v>
@@ -6181,39 +6181,39 @@
         <v>0</v>
       </c>
       <c r="O76" s="0">
-        <v>7.4710294353047641e-05</v>
+        <v>7.4710294363791556e-05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>709</v>
+        <v>815</v>
       </c>
       <c r="B77" s="0">
-        <v>0.85670698494413822</v>
+        <v>0.85670698539497991</v>
       </c>
       <c r="C77" s="0">
         <v>0.0016430985714285722</v>
       </c>
       <c r="D77" s="0">
-        <v>8.4453433249261227e-05</v>
+        <v>8.439240314097312e-05</v>
       </c>
       <c r="E77" s="0">
         <v>0</v>
       </c>
       <c r="F77" s="0">
-        <v>7.2491597054554608e-05</v>
+        <v>7.2533322584902467e-05</v>
       </c>
       <c r="G77" s="0">
-        <v>3.7638536042130418e-07</v>
+        <v>3.668611412080593e-07</v>
       </c>
       <c r="H77" s="0">
-        <v>1.0388979172493344e-19</v>
+        <v>7.1556089156111625e-20</v>
       </c>
       <c r="I77" s="0">
-        <v>1.1585793173304362e-05</v>
+        <v>1.1492553089150582e-05</v>
       </c>
       <c r="J77" s="0">
-        <v>-3.4233901914906199e-10</v>
+        <v>-3.3367428805959024e-10</v>
       </c>
       <c r="K77" s="0">
         <v>0</v>
@@ -6228,39 +6228,39 @@
         <v>0</v>
       </c>
       <c r="O77" s="0">
-        <v>0.00020422877042587729</v>
+        <v>0.00020422877031734017</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>710</v>
+        <v>816</v>
       </c>
       <c r="B78" s="0">
-        <v>0.69782870911019923</v>
+        <v>0.69782870947831466</v>
       </c>
       <c r="C78" s="0">
         <v>0.0025547289010989008</v>
       </c>
       <c r="D78" s="0">
-        <v>4.3446684734472882e-05</v>
+        <v>4.347184775745088e-05</v>
       </c>
       <c r="E78" s="0">
         <v>0</v>
       </c>
       <c r="F78" s="0">
-        <v>5.2939952976323636e-05</v>
+        <v>5.2890015301859725e-05</v>
       </c>
       <c r="G78" s="0">
-        <v>2.2644447776818633e-07</v>
+        <v>2.2054093851979953e-07</v>
       </c>
       <c r="H78" s="0">
-        <v>5.8703502600868e-20</v>
+        <v>5.4976975300518159e-20</v>
       </c>
       <c r="I78" s="0">
-        <v>-9.719506822225472e-06</v>
+        <v>-9.6385079540161241e-06</v>
       </c>
       <c r="J78" s="0">
-        <v>-2.0589739352739678e-10</v>
+        <v>-2.0052891257532244e-10</v>
       </c>
       <c r="K78" s="0">
         <v>0</v>
@@ -6275,39 +6275,39 @@
         <v>0</v>
       </c>
       <c r="O78" s="0">
-        <v>0.00022744738077036089</v>
+        <v>0.00022744738064919639</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>711</v>
+        <v>817</v>
       </c>
       <c r="B79" s="0">
-        <v>0.52873362439085847</v>
+        <v>0.52873362436339544</v>
       </c>
       <c r="C79" s="0">
         <v>0.022898872857142857</v>
       </c>
       <c r="D79" s="0">
-        <v>7.2291499268913379e-05</v>
+        <v>7.2356428483276214e-05</v>
       </c>
       <c r="E79" s="0">
-        <v>0.00020412115983555821</v>
+        <v>0.00020412115983708975</v>
       </c>
       <c r="F79" s="0">
-        <v>-0.00011032446100617412</v>
+        <v>-0.0001104323236426051</v>
       </c>
       <c r="G79" s="0">
-        <v>6.8417394370074345e-07</v>
+        <v>6.692947627564316e-07</v>
       </c>
       <c r="H79" s="0">
-        <v>5.479859486861691e-21</v>
+        <v>-4.723533107623551e-20</v>
       </c>
       <c r="I79" s="0">
-        <v>-2.2188751065398204e-05</v>
+        <v>-2.2001093576658e-05</v>
       </c>
       <c r="J79" s="0">
-        <v>-6.2243877323934875e-10</v>
+        <v>-6.0889730682585244e-10</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
@@ -6322,39 +6322,39 @@
         <v>0</v>
       </c>
       <c r="O79" s="0">
-        <v>0.0021168009769909771</v>
+        <v>0.002116800977089921</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>712</v>
+        <v>818</v>
       </c>
       <c r="B80" s="0">
-        <v>0.6011653774154383</v>
+        <v>0.60116537740370646</v>
       </c>
       <c r="C80" s="0">
         <v>0.014392112197802193</v>
       </c>
       <c r="D80" s="0">
-        <v>2.5468303979211845e-05</v>
+        <v>2.5500541307134963e-05</v>
       </c>
       <c r="E80" s="0">
-        <v>5.5270698998745419e-05</v>
+        <v>5.5270698968437008e-05</v>
       </c>
       <c r="F80" s="0">
-        <v>-2.3320048018419333e-05</v>
+        <v>-2.3340653510569851e-05</v>
       </c>
       <c r="G80" s="0">
-        <v>2.671561929959682e-07</v>
+        <v>2.6130232157500264e-07</v>
       </c>
       <c r="H80" s="0">
-        <v>8.4935064500727118e-20</v>
+        <v>-1.3113055633714536e-20</v>
       </c>
       <c r="I80" s="0">
-        <v>-6.7492600738397792e-06</v>
+        <v>-6.6905686820889135e-06</v>
       </c>
       <c r="J80" s="0">
-        <v>-2.4312027051452624e-10</v>
+        <v>-2.3779021827074006e-10</v>
       </c>
       <c r="K80" s="0">
         <v>1</v>
@@ -6369,39 +6369,39 @@
         <v>0</v>
       </c>
       <c r="O80" s="0">
-        <v>0.00085919922570765477</v>
+        <v>0.00085919922571995504</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>713</v>
+        <v>819</v>
       </c>
       <c r="B81" s="0">
-        <v>0.65996554817703512</v>
+        <v>0.65996554819550346</v>
       </c>
       <c r="C81" s="0">
         <v>0.02460239230769231</v>
       </c>
       <c r="D81" s="0">
-        <v>3.0806550997716952e-05</v>
+        <v>3.0816650038565887e-05</v>
       </c>
       <c r="E81" s="0">
-        <v>3.3125075013744299e-05</v>
+        <v>3.312507502910821e-05</v>
       </c>
       <c r="F81" s="0">
-        <v>-1.9221234827705514e-06</v>
+        <v>-1.9168269138600359e-06</v>
       </c>
       <c r="G81" s="0">
-        <v>1.7444133695795302e-07</v>
+        <v>1.7060703254049482e-07</v>
       </c>
       <c r="H81" s="0">
-        <v>-2.0645521028393642e-20</v>
+        <v>-6.7951911259513629e-20</v>
       </c>
       <c r="I81" s="0">
-        <v>-5.7068311708092749e-07</v>
+        <v>-5.6204984737392244e-07</v>
       </c>
       <c r="J81" s="0">
-        <v>-1.5875313380134674e-10</v>
+        <v>-1.552618487915308e-10</v>
       </c>
       <c r="K81" s="0">
         <v>1</v>
@@ -6416,39 +6416,39 @@
         <v>0</v>
       </c>
       <c r="O81" s="0">
-        <v>0.0079071714742021976</v>
+        <v>0.0079071714739398155</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>714</v>
+        <v>820</v>
       </c>
       <c r="B82" s="0">
-        <v>0.6564328276626773</v>
+        <v>0.65643281439591683</v>
       </c>
       <c r="C82" s="0">
         <v>0.0010859034065934066</v>
       </c>
       <c r="D82" s="0">
-        <v>5.1375886237679572e-05</v>
+        <v>5.1390187801259591e-05</v>
       </c>
       <c r="E82" s="0">
         <v>0</v>
       </c>
       <c r="F82" s="0">
-        <v>6.1976141081653024e-05</v>
+        <v>6.1913221125038285e-05</v>
       </c>
       <c r="G82" s="0">
-        <v>8.1055026286878037e-08</v>
+        <v>7.879335035232785e-08</v>
       </c>
       <c r="H82" s="0">
-        <v>1.8375303975243388e-19</v>
+        <v>1.9285337833010412e-19</v>
       </c>
       <c r="I82" s="0">
-        <v>-1.0681236176388173e-05</v>
+        <v>-1.0601755036262467e-05</v>
       </c>
       <c r="J82" s="0">
-        <v>-7.369387234099729e-11</v>
+        <v>-7.1637868748048697e-11</v>
       </c>
       <c r="K82" s="0">
         <v>0</v>
@@ -6463,39 +6463,39 @@
         <v>0</v>
       </c>
       <c r="O82" s="0">
-        <v>6.8009666734744487e-05</v>
+        <v>6.8009668108892502e-05</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>715</v>
+        <v>821</v>
       </c>
       <c r="B83" s="0">
-        <v>0.82966745179053092</v>
+        <v>0.82966745177947376</v>
       </c>
       <c r="C83" s="0">
         <v>0.0012608371428571427</v>
       </c>
       <c r="D83" s="0">
-        <v>7.1668959915718844e-05</v>
+        <v>7.1594359611105995e-05</v>
       </c>
       <c r="E83" s="0">
         <v>0</v>
       </c>
       <c r="F83" s="0">
-        <v>5.814029698563477e-05</v>
+        <v>5.8179830311267298e-05</v>
       </c>
       <c r="G83" s="0">
-        <v>2.4017204409416636e-07</v>
+        <v>2.3412433292431052e-07</v>
       </c>
       <c r="H83" s="0">
-        <v>1.1420441187992743e-20</v>
+        <v>4.8982704729744951e-21</v>
       </c>
       <c r="I83" s="0">
-        <v>1.3288709319291941e-05</v>
+        <v>1.3180617898698739e-05</v>
       </c>
       <c r="J83" s="0">
-        <v>-2.1843330204503186e-10</v>
+        <v>-2.1293178435676202e-10</v>
       </c>
       <c r="K83" s="0">
         <v>0</v>
@@ -6510,39 +6510,39 @@
         <v>0</v>
       </c>
       <c r="O83" s="0">
-        <v>0.0089717347992278613</v>
+        <v>0.0089717347993007856</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>716</v>
+        <v>822</v>
       </c>
       <c r="B84" s="0">
-        <v>0.63129349229229825</v>
+        <v>0.63129349251822553</v>
       </c>
       <c r="C84" s="0">
         <v>0.0042829491208791195</v>
       </c>
       <c r="D84" s="0">
-        <v>-1.6630327648728524e-05</v>
+        <v>-1.6618766980851408e-05</v>
       </c>
       <c r="E84" s="0">
         <v>0</v>
       </c>
       <c r="F84" s="0">
-        <v>-1.0286898285420868e-05</v>
+        <v>-1.0323309829045586e-05</v>
       </c>
       <c r="G84" s="0">
-        <v>2.2912821588966856e-07</v>
+        <v>2.2348346480726907e-07</v>
       </c>
       <c r="H84" s="0">
-        <v>1.5096607698434116e-20</v>
+        <v>-3.1827412175833926e-17</v>
       </c>
       <c r="I84" s="0">
-        <v>-6.5723493751386955e-06</v>
+        <v>-6.5187375404952756e-06</v>
       </c>
       <c r="J84" s="0">
-        <v>-2.0820405864445493e-10</v>
+        <v>-2.0307608598840547e-10</v>
       </c>
       <c r="K84" s="0">
         <v>0</v>
@@ -6557,39 +6557,39 @@
         <v>1</v>
       </c>
       <c r="O84" s="0">
-        <v>0.0053076736720775912</v>
+        <v>0.0053076736701504861</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>717</v>
+        <v>823</v>
       </c>
       <c r="B85" s="0">
-        <v>0.83165885430487985</v>
+        <v>0.83165885403716344</v>
       </c>
       <c r="C85" s="0">
         <v>0.0021703880219780219</v>
       </c>
       <c r="D85" s="0">
-        <v>-6.278527045282735e-07</v>
+        <v>-6.2931820250650444e-07</v>
       </c>
       <c r="E85" s="0">
         <v>0</v>
       </c>
       <c r="F85" s="0">
-        <v>-8.5324437468718848e-07</v>
+        <v>-8.5296317139716575e-07</v>
       </c>
       <c r="G85" s="0">
-        <v>5.8883486455541944e-08</v>
+        <v>5.7417789123276878e-08</v>
       </c>
       <c r="H85" s="0">
-        <v>5.1924527314245773e-21</v>
+        <v>-2.5026736951457031e-21</v>
       </c>
       <c r="I85" s="0">
-        <v>1.6656169598367009e-07</v>
+        <v>1.6627936045977312e-07</v>
       </c>
       <c r="J85" s="0">
-        <v>-5.3512280302245568e-11</v>
+        <v>-5.2180692386168836e-11</v>
       </c>
       <c r="K85" s="0">
         <v>1</v>
@@ -6604,39 +6604,39 @@
         <v>0</v>
       </c>
       <c r="O85" s="0">
-        <v>0.0051361490600558991</v>
+        <v>0.0051361490616825545</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>718</v>
+        <v>824</v>
       </c>
       <c r="B86" s="0">
-        <v>0.75541996285776414</v>
+        <v>0.75541996278938972</v>
       </c>
       <c r="C86" s="0">
         <v>0.00082946340659340641</v>
       </c>
       <c r="D86" s="0">
-        <v>4.3653982892234478e-05</v>
+        <v>4.3663978544226435e-05</v>
       </c>
       <c r="E86" s="0">
         <v>0</v>
       </c>
       <c r="F86" s="0">
-        <v>4.9940787219394529e-05</v>
+        <v>4.9903851796877525e-05</v>
       </c>
       <c r="G86" s="0">
-        <v>2.0570007739131772e-07</v>
+        <v>2.0031238376203511e-07</v>
       </c>
       <c r="H86" s="0">
-        <v>8.9394149109243286e-20</v>
+        <v>6.08718818483869e-20</v>
       </c>
       <c r="I86" s="0">
-        <v>-6.4923173452670849e-06</v>
+        <v>-6.4400034771426573e-06</v>
       </c>
       <c r="J86" s="0">
-        <v>-1.8705928437455922e-10</v>
+        <v>-1.8215927052939515e-10</v>
       </c>
       <c r="K86" s="0">
         <v>0</v>
@@ -6651,39 +6651,39 @@
         <v>0</v>
       </c>
       <c r="O86" s="0">
-        <v>0.00017006484822934315</v>
+        <v>0.00017006484824385183</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>719</v>
+        <v>825</v>
       </c>
       <c r="B87" s="0">
-        <v>0.88569374047079452</v>
+        <v>0.88569374065541928</v>
       </c>
       <c r="C87" s="0">
         <v>0.00041692989010989011</v>
       </c>
       <c r="D87" s="0">
-        <v>5.7089606572533202e-06</v>
+        <v>5.7230431494210921e-06</v>
       </c>
       <c r="E87" s="0">
         <v>0</v>
       </c>
       <c r="F87" s="0">
-        <v>1.1781228111229219e-05</v>
+        <v>1.1745587172392663e-05</v>
       </c>
       <c r="G87" s="0">
-        <v>7.4785982297557307e-08</v>
+        <v>7.2806646980568682e-08</v>
       </c>
       <c r="H87" s="0">
-        <v>7.273859666039546e-20</v>
+        <v>6.871482126465259e-20</v>
       </c>
       <c r="I87" s="0">
-        <v>-6.1469854268372963e-06</v>
+        <v>-6.0952844607431061e-06</v>
       </c>
       <c r="J87" s="0">
-        <v>-6.8009436232665502e-11</v>
+        <v>-6.6209209101874503e-11</v>
       </c>
       <c r="K87" s="0">
         <v>0</v>
@@ -6698,39 +6698,39 @@
         <v>0</v>
       </c>
       <c r="O87" s="0">
-        <v>0.00028350706134116707</v>
+        <v>0.00028350706128059541</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>720</v>
+        <v>826</v>
       </c>
       <c r="B88" s="0">
-        <v>0.86346120501878576</v>
+        <v>0.86346120492175782</v>
       </c>
       <c r="C88" s="0">
         <v>0.0015838630769230773</v>
       </c>
       <c r="D88" s="0">
-        <v>3.0360183589228927e-05</v>
+        <v>3.0355290139369866e-05</v>
       </c>
       <c r="E88" s="0">
         <v>0</v>
       </c>
       <c r="F88" s="0">
-        <v>2.9733349870478849e-05</v>
+        <v>2.9737176611323232e-05</v>
       </c>
       <c r="G88" s="0">
-        <v>1.7138115201684001e-07</v>
+        <v>1.6703095303360092e-07</v>
       </c>
       <c r="H88" s="0">
-        <v>7.7602968621605865e-20</v>
+        <v>6.9024761696771354e-20</v>
       </c>
       <c r="I88" s="0">
-        <v>4.5560844614309522e-07</v>
+        <v>4.5123449691686182e-07</v>
       </c>
       <c r="J88" s="0">
-        <v>-1.5587940993530883e-10</v>
+        <v>-1.5192190389838995e-10</v>
       </c>
       <c r="K88" s="0">
         <v>0</v>
@@ -6745,39 +6745,39 @@
         <v>0</v>
       </c>
       <c r="O88" s="0">
-        <v>0.00050023096459264984</v>
+        <v>0.00050023096464626039</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>721</v>
+        <v>827</v>
       </c>
       <c r="B89" s="0">
-        <v>0.90768418745615853</v>
+        <v>0.90768418745384349</v>
       </c>
       <c r="C89" s="0">
         <v>0.014315898461538461</v>
       </c>
       <c r="D89" s="0">
-        <v>1.6025240044265473e-06</v>
+        <v>1.6096785623169781e-06</v>
       </c>
       <c r="E89" s="0">
-        <v>8.7046594441094601e-06</v>
+        <v>8.7046594480190321e-06</v>
       </c>
       <c r="F89" s="0">
-        <v>-5.3411639553092123e-06</v>
+        <v>-5.3480310116449286e-06</v>
       </c>
       <c r="G89" s="0">
-        <v>8.5511227041846571e-08</v>
+        <v>8.351399859636994e-08</v>
       </c>
       <c r="H89" s="0">
-        <v>-2.0119307959590759e-21</v>
+        <v>-1.8892448766918645e-20</v>
       </c>
       <c r="I89" s="0">
-        <v>-1.8464049298479043e-06</v>
+        <v>-1.8303879080746982e-06</v>
       </c>
       <c r="J89" s="0">
-        <v>-7.7781567640170633e-11</v>
+        <v>-7.5964578778097843e-11</v>
       </c>
       <c r="K89" s="0">
         <v>1</v>
@@ -6792,39 +6792,39 @@
         <v>0</v>
       </c>
       <c r="O89" s="0">
-        <v>0.21122302721056005</v>
+        <v>0.21122302721000064</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>722</v>
+        <v>828</v>
       </c>
       <c r="B90" s="0">
-        <v>0.87660295419990319</v>
+        <v>0.8766029539329564</v>
       </c>
       <c r="C90" s="0">
         <v>0.00065676263736263757</v>
       </c>
       <c r="D90" s="0">
-        <v>5.8020311920978464e-05</v>
+        <v>5.7950130287788824e-05</v>
       </c>
       <c r="E90" s="0">
         <v>0</v>
       </c>
       <c r="F90" s="0">
-        <v>4.1842586630881455e-05</v>
+        <v>4.1899190029090621e-05</v>
       </c>
       <c r="G90" s="0">
-        <v>1.8987954368506443e-07</v>
+        <v>1.8524588488990472e-07</v>
       </c>
       <c r="H90" s="0">
-        <v>6.1226701517519187e-20</v>
+        <v>-1.1095990166474751e-19</v>
       </c>
       <c r="I90" s="0">
-        <v>1.5988018452676622e-05</v>
+        <v>1.5865862864610622e-05</v>
       </c>
       <c r="J90" s="0">
-        <v>-1.7270626473877442e-10</v>
+        <v>-1.6849080221247275e-10</v>
       </c>
       <c r="K90" s="0">
         <v>0</v>
@@ -6839,39 +6839,39 @@
         <v>0</v>
       </c>
       <c r="O90" s="0">
-        <v>0.000369627272054303</v>
+        <v>0.00036962727216494171</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>723</v>
+        <v>829</v>
       </c>
       <c r="B91" s="0">
-        <v>0.84086726070600193</v>
+        <v>0.84086726068591122</v>
       </c>
       <c r="C91" s="0">
         <v>0.0016166171428571427</v>
       </c>
       <c r="D91" s="0">
-        <v>3.4279340621871524e-05</v>
+        <v>3.4230365713186496e-05</v>
       </c>
       <c r="E91" s="0">
         <v>0</v>
       </c>
       <c r="F91" s="0">
-        <v>2.483377916213024e-05</v>
+        <v>2.4860859179199692e-05</v>
       </c>
       <c r="G91" s="0">
-        <v>9.6530944445293043e-08</v>
+        <v>9.4127724086100673e-08</v>
       </c>
       <c r="H91" s="0">
-        <v>2.1830902881112373e-21</v>
+        <v>-3.9610972367833062e-20</v>
       </c>
       <c r="I91" s="0">
-        <v>9.3491182773127077e-06</v>
+        <v>9.2754643872114161e-06</v>
       </c>
       <c r="J91" s="0">
-        <v>-8.7762016717549238e-11</v>
+        <v>-8.5577310672936904e-11</v>
       </c>
       <c r="K91" s="0">
         <v>0</v>
@@ -6886,39 +6886,39 @@
         <v>1</v>
       </c>
       <c r="O91" s="0">
-        <v>0.005061923606554406</v>
+        <v>0.0050619236066490316</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>724</v>
+        <v>830</v>
       </c>
       <c r="B92" s="0">
-        <v>0.88573320794875554</v>
+        <v>0.88573320339523642</v>
       </c>
       <c r="C92" s="0">
         <v>0.0004673857142857143</v>
       </c>
       <c r="D92" s="0">
-        <v>4.3861838822774809e-05</v>
+        <v>4.3810163529385937e-05</v>
       </c>
       <c r="E92" s="0">
         <v>0</v>
       </c>
       <c r="F92" s="0">
-        <v>3.3823640727916278e-05</v>
+        <v>3.3854221706979881e-05</v>
       </c>
       <c r="G92" s="0">
-        <v>1.0341140974255281e-07</v>
+        <v>1.0083959326337678e-07</v>
       </c>
       <c r="H92" s="0">
-        <v>9.320285313025508e-20</v>
+        <v>9.7856510841861966e-20</v>
       </c>
       <c r="I92" s="0">
-        <v>9.9348807295129693e-06</v>
+        <v>9.8551939342372907e-06</v>
       </c>
       <c r="J92" s="0">
-        <v>-9.4044397083329701e-11</v>
+        <v>-9.17050947085409e-11</v>
       </c>
       <c r="K92" s="0">
         <v>0</v>
@@ -6933,7 +6933,7 @@
         <v>0</v>
       </c>
       <c r="O92" s="0">
-        <v>0.00026225671300522235</v>
+        <v>0.00026225671435211006</v>
       </c>
     </row>
   </sheetData>
@@ -6941,7 +6941,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -6954,7 +6954,7 @@
     <col min="7" max="7" width="16.5703125" customWidth="true"/>
     <col min="8" max="8" width="18" customWidth="true"/>
     <col min="9" max="9" width="17.42578125" customWidth="true"/>
-    <col min="10" max="10" width="15.5703125" customWidth="true"/>
+    <col min="10" max="10" width="16.28515625" customWidth="true"/>
     <col min="11" max="11" width="16.7109375" customWidth="true"/>
     <col min="12" max="12" width="10.42578125" customWidth="true"/>
     <col min="13" max="13" width="13.42578125" customWidth="true"/>
@@ -7010,31 +7010,31 @@
         <v>740</v>
       </c>
       <c r="B2" s="0">
-        <v>0.78149579333799934</v>
+        <v>0.78149579344971631</v>
       </c>
       <c r="C2" s="0">
         <v>0.00099664659340659308</v>
       </c>
       <c r="D2" s="0">
-        <v>2.0136951148813972e-06</v>
+        <v>1.9900697254586188e-06</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>3.4892906176022027e-06</v>
+        <v>3.5045361520810589e-06</v>
       </c>
       <c r="G2" s="0">
-        <v>8.5552350798056308e-08</v>
+        <v>8.4769866086300773e-08</v>
       </c>
       <c r="H2" s="0">
-        <v>8.1948045414280025e-06</v>
+        <v>8.3987231258036823e-06</v>
       </c>
       <c r="I2" s="0">
-        <v>-9.7570304998489453e-06</v>
+        <v>-9.9990521334075038e-06</v>
       </c>
       <c r="J2" s="0">
-        <v>1.0781049020816829e-09</v>
+        <v>1.0927148950812254e-09</v>
       </c>
       <c r="K2" s="0">
         <v>0</v>
@@ -7054,31 +7054,31 @@
         <v>741</v>
       </c>
       <c r="B3" s="0">
-        <v>0.89377294262467666</v>
+        <v>0.89377294242544958</v>
       </c>
       <c r="C3" s="0">
         <v>0.0059910226373626405</v>
       </c>
       <c r="D3" s="0">
-        <v>4.5854601253666434e-05</v>
+        <v>4.6097668458654101e-05</v>
       </c>
       <c r="E3" s="0">
-        <v>5.6092878156187332e-05</v>
+        <v>5.6092878307398962e-05</v>
       </c>
       <c r="F3" s="0">
-        <v>-1.7018064889686864e-05</v>
+        <v>-1.713181781802315e-05</v>
       </c>
       <c r="G3" s="0">
-        <v>4.0161856686372956e-07</v>
+        <v>3.9702835894563232e-07</v>
       </c>
       <c r="H3" s="0">
-        <v>-9.5461535573181483e-06</v>
+        <v>-9.8516870552927001e-06</v>
       </c>
       <c r="I3" s="0">
-        <v>1.5918749597603938e-05</v>
+        <v>1.6585717378069669e-05</v>
       </c>
       <c r="J3" s="0">
-        <v>5.5733800164476808e-09</v>
+        <v>5.5492875556874429e-09</v>
       </c>
       <c r="K3" s="0">
         <v>1</v>
@@ -7098,31 +7098,31 @@
         <v>742</v>
       </c>
       <c r="B4" s="0">
-        <v>0.58038968102602051</v>
+        <v>0.58038968104253585</v>
       </c>
       <c r="C4" s="0">
         <v>0.024877143296703302</v>
       </c>
       <c r="D4" s="0">
-        <v>3.7112557667321514e-05</v>
+        <v>3.7269948494450528e-05</v>
       </c>
       <c r="E4" s="0">
-        <v>4.527008604012679e-05</v>
+        <v>4.5270085987693838e-05</v>
       </c>
       <c r="F4" s="0">
-        <v>-1.2626279588199527e-05</v>
+        <v>-1.2663977484241485e-05</v>
       </c>
       <c r="G4" s="0">
-        <v>2.6144858101123694e-07</v>
+        <v>2.5843584773213552e-07</v>
       </c>
       <c r="H4" s="0">
-        <v>-7.7143873535868545e-06</v>
+        <v>-8.0072936271127547e-06</v>
       </c>
       <c r="I4" s="0">
-        <v>1.1918856027277204e-05</v>
+        <v>1.240980409181546e-05</v>
       </c>
       <c r="J4" s="0">
-        <v>2.833960692664314e-09</v>
+        <v>2.8936785633342394e-09</v>
       </c>
       <c r="K4" s="0">
         <v>1</v>
@@ -7142,31 +7142,31 @@
         <v>743</v>
       </c>
       <c r="B5" s="0">
-        <v>0.49684304335047907</v>
+        <v>0.49684304334618173</v>
       </c>
       <c r="C5" s="0">
         <v>0.028964137692307681</v>
       </c>
       <c r="D5" s="0">
-        <v>6.5743204550880314e-05</v>
+        <v>6.6064717536043653e-05</v>
       </c>
       <c r="E5" s="0">
-        <v>9.6405943030097204e-05</v>
+        <v>9.640594304440149e-05</v>
       </c>
       <c r="F5" s="0">
-        <v>-3.7956393428140937e-05</v>
+        <v>-3.8141602898747344e-05</v>
       </c>
       <c r="G5" s="0">
-        <v>5.2586788979054887e-07</v>
+        <v>5.1919777502719729e-07</v>
       </c>
       <c r="H5" s="0">
-        <v>-8.5134334040928129e-06</v>
+        <v>-8.8472479347460524e-06</v>
       </c>
       <c r="I5" s="0">
-        <v>1.527167117831336e-05</v>
+        <v>1.6118668672542572e-05</v>
       </c>
       <c r="J5" s="0">
-        <v>9.5492849129500301e-09</v>
+        <v>9.758877565791015e-09</v>
       </c>
       <c r="K5" s="0">
         <v>1</v>
@@ -7186,31 +7186,31 @@
         <v>744</v>
       </c>
       <c r="B6" s="0">
-        <v>0.83894268763452251</v>
+        <v>0.83894268773261005</v>
       </c>
       <c r="C6" s="0">
         <v>0.00056924747252747249</v>
       </c>
       <c r="D6" s="0">
-        <v>2.1538805728124604e-05</v>
+        <v>2.1574957974692811e-05</v>
       </c>
       <c r="E6" s="0">
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>1.3163337847246787e-05</v>
+        <v>1.3068094109870497e-05</v>
       </c>
       <c r="G6" s="0">
-        <v>1.3971798762627256e-07</v>
+        <v>1.3741647897294413e-07</v>
       </c>
       <c r="H6" s="0">
-        <v>3.993439680794808e-05</v>
+        <v>4.0083985838612955e-05</v>
       </c>
       <c r="I6" s="0">
-        <v>-3.1701960303047267e-05</v>
+        <v>-3.1717829784444012e-05</v>
       </c>
       <c r="J6" s="0">
-        <v>3.3133883507312526e-09</v>
+        <v>3.2913316804254137e-09</v>
       </c>
       <c r="K6" s="0">
         <v>0</v>
@@ -7230,31 +7230,31 @@
         <v>745</v>
       </c>
       <c r="B7" s="0">
-        <v>0.9085352004413042</v>
+        <v>0.908535200552539</v>
       </c>
       <c r="C7" s="0">
         <v>0.0064199401098901073</v>
       </c>
       <c r="D7" s="0">
-        <v>3.1415681062157432e-05</v>
+        <v>3.1227825184966701e-05</v>
       </c>
       <c r="E7" s="0">
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>3.0513991664179122e-05</v>
+        <v>3.0573805338905819e-05</v>
       </c>
       <c r="G7" s="0">
-        <v>2.2775166446759912e-07</v>
+        <v>2.2521614644639557e-07</v>
       </c>
       <c r="H7" s="0">
-        <v>2.4507996416969836e-05</v>
+        <v>2.3921682776091813e-05</v>
       </c>
       <c r="I7" s="0">
-        <v>-2.3836366372482499e-05</v>
+        <v>-2.3494863305276729e-05</v>
       </c>
       <c r="J7" s="0">
-        <v>2.3076890233732455e-09</v>
+        <v>1.9842287994018557e-09</v>
       </c>
       <c r="K7" s="0">
         <v>0</v>
@@ -7274,31 +7274,31 @@
         <v>746</v>
       </c>
       <c r="B8" s="0">
-        <v>0.8389707174230655</v>
+        <v>0.83897071741063856</v>
       </c>
       <c r="C8" s="0">
         <v>0.0071889561538461526</v>
       </c>
       <c r="D8" s="0">
-        <v>2.2140228071516776e-05</v>
+        <v>2.208345799696226e-05</v>
       </c>
       <c r="E8" s="0">
-        <v>4.8116484804233987e-05</v>
+        <v>4.8116484526700938e-05</v>
       </c>
       <c r="F8" s="0">
-        <v>-1.7728318060527281e-05</v>
+        <v>-1.7726150351538717e-05</v>
       </c>
       <c r="G8" s="0">
-        <v>3.5297584024723804e-07</v>
+        <v>3.4729166152057451e-07</v>
       </c>
       <c r="H8" s="0">
-        <v>-1.7094112174782437e-06</v>
+        <v>-1.7203951790187307e-06</v>
       </c>
       <c r="I8" s="0">
-        <v>-6.8972570783776441e-06</v>
+        <v>-6.9396347368631319e-06</v>
       </c>
       <c r="J8" s="0">
-        <v>5.7537834187194813e-09</v>
+        <v>5.8620761613262004e-09</v>
       </c>
       <c r="K8" s="0">
         <v>0</v>
@@ -7318,31 +7318,31 @@
         <v>747</v>
       </c>
       <c r="B9" s="0">
-        <v>0.85359648677539157</v>
+        <v>0.85359648674592037</v>
       </c>
       <c r="C9" s="0">
         <v>0.0014056876923076917</v>
       </c>
       <c r="D9" s="0">
-        <v>0.00013192946594496653</v>
+        <v>0.00013190698263294796</v>
       </c>
       <c r="E9" s="0">
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>5.059159579502395e-05</v>
+        <v>5.0762793253485657e-05</v>
       </c>
       <c r="G9" s="0">
-        <v>3.9604960259153678e-07</v>
+        <v>3.919358216494932e-07</v>
       </c>
       <c r="H9" s="0">
-        <v>4.8099398544548053e-05</v>
+        <v>4.7394078593728396e-05</v>
       </c>
       <c r="I9" s="0">
-        <v>3.2838588898189185e-05</v>
+        <v>3.3354818629073274e-05</v>
       </c>
       <c r="J9" s="0">
-        <v>3.8331046138122575e-09</v>
+        <v>3.3563350111396923e-09</v>
       </c>
       <c r="K9" s="0">
         <v>0</v>
@@ -7362,31 +7362,31 @@
         <v>748</v>
       </c>
       <c r="B10" s="0">
-        <v>0.93573023505403186</v>
+        <v>0.93573023509885622</v>
       </c>
       <c r="C10" s="0">
         <v>0.0019589672527472535</v>
       </c>
       <c r="D10" s="0">
-        <v>3.5144198991491519e-05</v>
+        <v>3.4955363317342404e-05</v>
       </c>
       <c r="E10" s="0">
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>3.5428061687825868e-05</v>
+        <v>3.5563314901617889e-05</v>
       </c>
       <c r="G10" s="0">
-        <v>1.8234572196433129e-07</v>
+        <v>1.7931145058750362e-07</v>
       </c>
       <c r="H10" s="0">
-        <v>3.0157869813856401e-05</v>
+        <v>2.9728855741498981e-05</v>
       </c>
       <c r="I10" s="0">
-        <v>-3.0624711997448911e-05</v>
+        <v>-3.0516693247770781e-05</v>
       </c>
       <c r="J10" s="0">
-        <v>6.3376529382559027e-10</v>
+        <v>5.7447140881100589e-10</v>
       </c>
       <c r="K10" s="0">
         <v>0</v>
@@ -7406,31 +7406,31 @@
         <v>749</v>
       </c>
       <c r="B11" s="0">
-        <v>0.76744161783916032</v>
+        <v>0.76744161778897346</v>
       </c>
       <c r="C11" s="0">
         <v>0.0097142418681318687</v>
       </c>
       <c r="D11" s="0">
-        <v>6.4258003887952426e-05</v>
+        <v>6.4881996968837839e-05</v>
       </c>
       <c r="E11" s="0">
-        <v>8.330731102493227e-05</v>
+        <v>8.3307311031725258e-05</v>
       </c>
       <c r="F11" s="0">
-        <v>-3.4329695490066393e-05</v>
+        <v>-3.4584305090733601e-05</v>
       </c>
       <c r="G11" s="0">
-        <v>6.3104344684265593e-07</v>
+        <v>6.2377278197003093e-07</v>
       </c>
       <c r="H11" s="0">
-        <v>-3.1024238565469362e-06</v>
+        <v>-3.2309991525949809e-06</v>
       </c>
       <c r="I11" s="0">
-        <v>1.7738647402708901e-05</v>
+        <v>1.8752804892849853e-05</v>
       </c>
       <c r="J11" s="0">
-        <v>1.3121360081927896e-08</v>
+        <v>1.3412505621279708e-08</v>
       </c>
       <c r="K11" s="0">
         <v>1</v>
@@ -7450,31 +7450,31 @@
         <v>750</v>
       </c>
       <c r="B12" s="0">
-        <v>0.64522645358968622</v>
+        <v>0.64522645365168074</v>
       </c>
       <c r="C12" s="0">
         <v>0.014572179450549456</v>
       </c>
       <c r="D12" s="0">
-        <v>4.1683274572183295e-05</v>
+        <v>4.1672598243472539e-05</v>
       </c>
       <c r="E12" s="0">
-        <v>3.9161728526384605e-05</v>
+        <v>3.916172851490636e-05</v>
       </c>
       <c r="F12" s="0">
-        <v>2.5706520448915444e-06</v>
+        <v>2.6762804815156465e-06</v>
       </c>
       <c r="G12" s="0">
-        <v>3.1014755457259202e-07</v>
+        <v>3.0710911613927485e-07</v>
       </c>
       <c r="H12" s="0">
-        <v>-1.3512363181858895e-05</v>
+        <v>-1.3921168879151448e-05</v>
       </c>
       <c r="I12" s="0">
-        <v>1.314590853904908e-05</v>
+        <v>1.3441220723360424e-05</v>
       </c>
       <c r="J12" s="0">
-        <v>7.2010891443697163e-09</v>
+        <v>7.4282867022814063e-09</v>
       </c>
       <c r="K12" s="0">
         <v>1</v>
@@ -7494,31 +7494,31 @@
         <v>751</v>
       </c>
       <c r="B13" s="0">
-        <v>0.82012382005816176</v>
+        <v>0.82012381999086181</v>
       </c>
       <c r="C13" s="0">
         <v>0.041016255714285729</v>
       </c>
       <c r="D13" s="0">
-        <v>7.8902192268376145e-05</v>
+        <v>7.8447844134664393e-05</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
       </c>
       <c r="F13" s="0">
-        <v>7.1515078693980228e-05</v>
+        <v>7.1709763055300465e-05</v>
       </c>
       <c r="G13" s="0">
-        <v>3.7076393897050204e-07</v>
+        <v>3.649623751436058e-07</v>
       </c>
       <c r="H13" s="0">
-        <v>2.8768352696553257e-05</v>
+        <v>2.7911417993194505e-05</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.175455082687895e-05</v>
+        <v>-2.1540604739077954e-05</v>
       </c>
       <c r="J13" s="0">
-        <v>2.5477657511072322e-09</v>
+        <v>2.3054501037725848e-09</v>
       </c>
       <c r="K13" s="0">
         <v>0</v>
@@ -7538,31 +7538,31 @@
         <v>752</v>
       </c>
       <c r="B14" s="0">
-        <v>0.92530677364875635</v>
+        <v>0.92530677364918812</v>
       </c>
       <c r="C14" s="0">
         <v>0.045989524065934054</v>
       </c>
       <c r="D14" s="0">
-        <v>2.2321895573288301e-05</v>
+        <v>2.2122792780488103e-05</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>3.0869070151657749e-05</v>
+        <v>3.1007522323954741e-05</v>
       </c>
       <c r="G14" s="0">
-        <v>1.2735796423546229e-07</v>
+        <v>1.2521206291414883e-07</v>
       </c>
       <c r="H14" s="0">
-        <v>1.2811581128456677e-05</v>
+        <v>1.2420604646334439e-05</v>
       </c>
       <c r="I14" s="0">
-        <v>-2.1486065757484087e-05</v>
+        <v>-2.1430499675951335e-05</v>
       </c>
       <c r="J14" s="0">
-        <v>-4.7913577500767164e-11</v>
+        <v>-4.6576763889434776e-11</v>
       </c>
       <c r="K14" s="0">
         <v>0</v>
@@ -7582,31 +7582,31 @@
         <v>753</v>
       </c>
       <c r="B15" s="0">
-        <v>0.9079149677423094</v>
+        <v>0.9079149677510141</v>
       </c>
       <c r="C15" s="0">
         <v>0.00061881285714285729</v>
       </c>
       <c r="D15" s="0">
-        <v>0.00014033668716755018</v>
+        <v>0.00013997550528303628</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
       </c>
       <c r="F15" s="0">
-        <v>8.1767137304870793e-05</v>
+        <v>8.1861026118350668e-05</v>
       </c>
       <c r="G15" s="0">
-        <v>7.793081175600224e-07</v>
+        <v>7.6644149743677037e-07</v>
       </c>
       <c r="H15" s="0">
-        <v>8.5143165170320734e-05</v>
+        <v>8.4561086827146932e-05</v>
       </c>
       <c r="I15" s="0">
-        <v>-2.7360650743282254e-05</v>
+        <v>-2.7219662221765937e-05</v>
       </c>
       <c r="J15" s="0">
-        <v>7.727318080879089e-09</v>
+        <v>6.613061867841917e-09</v>
       </c>
       <c r="K15" s="0">
         <v>0</v>
@@ -7626,31 +7626,31 @@
         <v>754</v>
       </c>
       <c r="B16" s="0">
-        <v>0.90982261977488854</v>
+        <v>0.90982261985644763</v>
       </c>
       <c r="C16" s="0">
         <v>0.0010574215384615388</v>
       </c>
       <c r="D16" s="0">
-        <v>9.291321780530764e-05</v>
+        <v>9.2621611249108993e-05</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
       </c>
       <c r="F16" s="0">
-        <v>6.9084815799532438e-05</v>
+        <v>6.922039942356984e-05</v>
       </c>
       <c r="G16" s="0">
-        <v>6.598981726314717e-07</v>
+        <v>6.5071077785437936e-07</v>
       </c>
       <c r="H16" s="0">
-        <v>5.8551227489884293e-05</v>
+        <v>5.7839850910319656e-05</v>
       </c>
       <c r="I16" s="0">
-        <v>-3.5389329282487076e-05</v>
+        <v>-3.5094870908704101e-05</v>
       </c>
       <c r="J16" s="0">
-        <v>6.6056257465126251e-09</v>
+        <v>5.5210460692234451e-09</v>
       </c>
       <c r="K16" s="0">
         <v>0</v>
@@ -7670,31 +7670,31 @@
         <v>755</v>
       </c>
       <c r="B17" s="0">
-        <v>0.7924154816897645</v>
+        <v>0.79241548245486415</v>
       </c>
       <c r="C17" s="0">
         <v>0.0013863102197802196</v>
       </c>
       <c r="D17" s="0">
-        <v>0.00010587191685054673</v>
+        <v>0.00010536924664579233</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
       </c>
       <c r="F17" s="0">
-        <v>0.00011098790366935934</v>
+        <v>0.00011133934163417246</v>
       </c>
       <c r="G17" s="0">
-        <v>6.0345886541670981e-07</v>
+        <v>5.9510210946278985e-07</v>
       </c>
       <c r="H17" s="0">
-        <v>7.6261739174620323e-05</v>
+        <v>7.5180951776519314e-05</v>
       </c>
       <c r="I17" s="0">
-        <v>-8.1984635441843695e-05</v>
+        <v>-8.1749229664260502e-05</v>
       </c>
       <c r="J17" s="0">
-        <v>3.4505829940454031e-09</v>
+        <v>3.0807898982696544e-09</v>
       </c>
       <c r="K17" s="0">
         <v>0</v>
@@ -7714,31 +7714,31 @@
         <v>756</v>
       </c>
       <c r="B18" s="0">
-        <v>0.82169818775600156</v>
+        <v>0.82169818838093611</v>
       </c>
       <c r="C18" s="0">
         <v>0.0015645810989010991</v>
       </c>
       <c r="D18" s="0">
-        <v>4.5495910617462028e-05</v>
+        <v>4.539987920532234e-05</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
       </c>
       <c r="F18" s="0">
-        <v>3.9150401676852915e-05</v>
+        <v>3.9140227572515209e-05</v>
       </c>
       <c r="G18" s="0">
-        <v>1.9359613514762365e-07</v>
+        <v>1.9103473903008706e-07</v>
       </c>
       <c r="H18" s="0">
-        <v>6.4171614711186012e-05</v>
+        <v>6.4405911931142881e-05</v>
       </c>
       <c r="I18" s="0">
-        <v>-5.8021251606730817e-05</v>
+        <v>-5.8338715418857574e-05</v>
       </c>
       <c r="J18" s="0">
-        <v>1.5497010062939689e-09</v>
+        <v>1.4203814917380171e-09</v>
       </c>
       <c r="K18" s="0">
         <v>0</v>
@@ -7758,31 +7758,31 @@
         <v>757</v>
       </c>
       <c r="B19" s="0">
-        <v>0.74945301207952264</v>
+        <v>0.74945301184209867</v>
       </c>
       <c r="C19" s="0">
         <v>0.0035383113186813198</v>
       </c>
       <c r="D19" s="0">
-        <v>2.7084566468243708e-05</v>
+        <v>2.7102218589585664e-05</v>
       </c>
       <c r="E19" s="0">
-        <v>6.3640208230779577e-05</v>
+        <v>6.3640208300538108e-05</v>
       </c>
       <c r="F19" s="0">
-        <v>-3.7402528470481601e-05</v>
+        <v>-3.7466219484891061e-05</v>
       </c>
       <c r="G19" s="0">
-        <v>2.94652931508848e-07</v>
+        <v>2.907224379649799e-07</v>
       </c>
       <c r="H19" s="0">
-        <v>-7.7875228485127796e-06</v>
+        <v>-7.959245860577202e-06</v>
       </c>
       <c r="I19" s="0">
-        <v>8.3358396225783158e-06</v>
+        <v>8.5927433948466945e-06</v>
       </c>
       <c r="J19" s="0">
-        <v>3.91700237134319e-09</v>
+        <v>4.0098017041484023e-09</v>
       </c>
       <c r="K19" s="0">
         <v>1</v>
@@ -7802,31 +7802,31 @@
         <v>758</v>
       </c>
       <c r="B20" s="0">
-        <v>0.67062566720905337</v>
+        <v>0.6706256672362465</v>
       </c>
       <c r="C20" s="0">
         <v>0.013227400879120874</v>
       </c>
       <c r="D20" s="0">
-        <v>4.1012490281673671e-05</v>
+        <v>4.0940361378610627e-05</v>
       </c>
       <c r="E20" s="0">
-        <v>0.00010053981715883349</v>
+        <v>0.00010053981719394424</v>
       </c>
       <c r="F20" s="0">
-        <v>-5.3444262722940007e-05</v>
+        <v>-5.3530034223573991e-05</v>
       </c>
       <c r="G20" s="0">
-        <v>6.9521067968901653e-07</v>
+        <v>6.8462141765820564e-07</v>
       </c>
       <c r="H20" s="0">
-        <v>4.688472630807807e-06</v>
+        <v>4.422690124805897e-06</v>
       </c>
       <c r="I20" s="0">
-        <v>-1.1472013579761806e-05</v>
+        <v>-1.1182098598500611e-05</v>
       </c>
       <c r="J20" s="0">
-        <v>5.2661150451737321e-09</v>
+        <v>5.3654642768925933e-09</v>
       </c>
       <c r="K20" s="0">
         <v>0</v>
@@ -7846,31 +7846,31 @@
         <v>759</v>
       </c>
       <c r="B21" s="0">
-        <v>0.72714244584911225</v>
+        <v>0.72714244585210863</v>
       </c>
       <c r="C21" s="0">
         <v>0.020689979230769231</v>
       </c>
       <c r="D21" s="0">
-        <v>6.1370219723223384e-05</v>
+        <v>6.1767754382941714e-05</v>
       </c>
       <c r="E21" s="0">
-        <v>7.8949506548336201e-05</v>
+        <v>7.8949506544632011e-05</v>
       </c>
       <c r="F21" s="0">
-        <v>-2.8453196608876139e-05</v>
+        <v>-2.8609345516273219e-05</v>
       </c>
       <c r="G21" s="0">
-        <v>4.9652344070984838e-07</v>
+        <v>4.9140876767692237e-07</v>
       </c>
       <c r="H21" s="0">
-        <v>-9.1885977653343551e-06</v>
+        <v>-9.5393114117417216e-06</v>
       </c>
       <c r="I21" s="0">
-        <v>1.9561543738785603e-05</v>
+        <v>2.0470933269609714e-05</v>
       </c>
       <c r="J21" s="0">
-        <v>4.4403696022257287e-09</v>
+        <v>4.56272903800778e-09</v>
       </c>
       <c r="K21" s="0">
         <v>1</v>
@@ -7890,31 +7890,31 @@
         <v>760</v>
       </c>
       <c r="B22" s="0">
-        <v>0.6896356885712891</v>
+        <v>0.68963568877976777</v>
       </c>
       <c r="C22" s="0">
         <v>0.035353695054945039</v>
       </c>
       <c r="D22" s="0">
-        <v>3.5632770668658732e-05</v>
+        <v>3.581698400952587e-05</v>
       </c>
       <c r="E22" s="0">
-        <v>5.0143784421009414e-05</v>
+        <v>5.0143784441965768e-05</v>
       </c>
       <c r="F22" s="0">
-        <v>-1.897142871539623e-05</v>
+        <v>-1.9053363871274676e-05</v>
       </c>
       <c r="G22" s="0">
-        <v>2.9063126251660749e-07</v>
+        <v>2.8729849843403529e-07</v>
       </c>
       <c r="H22" s="0">
-        <v>-6.4067484012641266e-06</v>
+        <v>-6.6428974721002299e-06</v>
       </c>
       <c r="I22" s="0">
-        <v>1.0573368661649883e-05</v>
+        <v>1.1078928519032012e-05</v>
       </c>
       <c r="J22" s="0">
-        <v>3.1634401431838999e-09</v>
+        <v>3.2338934689608997e-09</v>
       </c>
       <c r="K22" s="0">
         <v>1</v>
@@ -7934,31 +7934,31 @@
         <v>761</v>
       </c>
       <c r="B23" s="0">
-        <v>0.81607049181438751</v>
+        <v>0.81607049158119394</v>
       </c>
       <c r="C23" s="0">
         <v>0.00058346373626373617</v>
       </c>
       <c r="D23" s="0">
-        <v>8.5181344045622283e-05</v>
+        <v>8.4687757109977303e-05</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
       </c>
       <c r="F23" s="0">
-        <v>0.00010384993467460605</v>
+        <v>0.00010428085026581993</v>
       </c>
       <c r="G23" s="0">
-        <v>5.7766499821691262e-07</v>
+        <v>5.7104377308177636e-07</v>
       </c>
       <c r="H23" s="0">
-        <v>5.9935089524622417e-05</v>
+        <v>5.8763501500812367e-05</v>
       </c>
       <c r="I23" s="0">
-        <v>-7.9184869808236619e-05</v>
+        <v>-7.893080299252312e-05</v>
       </c>
       <c r="J23" s="0">
-        <v>3.5246564135220371e-09</v>
+        <v>3.1645627863508864e-09</v>
       </c>
       <c r="K23" s="0">
         <v>0</v>
@@ -7978,31 +7978,31 @@
         <v>762</v>
       </c>
       <c r="B24" s="0">
-        <v>0.83693409514047812</v>
+        <v>0.83693409451307599</v>
       </c>
       <c r="C24" s="0">
         <v>0.00077550758241758219</v>
       </c>
       <c r="D24" s="0">
-        <v>0.00010860341167993467</v>
+        <v>0.00010814108023017083</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>8.2123734463997338e-05</v>
+        <v>8.2347383341448539e-05</v>
       </c>
       <c r="G24" s="0">
-        <v>5.5352778356843138e-07</v>
+        <v>5.4638431907356867e-07</v>
       </c>
       <c r="H24" s="0">
-        <v>4.8779846275985414e-05</v>
+        <v>4.7445247491145427e-05</v>
       </c>
       <c r="I24" s="0">
-        <v>-2.2858381715025196e-05</v>
+        <v>-2.2202096461883378e-05</v>
       </c>
       <c r="J24" s="0">
-        <v>4.684871408678151e-09</v>
+        <v>4.1615403866770322e-09</v>
       </c>
       <c r="K24" s="0">
         <v>0</v>
@@ -8022,31 +8022,31 @@
         <v>763</v>
       </c>
       <c r="B25" s="0">
-        <v>0.87863421383823914</v>
+        <v>0.87863421325276381</v>
       </c>
       <c r="C25" s="0">
         <v>0.00163550934065934</v>
       </c>
       <c r="D25" s="0">
-        <v>6.1107430978920557e-05</v>
+        <v>6.0788117733335188e-05</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
       </c>
       <c r="F25" s="0">
-        <v>6.2164340589116653e-05</v>
+        <v>6.235009914705737e-05</v>
       </c>
       <c r="G25" s="0">
-        <v>3.4793832273934259e-07</v>
+        <v>3.4254412939297521e-07</v>
       </c>
       <c r="H25" s="0">
-        <v>5.2303749117754635e-05</v>
+        <v>5.1667257006144419e-05</v>
       </c>
       <c r="I25" s="0">
-        <v>-5.3710608806701266e-05</v>
+        <v>-5.3573594583611476e-05</v>
       </c>
       <c r="J25" s="0">
-        <v>2.0117560111944073e-09</v>
+        <v>1.8120343518989454e-09</v>
       </c>
       <c r="K25" s="0">
         <v>0</v>
@@ -8066,31 +8066,31 @@
         <v>764</v>
       </c>
       <c r="B26" s="0">
-        <v>0.81001725405564173</v>
+        <v>0.8100172540067323</v>
       </c>
       <c r="C26" s="0">
         <v>0.01328132923076923</v>
       </c>
       <c r="D26" s="0">
-        <v>3.5820499172341685e-05</v>
+        <v>3.6028593712791266e-05</v>
       </c>
       <c r="E26" s="0">
-        <v>5.9378452703179745e-05</v>
+        <v>5.9378452696773967e-05</v>
       </c>
       <c r="F26" s="0">
-        <v>-2.836927744364384e-05</v>
+        <v>-2.8509461542012611e-05</v>
       </c>
       <c r="G26" s="0">
-        <v>3.3113777749899343e-07</v>
+        <v>3.268391611910584e-07</v>
       </c>
       <c r="H26" s="0">
-        <v>-5.6897911904107607e-06</v>
+        <v>-5.9162375998713385e-06</v>
       </c>
       <c r="I26" s="0">
-        <v>1.0162748302535644e-05</v>
+        <v>1.0741586409066136e-05</v>
       </c>
       <c r="J26" s="0">
-        <v>7.2290231819041855e-09</v>
+        <v>7.4145876440531494e-09</v>
       </c>
       <c r="K26" s="0">
         <v>1</v>
@@ -8110,31 +8110,31 @@
         <v>765</v>
       </c>
       <c r="B27" s="0">
-        <v>0.57923297511811345</v>
+        <v>0.57923297472173718</v>
       </c>
       <c r="C27" s="0">
         <v>0.014742598461538463</v>
       </c>
       <c r="D27" s="0">
-        <v>8.3970484937078609e-05</v>
+        <v>8.385027017380449e-05</v>
       </c>
       <c r="E27" s="0">
-        <v>0.00018925866947844326</v>
+        <v>0.00018925866941563467</v>
       </c>
       <c r="F27" s="0">
-        <v>-9.5418745877078851e-05</v>
+        <v>-9.5529835083755808e-05</v>
       </c>
       <c r="G27" s="0">
-        <v>1.1763344847693941e-06</v>
+        <v>1.1586777119680097e-06</v>
       </c>
       <c r="H27" s="0">
-        <v>6.1518139227485201e-06</v>
+        <v>5.819599081870149e-06</v>
       </c>
       <c r="I27" s="0">
-        <v>-1.720925033999572e-05</v>
+        <v>-1.6868715405035537e-05</v>
       </c>
       <c r="J27" s="0">
-        <v>1.1663268192004141e-08</v>
+        <v>1.1874453123007203e-08</v>
       </c>
       <c r="K27" s="0">
         <v>0</v>
@@ -8154,31 +8154,31 @@
         <v>766</v>
       </c>
       <c r="B28" s="0">
-        <v>0.88645176910926837</v>
+        <v>0.88645176921665325</v>
       </c>
       <c r="C28" s="0">
         <v>0.00056269538461538424</v>
       </c>
       <c r="D28" s="0">
-        <v>0.00013038423432632624</v>
+        <v>0.00013021370716755721</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>7.007533751755558e-05</v>
+        <v>7.0088682851597041e-05</v>
       </c>
       <c r="G28" s="0">
-        <v>7.7795987119374409e-07</v>
+        <v>7.6595335778466882e-07</v>
       </c>
       <c r="H28" s="0">
-        <v>0.00012641462718709337</v>
+        <v>0.0001262775885549285</v>
       </c>
       <c r="I28" s="0">
-        <v>-6.6891653504846409e-05</v>
+        <v>-6.6925588141298779e-05</v>
       </c>
       <c r="J28" s="0">
-        <v>7.9632553299531896e-09</v>
+        <v>7.0705445457790997e-09</v>
       </c>
       <c r="K28" s="0">
         <v>0</v>
@@ -8198,31 +8198,31 @@
         <v>767</v>
       </c>
       <c r="B29" s="0">
-        <v>0.68710694899702685</v>
+        <v>0.68710694951369455</v>
       </c>
       <c r="C29" s="0">
         <v>0.016124222307692306</v>
       </c>
       <c r="D29" s="0">
-        <v>9.7579237130133802e-05</v>
+        <v>9.8174699269337434e-05</v>
       </c>
       <c r="E29" s="0">
-        <v>0.00012799179861964398</v>
+        <v>0.00012799179871744997</v>
       </c>
       <c r="F29" s="0">
-        <v>-4.5353574750619579e-05</v>
+        <v>-4.5553671564022026e-05</v>
       </c>
       <c r="G29" s="0">
-        <v>6.6386439841965594e-07</v>
+        <v>6.5657306844046065e-07</v>
       </c>
       <c r="H29" s="0">
-        <v>-1.2260025569374175e-05</v>
+        <v>-1.2727260314730658e-05</v>
       </c>
       <c r="I29" s="0">
-        <v>2.6530450670140626e-05</v>
+        <v>2.7800351242922607e-05</v>
       </c>
       <c r="J29" s="0">
-        <v>6.7237619232942694e-09</v>
+        <v>6.9081192770790946e-09</v>
       </c>
       <c r="K29" s="0">
         <v>1</v>
@@ -8242,31 +8242,31 @@
         <v>768</v>
       </c>
       <c r="B30" s="0">
-        <v>0.77759445748602507</v>
+        <v>0.77759445751360423</v>
       </c>
       <c r="C30" s="0">
         <v>0.014526590109890108</v>
       </c>
       <c r="D30" s="0">
-        <v>3.834746493166417e-05</v>
+        <v>3.8576651959683029e-05</v>
       </c>
       <c r="E30" s="0">
-        <v>5.405171856976819e-05</v>
+        <v>5.4051718498037184e-05</v>
       </c>
       <c r="F30" s="0">
-        <v>-2.1226335769339063e-05</v>
+        <v>-2.1330713526915081e-05</v>
       </c>
       <c r="G30" s="0">
-        <v>3.2573266972343246e-07</v>
+        <v>3.2231933338857907e-07</v>
       </c>
       <c r="H30" s="0">
-        <v>-8.5519179712226971e-06</v>
+        <v>-8.8423237017547499e-06</v>
       </c>
       <c r="I30" s="0">
-        <v>1.3744883324502267e-05</v>
+        <v>1.437217421987843e-05</v>
       </c>
       <c r="J30" s="0">
-        <v>3.3841082320406463e-09</v>
+        <v>3.4771370486667207e-09</v>
       </c>
       <c r="K30" s="0">
         <v>1</v>
@@ -8286,31 +8286,31 @@
         <v>769</v>
       </c>
       <c r="B31" s="0">
-        <v>0.91705560397319819</v>
+        <v>0.91705560400373709</v>
       </c>
       <c r="C31" s="0">
         <v>0.0023755154945054946</v>
       </c>
       <c r="D31" s="0">
-        <v>0.00011301039278857231</v>
+        <v>0.00011280787050183047</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>
       </c>
       <c r="F31" s="0">
-        <v>6.78240827399461e-05</v>
+        <v>6.8039077808335625e-05</v>
       </c>
       <c r="G31" s="0">
-        <v>7.3013080648752839e-07</v>
+        <v>7.2234102422037797e-07</v>
       </c>
       <c r="H31" s="0">
-        <v>5.3826622118745472e-05</v>
+        <v>5.2939010454762106e-05</v>
       </c>
       <c r="I31" s="0">
-        <v>-9.3773137103620566e-06</v>
+        <v>-8.8982104285044013e-06</v>
       </c>
       <c r="J31" s="0">
-        <v>6.8708337552699097e-09</v>
+        <v>5.651643016764296e-09</v>
       </c>
       <c r="K31" s="0">
         <v>0</v>
@@ -8330,31 +8330,31 @@
         <v>770</v>
       </c>
       <c r="B32" s="0">
-        <v>0.76611404182693987</v>
+        <v>0.76611404182759835</v>
       </c>
       <c r="C32" s="0">
         <v>0.013309501648351648</v>
       </c>
       <c r="D32" s="0">
-        <v>3.7255756329613957e-05</v>
+        <v>3.7494605903601357e-05</v>
       </c>
       <c r="E32" s="0">
-        <v>5.6876094731229577e-05</v>
+        <v>5.6876094738498522e-05</v>
       </c>
       <c r="F32" s="0">
-        <v>-2.6245046909735648e-05</v>
+        <v>-2.6394274128456444e-05</v>
       </c>
       <c r="G32" s="0">
-        <v>3.6835369094507101e-07</v>
+        <v>3.6446877739345368e-07</v>
       </c>
       <c r="H32" s="0">
-        <v>-6.744448214453664e-06</v>
+        <v>-6.9786734633724512e-06</v>
       </c>
       <c r="I32" s="0">
-        <v>1.299631229172043e-05</v>
+        <v>1.3622379157303215e-05</v>
       </c>
       <c r="J32" s="0">
-        <v>4.4907399081913629e-09</v>
+        <v>4.6108222350605402e-09</v>
       </c>
       <c r="K32" s="0">
         <v>1</v>
@@ -8374,31 +8374,31 @@
         <v>771</v>
       </c>
       <c r="B33" s="0">
-        <v>0.81210548499654189</v>
+        <v>0.81210548491603707</v>
       </c>
       <c r="C33" s="0">
         <v>0.00021664318681318683</v>
       </c>
       <c r="D33" s="0">
-        <v>8.9952340380483506e-05</v>
+        <v>9.0049862806076522e-05</v>
       </c>
       <c r="E33" s="0">
         <v>0</v>
       </c>
       <c r="F33" s="0">
-        <v>5.0433712893000095e-05</v>
+        <v>5.0385469414391356e-05</v>
       </c>
       <c r="G33" s="0">
-        <v>5.7048687355782065e-07</v>
+        <v>5.6265299819495659e-07</v>
       </c>
       <c r="H33" s="0">
-        <v>0.00011933508717787163</v>
+        <v>0.00011984934459353242</v>
       </c>
       <c r="I33" s="0">
-        <v>-8.0394712843159639e-05</v>
+        <v>-8.0755128665654772e-05</v>
       </c>
       <c r="J33" s="0">
-        <v>7.7662792136000284e-09</v>
+        <v>7.5244656125696228e-09</v>
       </c>
       <c r="K33" s="0">
         <v>0</v>
@@ -8418,31 +8418,31 @@
         <v>772</v>
       </c>
       <c r="B34" s="0">
-        <v>0.78938339089885556</v>
+        <v>0.78938339007987779</v>
       </c>
       <c r="C34" s="0">
         <v>0.00026451241758241754</v>
       </c>
       <c r="D34" s="0">
-        <v>0.00026060908963264318</v>
+        <v>0.00026040007411501413</v>
       </c>
       <c r="E34" s="0">
         <v>0</v>
       </c>
       <c r="F34" s="0">
-        <v>0.00015646326427980363</v>
+        <v>0.00015647969688402732</v>
       </c>
       <c r="G34" s="0">
-        <v>1.56475874309573e-06</v>
+        <v>1.5393797824758917e-06</v>
       </c>
       <c r="H34" s="0">
-        <v>0.00021656818910683291</v>
+        <v>0.00021694986065718376</v>
       </c>
       <c r="I34" s="0">
-        <v>-0.00011400075944832129</v>
+        <v>-0.00011458036679417705</v>
       </c>
       <c r="J34" s="0">
-        <v>1.363695123221076e-08</v>
+        <v>1.1503585504212877e-08</v>
       </c>
       <c r="K34" s="0">
         <v>0</v>
@@ -8462,31 +8462,31 @@
         <v>773</v>
       </c>
       <c r="B35" s="0">
-        <v>0.72881785879860883</v>
+        <v>0.7288178584438606</v>
       </c>
       <c r="C35" s="0">
-        <v>0.0032344040659340666</v>
+        <v>0.0036720769230769229</v>
       </c>
       <c r="D35" s="0">
-        <v>3.5759107428315302e-05</v>
+        <v>3.6020062679598617e-05</v>
       </c>
       <c r="E35" s="0">
-        <v>8.4520767128244727e-05</v>
+        <v>8.4520767161502588e-05</v>
       </c>
       <c r="F35" s="0">
-        <v>-5.0700407670827623e-05</v>
+        <v>-5.0978087508477582e-05</v>
       </c>
       <c r="G35" s="0">
-        <v>3.7907892015237157e-07</v>
+        <v>3.7397440568301539e-07</v>
       </c>
       <c r="H35" s="0">
-        <v>-9.5255416162218149e-06</v>
+        <v>-9.2404087563369155e-06</v>
       </c>
       <c r="I35" s="0">
-        <v>1.1078089625391454e-05</v>
+        <v>1.1336547495217244e-05</v>
       </c>
       <c r="J35" s="0">
-        <v>7.1210415761881185e-09</v>
+        <v>7.2698820102657551e-09</v>
       </c>
       <c r="K35" s="0">
         <v>1</v>
@@ -8506,31 +8506,31 @@
         <v>774</v>
       </c>
       <c r="B36" s="0">
-        <v>0.82119446195065471</v>
+        <v>0.82119446191327083</v>
       </c>
       <c r="C36" s="0">
         <v>0.0020271178021978027</v>
       </c>
       <c r="D36" s="0">
-        <v>6.1069099873045497e-05</v>
+        <v>6.0815310847445948e-05</v>
       </c>
       <c r="E36" s="0">
         <v>0</v>
       </c>
       <c r="F36" s="0">
-        <v>6.1055652107288216e-05</v>
+        <v>6.1206112047597515e-05</v>
       </c>
       <c r="G36" s="0">
-        <v>2.9455942568994941e-07</v>
+        <v>2.911144428137312e-07</v>
       </c>
       <c r="H36" s="0">
-        <v>6.3325827205186857e-05</v>
+        <v>6.2729944312527576e-05</v>
       </c>
       <c r="I36" s="0">
-        <v>-6.3608816806793079e-05</v>
+        <v>-6.3413498723845788e-05</v>
       </c>
       <c r="J36" s="0">
-        <v>1.8779416735591799e-09</v>
+        <v>1.6387683529113387e-09</v>
       </c>
       <c r="K36" s="0">
         <v>0</v>
@@ -8550,31 +8550,31 @@
         <v>775</v>
       </c>
       <c r="B37" s="0">
-        <v>0.81316977794823553</v>
+        <v>0.81316977808894941</v>
       </c>
       <c r="C37" s="0">
         <v>0.0069718854945054936</v>
       </c>
       <c r="D37" s="0">
-        <v>-1.262397077111091e-06</v>
+        <v>-1.2863194077375013e-06</v>
       </c>
       <c r="E37" s="0">
         <v>0</v>
       </c>
       <c r="F37" s="0">
-        <v>1.4017216425551509e-06</v>
+        <v>1.3956697850215562e-06</v>
       </c>
       <c r="G37" s="0">
-        <v>8.825784587149088e-08</v>
+        <v>8.7287068051975491e-08</v>
       </c>
       <c r="H37" s="0">
-        <v>-1.4791194655036398e-06</v>
+        <v>-1.473368026092277e-06</v>
       </c>
       <c r="I37" s="0">
-        <v>-1.2765441633991139e-06</v>
+        <v>-1.2992822399968541e-06</v>
       </c>
       <c r="J37" s="0">
-        <v>3.2870633650210253e-09</v>
+        <v>3.3740052780985778e-09</v>
       </c>
       <c r="K37" s="0">
         <v>0</v>
@@ -8594,31 +8594,31 @@
         <v>776</v>
       </c>
       <c r="B38" s="0">
-        <v>0.50886706745243537</v>
+        <v>0.50886706740239385</v>
       </c>
       <c r="C38" s="0">
         <v>0.0054763300000000023</v>
       </c>
       <c r="D38" s="0">
-        <v>6.8068354973429041e-05</v>
+        <v>6.7976843215538681e-05</v>
       </c>
       <c r="E38" s="0">
-        <v>0.00013362581415844163</v>
+        <v>0.00013362581434950394</v>
       </c>
       <c r="F38" s="0">
-        <v>-6.3408740582966195e-05</v>
+        <v>-6.3498255829573476e-05</v>
       </c>
       <c r="G38" s="0">
-        <v>9.9960982926472014e-07</v>
+        <v>9.8374089872849463e-07</v>
       </c>
       <c r="H38" s="0">
-        <v>3.0218298043125705e-06</v>
+        <v>2.7854214691189788e-06</v>
       </c>
       <c r="I38" s="0">
-        <v>-6.1803147196690828e-06</v>
+        <v>-5.9301792776459072e-06</v>
       </c>
       <c r="J38" s="0">
-        <v>1.0156484045400579e-08</v>
+        <v>1.0301605406654091e-08</v>
       </c>
       <c r="K38" s="0">
         <v>0</v>
@@ -8638,31 +8638,31 @@
         <v>777</v>
       </c>
       <c r="B39" s="0">
-        <v>0.89510413373288555</v>
+        <v>0.89510413362604568</v>
       </c>
       <c r="C39" s="0">
         <v>0.00085353087912087876</v>
       </c>
       <c r="D39" s="0">
-        <v>7.3282019034101722e-05</v>
+        <v>7.3042074922565015e-05</v>
       </c>
       <c r="E39" s="0">
         <v>0</v>
       </c>
       <c r="F39" s="0">
-        <v>5.118807639209603e-05</v>
+        <v>5.1313964251758424e-05</v>
       </c>
       <c r="G39" s="0">
-        <v>2.4051774418712266e-07</v>
+        <v>2.3611659819345337e-07</v>
       </c>
       <c r="H39" s="0">
-        <v>4.4048605806526304e-05</v>
+        <v>4.3580451370594634e-05</v>
       </c>
       <c r="I39" s="0">
-        <v>-2.2196480808785559e-05</v>
+        <v>-2.2089558406844481e-05</v>
       </c>
       <c r="J39" s="0">
-        <v>1.2999000778232163e-09</v>
+        <v>1.1011088629835032e-09</v>
       </c>
       <c r="K39" s="0">
         <v>0</v>
@@ -8682,31 +8682,31 @@
         <v>778</v>
       </c>
       <c r="B40" s="0">
-        <v>0.90975405657355435</v>
+        <v>0.90975405654482888</v>
       </c>
       <c r="C40" s="0">
         <v>0.00085380681318681306</v>
       </c>
       <c r="D40" s="0">
-        <v>3.550556595660506e-05</v>
+        <v>3.539605192807253e-05</v>
       </c>
       <c r="E40" s="0">
         <v>0</v>
       </c>
       <c r="F40" s="0">
-        <v>3.2728731326817541e-05</v>
+        <v>3.2806137687268892e-05</v>
       </c>
       <c r="G40" s="0">
-        <v>1.4397008820977529e-07</v>
+        <v>1.4124343056659046e-07</v>
       </c>
       <c r="H40" s="0">
-        <v>4.5235333680451512e-05</v>
+        <v>4.5205952846676627e-05</v>
       </c>
       <c r="I40" s="0">
-        <v>-4.2602735208022043e-05</v>
+        <v>-4.2757530409588447e-05</v>
       </c>
       <c r="J40" s="0">
-        <v>2.6606914827425167e-10</v>
+        <v>2.4837314887074524e-10</v>
       </c>
       <c r="K40" s="0">
         <v>0</v>
@@ -8726,31 +8726,31 @@
         <v>779</v>
       </c>
       <c r="B41" s="0">
-        <v>0.44492538831216377</v>
+        <v>0.44492538831376283</v>
       </c>
       <c r="C41" s="0">
         <v>0.014438330329670323</v>
       </c>
       <c r="D41" s="0">
-        <v>3.8527750270463878e-05</v>
+        <v>3.8632298501758493e-05</v>
       </c>
       <c r="E41" s="0">
-        <v>7.7541363087191696e-05</v>
+        <v>7.7541363004633319e-05</v>
       </c>
       <c r="F41" s="0">
-        <v>-4.4303052948389175e-05</v>
+        <v>-4.4524364354209356e-05</v>
       </c>
       <c r="G41" s="0">
-        <v>4.8764277894736406e-07</v>
+        <v>4.8232092456551362e-07</v>
       </c>
       <c r="H41" s="0">
-        <v>-5.7524231218247794e-06</v>
+        <v>-5.9594249188291648e-06</v>
       </c>
       <c r="I41" s="0">
-        <v>1.0550261194455396e-05</v>
+        <v>1.1088463849460179e-05</v>
       </c>
       <c r="J41" s="0">
-        <v>3.9592800833768138e-09</v>
+        <v>3.9399961380035903e-09</v>
       </c>
       <c r="K41" s="0">
         <v>1</v>
@@ -8770,31 +8770,31 @@
         <v>780</v>
       </c>
       <c r="B42" s="0">
-        <v>0.7810362480761236</v>
+        <v>0.78103624807029925</v>
       </c>
       <c r="C42" s="0">
         <v>0.024008800989010985</v>
       </c>
       <c r="D42" s="0">
-        <v>4.2247298113437321e-05</v>
+        <v>4.2491248200426781e-05</v>
       </c>
       <c r="E42" s="0">
-        <v>5.9699103720211536e-05</v>
+        <v>5.969910373525125e-05</v>
       </c>
       <c r="F42" s="0">
-        <v>-2.3757817304633717e-05</v>
+        <v>-2.3868042549100276e-05</v>
       </c>
       <c r="G42" s="0">
-        <v>3.5297754820398891e-07</v>
+        <v>3.4909343233271049e-07</v>
       </c>
       <c r="H42" s="0">
-        <v>-7.4604986884441573e-06</v>
+        <v>-7.7534740456706071e-06</v>
       </c>
       <c r="I42" s="0">
-        <v>1.3408792542431279e-05</v>
+        <v>1.4059697261255368e-05</v>
       </c>
       <c r="J42" s="0">
-        <v>4.7402956683914615e-09</v>
+        <v>4.870366358336462e-09</v>
       </c>
       <c r="K42" s="0">
         <v>1</v>
@@ -8814,31 +8814,31 @@
         <v>781</v>
       </c>
       <c r="B43" s="0">
-        <v>0.80091288434131924</v>
+        <v>0.80091288431717012</v>
       </c>
       <c r="C43" s="0">
         <v>0.0032003447252747256</v>
       </c>
       <c r="D43" s="0">
-        <v>1.8219952313767537e-05</v>
+        <v>1.8117377090170626e-05</v>
       </c>
       <c r="E43" s="0">
         <v>0</v>
       </c>
       <c r="F43" s="0">
-        <v>3.5393020181375808e-05</v>
+        <v>3.5570456832972248e-05</v>
       </c>
       <c r="G43" s="0">
-        <v>2.4229305606097409e-07</v>
+        <v>2.3972946837305556e-07</v>
       </c>
       <c r="H43" s="0">
-        <v>1.4225894880618648e-05</v>
+        <v>1.412290120033786e-05</v>
       </c>
       <c r="I43" s="0">
-        <v>-3.164480285972116e-05</v>
+        <v>-3.1819127754696621e-05</v>
       </c>
       <c r="J43" s="0">
-        <v>3.5470554332676886e-09</v>
+        <v>3.4173431840794867e-09</v>
       </c>
       <c r="K43" s="0">
         <v>0</v>
@@ -8858,31 +8858,31 @@
         <v>782</v>
       </c>
       <c r="B44" s="0">
-        <v>0.90903772064705446</v>
+        <v>0.90903772062833732</v>
       </c>
       <c r="C44" s="0">
         <v>0.0063659247252747251</v>
       </c>
       <c r="D44" s="0">
-        <v>4.9732533552479431e-05</v>
+        <v>5.0082331804465704e-05</v>
       </c>
       <c r="E44" s="0">
-        <v>6.6398648110830625e-05</v>
+        <v>6.6398648115475998e-05</v>
       </c>
       <c r="F44" s="0">
-        <v>-2.6382261383723679e-05</v>
+        <v>-2.6539535595315956e-05</v>
       </c>
       <c r="G44" s="0">
-        <v>5.2913969218809291e-07</v>
+        <v>5.2431138575243579e-07</v>
       </c>
       <c r="H44" s="0">
-        <v>-8.0546750490323869e-06</v>
+        <v>-8.3304923923508136e-06</v>
       </c>
       <c r="I44" s="0">
-        <v>1.7237047490155547e-05</v>
+        <v>1.8024603625909862e-05</v>
       </c>
       <c r="J44" s="0">
-        <v>4.6346920612319945e-09</v>
+        <v>4.7966649941787816e-09</v>
       </c>
       <c r="K44" s="0">
         <v>1</v>
@@ -8902,31 +8902,31 @@
         <v>783</v>
       </c>
       <c r="B45" s="0">
-        <v>0.7750744033095478</v>
+        <v>0.77507440361489521</v>
       </c>
       <c r="C45" s="0">
         <v>0.003136649120879121</v>
       </c>
       <c r="D45" s="0">
-        <v>6.85545288729595e-05</v>
+        <v>6.8256446246540186e-05</v>
       </c>
       <c r="E45" s="0">
         <v>0</v>
       </c>
       <c r="F45" s="0">
-        <v>7.1655870679355685e-05</v>
+        <v>7.176239141250547e-05</v>
       </c>
       <c r="G45" s="0">
-        <v>3.9615343126111523e-07</v>
+        <v>3.9085393790174198e-07</v>
       </c>
       <c r="H45" s="0">
-        <v>6.252553962350616e-05</v>
+        <v>6.1925160383532668e-05</v>
       </c>
       <c r="I45" s="0">
-        <v>-6.6027072942318455e-05</v>
+        <v>-6.5825487221390051e-05</v>
       </c>
       <c r="J45" s="0">
-        <v>4.0380811549916261e-09</v>
+        <v>3.5277339903574479e-09</v>
       </c>
       <c r="K45" s="0">
         <v>0</v>
@@ -8946,31 +8946,31 @@
         <v>784</v>
       </c>
       <c r="B46" s="0">
-        <v>0.7446650776949254</v>
+        <v>0.74466507764501477</v>
       </c>
       <c r="C46" s="0">
         <v>0.00077207417582417627</v>
       </c>
       <c r="D46" s="0">
-        <v>4.9683480528731232e-05</v>
+        <v>4.9728183957391768e-05</v>
       </c>
       <c r="E46" s="0">
         <v>0</v>
       </c>
       <c r="F46" s="0">
-        <v>3.558250158143921e-05</v>
+        <v>3.5566731389948467e-05</v>
       </c>
       <c r="G46" s="0">
-        <v>6.6695224602391144e-07</v>
+        <v>6.5838450034942366e-07</v>
       </c>
       <c r="H46" s="0">
-        <v>4.1257060085795946e-05</v>
+        <v>4.1129741898401869e-05</v>
       </c>
       <c r="I46" s="0">
-        <v>-2.7835989972120224e-05</v>
+        <v>-2.763975520590885e-05</v>
       </c>
       <c r="J46" s="0">
-        <v>1.2956587592387618e-08</v>
+        <v>1.3081374600855861e-08</v>
       </c>
       <c r="K46" s="0">
         <v>0</v>
@@ -8990,31 +8990,31 @@
         <v>785</v>
       </c>
       <c r="B47" s="0">
-        <v>0.86309745266608595</v>
+        <v>0.86309745266543925</v>
       </c>
       <c r="C47" s="0">
         <v>0.0020190452747252739</v>
       </c>
       <c r="D47" s="0">
-        <v>2.6437091857588926e-05</v>
+        <v>2.6282251413095834e-05</v>
       </c>
       <c r="E47" s="0">
         <v>0</v>
       </c>
       <c r="F47" s="0">
-        <v>2.6452868149972155e-05</v>
+        <v>2.6508366505578851e-05</v>
       </c>
       <c r="G47" s="0">
-        <v>3.0267380224120653e-07</v>
+        <v>2.9989400350567987e-07</v>
       </c>
       <c r="H47" s="0">
-        <v>3.1118230557865635e-05</v>
+        <v>3.0654355204379109e-05</v>
       </c>
       <c r="I47" s="0">
-        <v>-3.1439167796744728e-05</v>
+        <v>-3.1182582929229268e-05</v>
       </c>
       <c r="J47" s="0">
-        <v>2.4871442546608069e-09</v>
+        <v>2.2186288614655172e-09</v>
       </c>
       <c r="K47" s="0">
         <v>0</v>
@@ -9034,31 +9034,31 @@
         <v>786</v>
       </c>
       <c r="B48" s="0">
-        <v>0.83203566382320415</v>
+        <v>0.83203566378564087</v>
       </c>
       <c r="C48" s="0">
         <v>0.0070545008791208785</v>
       </c>
       <c r="D48" s="0">
-        <v>1.2028124190170616e-05</v>
+        <v>1.175976712577472e-05</v>
       </c>
       <c r="E48" s="0">
-        <v>1.2360467702452213e-06</v>
+        <v>1.23604676137642e-06</v>
       </c>
       <c r="F48" s="0">
-        <v>1.9867817886291176e-05</v>
+        <v>2.0125419804961011e-05</v>
       </c>
       <c r="G48" s="0">
-        <v>1.3782292790735231e-07</v>
+        <v>1.3600273273897363e-07</v>
       </c>
       <c r="H48" s="0">
-        <v>-4.3360046181414241e-06</v>
+        <v>-4.4878111002374696e-06</v>
       </c>
       <c r="I48" s="0">
-        <v>-4.8825256122097054e-06</v>
+        <v>-5.2547619986710835e-06</v>
       </c>
       <c r="J48" s="0">
-        <v>4.9668360779959929e-09</v>
+        <v>4.8709256068686502e-09</v>
       </c>
       <c r="K48" s="0">
         <v>1</v>
@@ -9078,31 +9078,31 @@
         <v>787</v>
       </c>
       <c r="B49" s="0">
-        <v>0.90455694835793987</v>
+        <v>0.90455694697840028</v>
       </c>
       <c r="C49" s="0">
         <v>0.0029544837362637352</v>
       </c>
       <c r="D49" s="0">
-        <v>3.8490355730651627e-05</v>
+        <v>3.8475168908206086e-05</v>
       </c>
       <c r="E49" s="0">
         <v>0</v>
       </c>
       <c r="F49" s="0">
-        <v>1.3168741589086961e-05</v>
+        <v>1.3224500766075732e-05</v>
       </c>
       <c r="G49" s="0">
-        <v>1.7614463394967641e-07</v>
+        <v>1.7459330344042195e-07</v>
       </c>
       <c r="H49" s="0">
-        <v>2.1744490591026395e-05</v>
+        <v>2.1452421733058754e-05</v>
       </c>
       <c r="I49" s="0">
-        <v>3.4005470968932323e-06</v>
+        <v>3.6232270789268252e-06</v>
       </c>
       <c r="J49" s="0">
-        <v>4.3181969536359039e-10</v>
+        <v>4.2602670435172463e-10</v>
       </c>
       <c r="K49" s="0">
         <v>0</v>
@@ -9122,31 +9122,31 @@
         <v>788</v>
       </c>
       <c r="B50" s="0">
-        <v>0.71137118377682762</v>
+        <v>0.71137118352994644</v>
       </c>
       <c r="C50" s="0">
         <v>0.0036961735164835192</v>
       </c>
       <c r="D50" s="0">
-        <v>2.7980472178139215e-05</v>
+        <v>2.7727872366312242e-05</v>
       </c>
       <c r="E50" s="0">
         <v>0</v>
       </c>
       <c r="F50" s="0">
-        <v>5.5709729598411388e-05</v>
+        <v>5.6015322629135957e-05</v>
       </c>
       <c r="G50" s="0">
-        <v>3.2545583897836339e-07</v>
+        <v>3.219610896450926e-07</v>
       </c>
       <c r="H50" s="0">
-        <v>2.6621014723215026e-05</v>
+        <v>2.6169555869926115e-05</v>
       </c>
       <c r="I50" s="0">
-        <v>-5.4680884468116909e-05</v>
+        <v>-5.4784065330872063e-05</v>
       </c>
       <c r="J50" s="0">
-        <v>5.1564856513454491e-09</v>
+        <v>5.0981084771434845e-09</v>
       </c>
       <c r="K50" s="0">
         <v>0</v>
@@ -9166,31 +9166,31 @@
         <v>789</v>
       </c>
       <c r="B51" s="0">
-        <v>0.84693045303058656</v>
+        <v>0.84693045321762972</v>
       </c>
       <c r="C51" s="0">
         <v>0.00097700439560439588</v>
       </c>
       <c r="D51" s="0">
-        <v>0.0001144548100909089</v>
+        <v>0.00011414698199818847</v>
       </c>
       <c r="E51" s="0">
         <v>0</v>
       </c>
       <c r="F51" s="0">
-        <v>7.8704328625448696e-05</v>
+        <v>7.876142279697713e-05</v>
       </c>
       <c r="G51" s="0">
-        <v>6.3530018479043527e-07</v>
+        <v>6.2644804529973241e-07</v>
       </c>
       <c r="H51" s="0">
-        <v>8.4648545717110762e-05</v>
+        <v>8.3982590028610642e-05</v>
       </c>
       <c r="I51" s="0">
-        <v>-4.9540625574943033e-05</v>
+        <v>-4.9229855463208429e-05</v>
       </c>
       <c r="J51" s="0">
-        <v>7.2611385020459294e-09</v>
+        <v>6.3765905093933852e-09</v>
       </c>
       <c r="K51" s="0">
         <v>0</v>
@@ -9210,31 +9210,31 @@
         <v>790</v>
       </c>
       <c r="B52" s="0">
-        <v>0.49467206477960474</v>
+        <v>0.4946720646314165</v>
       </c>
       <c r="C52" s="0">
         <v>0.0095371454945054959</v>
       </c>
       <c r="D52" s="0">
-        <v>0.00017878713292638875</v>
+        <v>0.00017869430412456447</v>
       </c>
       <c r="E52" s="0">
-        <v>0.00036468477100178899</v>
+        <v>0.00036468477097110114</v>
       </c>
       <c r="F52" s="0">
-        <v>-0.00016535599692042976</v>
+        <v>-0.00016549992584684691</v>
       </c>
       <c r="G52" s="0">
-        <v>1.9198035763594699e-06</v>
+        <v>1.8931196629861222e-06</v>
       </c>
       <c r="H52" s="0">
-        <v>7.6971134106596723e-06</v>
+        <v>7.3797501697676677e-06</v>
       </c>
       <c r="I52" s="0">
-        <v>-3.0170275313716253e-05</v>
+        <v>-2.9775357803512667e-05</v>
       </c>
       <c r="J52" s="0">
-        <v>1.1717171726628018e-08</v>
+        <v>1.1946971069129821e-08</v>
       </c>
       <c r="K52" s="0">
         <v>0</v>
@@ -9254,31 +9254,31 @@
         <v>791</v>
       </c>
       <c r="B53" s="0">
-        <v>0.72938748485475291</v>
+        <v>0.72938748481945315</v>
       </c>
       <c r="C53" s="0">
         <v>0.042665651648351621</v>
       </c>
       <c r="D53" s="0">
-        <v>2.5200734564300777e-06</v>
+        <v>2.4450223457933331e-06</v>
       </c>
       <c r="E53" s="0">
-        <v>4.730273530725303e-06</v>
+        <v>4.7302735307826861e-06</v>
       </c>
       <c r="F53" s="0">
-        <v>-5.6075904033353644e-07</v>
+        <v>-5.0234947178497617e-07</v>
       </c>
       <c r="G53" s="0">
-        <v>1.6129906075554994e-08</v>
+        <v>1.57773810400826e-08</v>
       </c>
       <c r="H53" s="0">
-        <v>-4.5714035040455653e-06</v>
+        <v>-4.7186247055205722e-06</v>
       </c>
       <c r="I53" s="0">
-        <v>2.9053099253447943e-06</v>
+        <v>2.9194084407458058e-06</v>
       </c>
       <c r="J53" s="0">
-        <v>5.2263866352706545e-10</v>
+        <v>5.3717053030676924e-10</v>
       </c>
       <c r="K53" s="0">
         <v>1</v>
@@ -9298,31 +9298,31 @@
         <v>792</v>
       </c>
       <c r="B54" s="0">
-        <v>0.67528287593361136</v>
+        <v>0.67528287597857872</v>
       </c>
       <c r="C54" s="0">
         <v>0.011126930109890108</v>
       </c>
       <c r="D54" s="0">
-        <v>6.6838626808963511e-05</v>
+        <v>6.6782599914594617e-05</v>
       </c>
       <c r="E54" s="0">
-        <v>0.0001287915728259045</v>
+        <v>0.00012879157283448081</v>
       </c>
       <c r="F54" s="0">
-        <v>-5.2738372851314068e-05</v>
+        <v>-5.2746335714642059e-05</v>
       </c>
       <c r="G54" s="0">
-        <v>8.1413536723993218e-07</v>
+        <v>8.0267738235097378e-07</v>
       </c>
       <c r="H54" s="0">
-        <v>3.0553033464702052e-06</v>
+        <v>2.8945174925465699e-06</v>
       </c>
       <c r="I54" s="0">
-        <v>-1.3094136191913252e-05</v>
+        <v>-1.2970183862995304e-05</v>
       </c>
       <c r="J54" s="0">
-        <v>1.0124312576191845e-08</v>
+        <v>1.0351782853623435e-08</v>
       </c>
       <c r="K54" s="0">
         <v>0</v>
@@ -9342,31 +9342,31 @@
         <v>793</v>
       </c>
       <c r="B55" s="0">
-        <v>0.82399881399324948</v>
+        <v>0.82399881515213313</v>
       </c>
       <c r="C55" s="0">
         <v>0.0021432036263736242</v>
       </c>
       <c r="D55" s="0">
-        <v>0.000103388948143635</v>
+        <v>0.00010275168349358293</v>
       </c>
       <c r="E55" s="0">
         <v>0</v>
       </c>
       <c r="F55" s="0">
-        <v>0.00011356333249958648</v>
+        <v>0.00011396245176242118</v>
       </c>
       <c r="G55" s="0">
-        <v>5.9543364026216559e-07</v>
+        <v>5.8578100934573302e-07</v>
       </c>
       <c r="H55" s="0">
-        <v>5.2867395765743386e-05</v>
+        <v>5.1703563734194467e-05</v>
       </c>
       <c r="I55" s="0">
-        <v>-6.3639074827176795e-05</v>
+        <v>-6.3501780456015326e-05</v>
       </c>
       <c r="J55" s="0">
-        <v>1.8610652197521534e-09</v>
+        <v>1.6674436368739913e-09</v>
       </c>
       <c r="K55" s="0">
         <v>0</v>
@@ -9386,31 +9386,31 @@
         <v>794</v>
       </c>
       <c r="B56" s="0">
-        <v>0.86070956564543077</v>
+        <v>0.86070956641605478</v>
       </c>
       <c r="C56" s="0">
         <v>0.0025875605494505485</v>
       </c>
       <c r="D56" s="0">
-        <v>0.00010586733173520889</v>
+        <v>0.00010549891457377787</v>
       </c>
       <c r="E56" s="0">
         <v>0</v>
       </c>
       <c r="F56" s="0">
-        <v>7.8174799205447983e-05</v>
+        <v>7.8327111487871124e-05</v>
       </c>
       <c r="G56" s="0">
-        <v>8.8226974923704054e-07</v>
+        <v>8.7301672403090171e-07</v>
       </c>
       <c r="H56" s="0">
-        <v>5.8126509870451868e-05</v>
+        <v>5.6973791076026779e-05</v>
       </c>
       <c r="I56" s="0">
-        <v>-3.1323096494787839e-05</v>
+        <v>-3.0680787522535334e-05</v>
       </c>
       <c r="J56" s="0">
-        <v>6.8494048598432026e-09</v>
+        <v>5.782808384402515e-09</v>
       </c>
       <c r="K56" s="0">
         <v>0</v>
@@ -9430,31 +9430,31 @@
         <v>795</v>
       </c>
       <c r="B57" s="0">
-        <v>0.69541698665151885</v>
+        <v>0.69541698652824135</v>
       </c>
       <c r="C57" s="0">
         <v>0.000901488571428571</v>
       </c>
       <c r="D57" s="0">
-        <v>3.7033237555875629e-05</v>
+        <v>3.6930537630679275e-05</v>
       </c>
       <c r="E57" s="0">
         <v>0</v>
       </c>
       <c r="F57" s="0">
-        <v>4.2080071343478004e-05</v>
+        <v>4.2151489061583559e-05</v>
       </c>
       <c r="G57" s="0">
-        <v>2.3144641781695666e-07</v>
+        <v>2.2887518541440078e-07</v>
       </c>
       <c r="H57" s="0">
-        <v>4.812624113418746e-05</v>
+        <v>4.854803893933137e-05</v>
       </c>
       <c r="I57" s="0">
-        <v>-5.3406271486392046e-05</v>
+        <v>-5.3999631505226254e-05</v>
       </c>
       <c r="J57" s="0">
-        <v>1.7501467852536721e-09</v>
+        <v>1.7659495762006915e-09</v>
       </c>
       <c r="K57" s="0">
         <v>0</v>
@@ -9474,31 +9474,31 @@
         <v>796</v>
       </c>
       <c r="B58" s="0">
-        <v>0.7353386346117512</v>
+        <v>0.73533863539090405</v>
       </c>
       <c r="C58" s="0">
         <v>0.0019742773626373628</v>
       </c>
       <c r="D58" s="0">
-        <v>-3.6663734796905108e-07</v>
+        <v>-3.2694836753647129e-07</v>
       </c>
       <c r="E58" s="0">
         <v>0</v>
       </c>
       <c r="F58" s="0">
-        <v>-4.06539921057478e-06</v>
+        <v>-4.1803895613338991e-06</v>
       </c>
       <c r="G58" s="0">
-        <v>2.4099145936425502e-07</v>
+        <v>2.3609119440106421e-07</v>
       </c>
       <c r="H58" s="0">
-        <v>1.3135584521843051e-05</v>
+        <v>1.3433430792913439e-05</v>
       </c>
       <c r="I58" s="0">
-        <v>-9.6957926755617228e-06</v>
+        <v>-9.8345160000007531e-06</v>
       </c>
       <c r="J58" s="0">
-        <v>1.7978556960145101e-08</v>
+        <v>1.843520648367839e-08</v>
       </c>
       <c r="K58" s="0">
         <v>0</v>
@@ -9518,31 +9518,31 @@
         <v>797</v>
       </c>
       <c r="B59" s="0">
-        <v>0.90477592581094413</v>
+        <v>0.90477592597111112</v>
       </c>
       <c r="C59" s="0">
         <v>0.00093552098901098846</v>
       </c>
       <c r="D59" s="0">
-        <v>1.6426555834807307e-05</v>
+        <v>1.6423913171493905e-05</v>
       </c>
       <c r="E59" s="0">
         <v>0</v>
       </c>
       <c r="F59" s="0">
-        <v>1.4946447014374124e-05</v>
+        <v>1.4950167180442937e-05</v>
       </c>
       <c r="G59" s="0">
-        <v>2.7517958619305965e-07</v>
+        <v>2.720869118487328e-07</v>
       </c>
       <c r="H59" s="0">
-        <v>3.1763384363108833e-05</v>
+        <v>3.1834352402791519e-05</v>
       </c>
       <c r="I59" s="0">
-        <v>-3.0562327530718764e-05</v>
+        <v>-3.0636398116450257e-05</v>
       </c>
       <c r="J59" s="0">
-        <v>3.8724018500537003e-09</v>
+        <v>3.7047928609743475e-09</v>
       </c>
       <c r="K59" s="0">
         <v>0</v>
@@ -9562,31 +9562,31 @@
         <v>798</v>
       </c>
       <c r="B60" s="0">
-        <v>0.5924146013925119</v>
+        <v>0.5924146020926212</v>
       </c>
       <c r="C60" s="0">
         <v>0.0079997632967032974</v>
       </c>
       <c r="D60" s="0">
-        <v>6.6525274667072944e-05</v>
+        <v>6.6786489667788949e-05</v>
       </c>
       <c r="E60" s="0">
-        <v>7.6145747081994762e-05</v>
+        <v>7.6145747225165732e-05</v>
       </c>
       <c r="F60" s="0">
-        <v>-1.3771600979282185e-05</v>
+        <v>-1.371709743677589e-05</v>
       </c>
       <c r="G60" s="0">
-        <v>4.2582829875845756e-07</v>
+        <v>4.2082673267647063e-07</v>
       </c>
       <c r="H60" s="0">
-        <v>-1.1862854720441922e-05</v>
+        <v>-1.2210660309307164e-05</v>
       </c>
       <c r="I60" s="0">
-        <v>1.5585311898433744e-05</v>
+        <v>1.6144714229018576e-05</v>
       </c>
       <c r="J60" s="0">
-        <v>2.8430876100885222e-09</v>
+        <v>2.9592270112242683e-09</v>
       </c>
       <c r="K60" s="0">
         <v>1</v>
@@ -9606,31 +9606,31 @@
         <v>799</v>
       </c>
       <c r="B61" s="0">
-        <v>0.6326412571748784</v>
+        <v>0.63264125648709901</v>
       </c>
       <c r="C61" s="0">
         <v>0.0010330782417582412</v>
       </c>
       <c r="D61" s="0">
-        <v>0.00016959608775022882</v>
+        <v>0.00016906347218625936</v>
       </c>
       <c r="E61" s="0">
         <v>0</v>
       </c>
       <c r="F61" s="0">
-        <v>0.00015156624528610236</v>
+        <v>0.00015157706692216851</v>
       </c>
       <c r="G61" s="0">
-        <v>1.1011666378164501e-06</v>
+        <v>1.0884437326695915e-06</v>
       </c>
       <c r="H61" s="0">
-        <v>0.00010539933679078818</v>
+        <v>0.000104392397882641</v>
       </c>
       <c r="I61" s="0">
-        <v>-8.8477612255247084e-05</v>
+        <v>-8.8000174048587769e-05</v>
       </c>
       <c r="J61" s="0">
-        <v>6.9512907689087827e-09</v>
+        <v>5.7376973680329114e-09</v>
       </c>
       <c r="K61" s="0">
         <v>0</v>
@@ -9650,31 +9650,31 @@
         <v>800</v>
       </c>
       <c r="B62" s="0">
-        <v>0.86580262765809413</v>
+        <v>0.86580262795585761</v>
       </c>
       <c r="C62" s="0">
         <v>0.00086934967032967052</v>
       </c>
       <c r="D62" s="0">
-        <v>7.4077713413884191e-05</v>
+        <v>7.407141132091887e-05</v>
       </c>
       <c r="E62" s="0">
         <v>0</v>
       </c>
       <c r="F62" s="0">
-        <v>3.8723918229214603e-05</v>
+        <v>3.8634139381390079e-05</v>
       </c>
       <c r="G62" s="0">
-        <v>3.1246259113305131e-07</v>
+        <v>3.0752816528960392e-07</v>
       </c>
       <c r="H62" s="0">
-        <v>0.00010364044819602362</v>
+        <v>0.00010378105258074288</v>
       </c>
       <c r="I62" s="0">
-        <v>-6.859993424040769e-05</v>
+        <v>-6.8652028527376715e-05</v>
       </c>
       <c r="J62" s="0">
-        <v>8.1863792060856734e-10</v>
+        <v>7.1972087302776561e-10</v>
       </c>
       <c r="K62" s="0">
         <v>0</v>
@@ -9694,31 +9694,31 @@
         <v>801</v>
       </c>
       <c r="B63" s="0">
-        <v>0.8595158467241002</v>
+        <v>0.85951584381059909</v>
       </c>
       <c r="C63" s="0">
         <v>0.00042814329670329667</v>
       </c>
       <c r="D63" s="0">
-        <v>9.1192261541237646e-05</v>
+        <v>9.117728831395329e-05</v>
       </c>
       <c r="E63" s="0">
         <v>0</v>
       </c>
       <c r="F63" s="0">
-        <v>5.738579892686975e-05</v>
+        <v>5.741833187740594e-05</v>
       </c>
       <c r="G63" s="0">
-        <v>7.3685077251649965e-07</v>
+        <v>7.271892211297993e-07</v>
       </c>
       <c r="H63" s="0">
-        <v>0.00010867953769316398</v>
+        <v>0.00010869180671279786</v>
       </c>
       <c r="I63" s="0">
-        <v>-7.5616239364141954e-05</v>
+        <v>-7.5665831900261773e-05</v>
       </c>
       <c r="J63" s="0">
-        <v>6.3135128293716116e-09</v>
+        <v>5.792402881454016e-09</v>
       </c>
       <c r="K63" s="0">
         <v>0</v>
@@ -9738,31 +9738,31 @@
         <v>802</v>
       </c>
       <c r="B64" s="0">
-        <v>0.81176465893378724</v>
+        <v>0.81176465883274429</v>
       </c>
       <c r="C64" s="0">
         <v>0.00080047703296703314</v>
       </c>
       <c r="D64" s="0">
-        <v>4.6120552638722977e-05</v>
+        <v>4.5956329603902174e-05</v>
       </c>
       <c r="E64" s="0">
         <v>0</v>
       </c>
       <c r="F64" s="0">
-        <v>4.4320773756856882e-05</v>
+        <v>4.4378044229077941e-05</v>
       </c>
       <c r="G64" s="0">
-        <v>2.6168064374062195e-07</v>
+        <v>2.5857541081299297e-07</v>
       </c>
       <c r="H64" s="0">
-        <v>6.557147089477116e-05</v>
+        <v>6.5234657540164996e-05</v>
       </c>
       <c r="I64" s="0">
-        <v>-6.4035941544762857e-05</v>
+        <v>-6.3917300081644475e-05</v>
       </c>
       <c r="J64" s="0">
-        <v>2.5688881171738714e-09</v>
+        <v>2.3525054907168374e-09</v>
       </c>
       <c r="K64" s="0">
         <v>0</v>
@@ -9782,31 +9782,31 @@
         <v>803</v>
       </c>
       <c r="B65" s="0">
-        <v>0.51366240636625837</v>
+        <v>0.513662406380895</v>
       </c>
       <c r="C65" s="0">
         <v>0.031474542747252747</v>
       </c>
       <c r="D65" s="0">
-        <v>9.0293784524114371e-05</v>
+        <v>9.0899453629030252e-05</v>
       </c>
       <c r="E65" s="0">
-        <v>0.00014371162889811439</v>
+        <v>0.00014371162870346985</v>
       </c>
       <c r="F65" s="0">
-        <v>-6.7173684862564611e-05</v>
+        <v>-6.7534194556606063e-05</v>
       </c>
       <c r="G65" s="0">
-        <v>7.796980226071179e-07</v>
+        <v>7.6972566329814833e-07</v>
       </c>
       <c r="H65" s="0">
-        <v>-6.9964991023761192e-06</v>
+        <v>-7.3124437465106742e-06</v>
       </c>
       <c r="I65" s="0">
-        <v>1.9961132352460217e-05</v>
+        <v>2.1253011159115784e-05</v>
       </c>
       <c r="J65" s="0">
-        <v>1.15092158733764e-08</v>
+        <v>1.1726406263205005e-08</v>
       </c>
       <c r="K65" s="0">
         <v>1</v>
@@ -9826,31 +9826,31 @@
         <v>804</v>
       </c>
       <c r="B66" s="0">
-        <v>0.73207782933897247</v>
+        <v>0.73207782910962793</v>
       </c>
       <c r="C66" s="0">
         <v>0.02713582912087913</v>
       </c>
       <c r="D66" s="0">
-        <v>2.2210678219478946e-05</v>
+        <v>2.2298055639560907e-05</v>
       </c>
       <c r="E66" s="0">
-        <v>4.6988642928115428e-05</v>
+        <v>4.698864291522957e-05</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.2329328758502879e-05</v>
+        <v>-2.2432407399796662e-05</v>
       </c>
       <c r="G66" s="0">
-        <v>2.888442641517632e-07</v>
+        <v>2.853609307212035e-07</v>
       </c>
       <c r="H66" s="0">
-        <v>-5.2699236424761606e-06</v>
+        <v>-5.4639594784632172e-06</v>
       </c>
       <c r="I66" s="0">
-        <v>2.5284518087570782e-06</v>
+        <v>2.9163494126036414e-06</v>
       </c>
       <c r="J66" s="0">
-        <v>3.9916194337169419e-09</v>
+        <v>4.0692592663716073e-09</v>
       </c>
       <c r="K66" s="0">
         <v>1</v>
@@ -9870,31 +9870,31 @@
         <v>805</v>
       </c>
       <c r="B67" s="0">
-        <v>0.89534124640643975</v>
+        <v>0.89534124680275695</v>
       </c>
       <c r="C67" s="0">
         <v>0.0013432845054945051</v>
       </c>
       <c r="D67" s="0">
-        <v>2.4584982933868946e-05</v>
+        <v>2.4562043273641245e-05</v>
       </c>
       <c r="E67" s="0">
         <v>0</v>
       </c>
       <c r="F67" s="0">
-        <v>1.5689465919927898e-05</v>
+        <v>1.5728158247471668e-05</v>
       </c>
       <c r="G67" s="0">
-        <v>2.4060340962878443e-07</v>
+        <v>2.3847239002881445e-07</v>
       </c>
       <c r="H67" s="0">
-        <v>1.3321141479581123e-05</v>
+        <v>1.3158831657958258e-05</v>
       </c>
       <c r="I67" s="0">
-        <v>-4.6681064868931144e-06</v>
+        <v>-4.5651459772225511e-06</v>
       </c>
       <c r="J67" s="0">
-        <v>1.8786116242543402e-09</v>
+        <v>1.7269554050562062e-09</v>
       </c>
       <c r="K67" s="0">
         <v>0</v>
@@ -9914,31 +9914,31 @@
         <v>806</v>
       </c>
       <c r="B68" s="0">
-        <v>0.85790778853671634</v>
+        <v>0.85790778857774874</v>
       </c>
       <c r="C68" s="0">
         <v>0.0087388856043956065</v>
       </c>
       <c r="D68" s="0">
-        <v>3.6737940584339206e-05</v>
+        <v>3.691478902599302e-05</v>
       </c>
       <c r="E68" s="0">
-        <v>4.7671099826719466e-05</v>
+        <v>4.7671099836999478e-05</v>
       </c>
       <c r="F68" s="0">
-        <v>-1.3581664693209266e-05</v>
+        <v>-1.3647848908637511e-05</v>
       </c>
       <c r="G68" s="0">
-        <v>2.9747006108328805e-07</v>
+        <v>2.937809606348907e-07</v>
       </c>
       <c r="H68" s="0">
-        <v>-7.8860671455874067e-06</v>
+        <v>-8.1275704019805995e-06</v>
       </c>
       <c r="I68" s="0">
-        <v>1.0232764357114426e-05</v>
+        <v>1.0720990704001794e-05</v>
       </c>
       <c r="J68" s="0">
-        <v>4.3381782186983014e-09</v>
+        <v>4.336834974966793e-09</v>
       </c>
       <c r="K68" s="0">
         <v>1</v>
@@ -9958,31 +9958,31 @@
         <v>807</v>
       </c>
       <c r="B69" s="0">
-        <v>0.95464010071692817</v>
+        <v>0.95464010084555717</v>
       </c>
       <c r="C69" s="0">
         <v>0.0028873060439560442</v>
       </c>
       <c r="D69" s="0">
-        <v>3.1846392696435455e-05</v>
+        <v>3.1724833808455965e-05</v>
       </c>
       <c r="E69" s="0">
         <v>0</v>
       </c>
       <c r="F69" s="0">
-        <v>2.3494678156731453e-05</v>
+        <v>2.3575953614650086e-05</v>
       </c>
       <c r="G69" s="0">
-        <v>1.6095606206932784e-07</v>
+        <v>1.5894863755009182e-07</v>
       </c>
       <c r="H69" s="0">
-        <v>1.7686365338829247e-05</v>
+        <v>1.7251107270270931e-05</v>
       </c>
       <c r="I69" s="0">
-        <v>-9.4972612521304136e-06</v>
+        <v>-9.2626093092502871e-06</v>
       </c>
       <c r="J69" s="0">
-        <v>1.6543909358403893e-09</v>
+        <v>1.4335952351428029e-09</v>
       </c>
       <c r="K69" s="0">
         <v>0</v>
@@ -10002,31 +10002,31 @@
         <v>808</v>
       </c>
       <c r="B70" s="0">
-        <v>0.89451288314659461</v>
+        <v>0.89451288332467105</v>
       </c>
       <c r="C70" s="0">
         <v>0.0016293460439560444</v>
       </c>
       <c r="D70" s="0">
-        <v>2.8258070596172621e-05</v>
+        <v>2.8141028448310517e-05</v>
       </c>
       <c r="E70" s="0">
         <v>0</v>
       </c>
       <c r="F70" s="0">
-        <v>2.8333840128154749e-05</v>
+        <v>2.8409136575264826e-05</v>
       </c>
       <c r="G70" s="0">
-        <v>1.7809366459189715e-07</v>
+        <v>1.7572084674217941e-07</v>
       </c>
       <c r="H70" s="0">
-        <v>3.173177833370286e-05</v>
+        <v>3.1601320007448265e-05</v>
       </c>
       <c r="I70" s="0">
-        <v>-3.1987016794051512e-05</v>
+        <v>-3.2046367740874784e-05</v>
       </c>
       <c r="J70" s="0">
-        <v>1.3752637746262931e-09</v>
+        <v>1.2187597300323443e-09</v>
       </c>
       <c r="K70" s="0">
         <v>0</v>
@@ -10046,31 +10046,31 @@
         <v>809</v>
       </c>
       <c r="B71" s="0">
-        <v>0.77033451438176059</v>
+        <v>0.77033451440743295</v>
       </c>
       <c r="C71" s="0">
         <v>0.0077156657142857131</v>
       </c>
       <c r="D71" s="0">
-        <v>2.6847813210105221e-05</v>
+        <v>2.6794538903181026e-05</v>
       </c>
       <c r="E71" s="0">
-        <v>6.4379166487608965e-05</v>
+        <v>6.4379166417257797e-05</v>
       </c>
       <c r="F71" s="0">
-        <v>-3.5816485443559622e-05</v>
+        <v>-3.5866533199250931e-05</v>
       </c>
       <c r="G71" s="0">
-        <v>4.8392393330564076e-07</v>
+        <v>4.7638836285600677e-07</v>
       </c>
       <c r="H71" s="0">
-        <v>2.3670540047077331e-06</v>
+        <v>2.2061294436320214e-06</v>
       </c>
       <c r="I71" s="0">
-        <v>-4.5697546499377154e-06</v>
+        <v>-4.4045889199883912e-06</v>
       </c>
       <c r="J71" s="0">
-        <v>3.9088779802195502e-09</v>
+        <v>3.9767986745238795e-09</v>
       </c>
       <c r="K71" s="0">
         <v>0</v>
@@ -10090,31 +10090,31 @@
         <v>810</v>
       </c>
       <c r="B72" s="0">
-        <v>0.73572122186635847</v>
+        <v>0.73572122196632761</v>
       </c>
       <c r="C72" s="0">
         <v>0.0086889267032967087</v>
       </c>
       <c r="D72" s="0">
-        <v>1.8573520578446219e-05</v>
+        <v>1.8601847501628684e-05</v>
       </c>
       <c r="E72" s="0">
-        <v>3.0217815680652784e-05</v>
+        <v>3.0217815711520617e-05</v>
       </c>
       <c r="F72" s="0">
-        <v>-1.1668822983030527e-05</v>
+        <v>-1.1671075499463122e-05</v>
       </c>
       <c r="G72" s="0">
-        <v>1.450445311969367e-07</v>
+        <v>1.4297752049730559e-07</v>
       </c>
       <c r="H72" s="0">
-        <v>-5.8389486174560491e-06</v>
+        <v>-6.028307855680002e-06</v>
       </c>
       <c r="I72" s="0">
-        <v>5.7159245723461209e-06</v>
+        <v>5.9378690038237817e-06</v>
       </c>
       <c r="J72" s="0">
-        <v>2.5073947369524499e-09</v>
+        <v>2.5686209301038765e-09</v>
       </c>
       <c r="K72" s="0">
         <v>1</v>
@@ -10134,31 +10134,31 @@
         <v>811</v>
       </c>
       <c r="B73" s="0">
-        <v>0.92181455249908772</v>
+        <v>0.92181455249366417</v>
       </c>
       <c r="C73" s="0">
         <v>0.0018244775824175833</v>
       </c>
       <c r="D73" s="0">
-        <v>3.2618213812691861e-05</v>
+        <v>3.2571627830659006e-05</v>
       </c>
       <c r="E73" s="0">
         <v>0</v>
       </c>
       <c r="F73" s="0">
-        <v>1.811800740466412e-05</v>
+        <v>1.8180998362676918e-05</v>
       </c>
       <c r="G73" s="0">
-        <v>1.7770982331573713e-07</v>
+        <v>1.7602683535291474e-07</v>
       </c>
       <c r="H73" s="0">
-        <v>2.079552928252188e-05</v>
+        <v>2.0523540092555758e-05</v>
       </c>
       <c r="I73" s="0">
-        <v>-6.47456516962715e-06</v>
+        <v>-6.3102490645556005e-06</v>
       </c>
       <c r="J73" s="0">
-        <v>1.5324718172746198e-09</v>
+        <v>1.3116046290164587e-09</v>
       </c>
       <c r="K73" s="0">
         <v>0</v>
@@ -10178,31 +10178,31 @@
         <v>812</v>
       </c>
       <c r="B74" s="0">
-        <v>0.73423441253282196</v>
+        <v>0.73423441261182676</v>
       </c>
       <c r="C74" s="0">
         <v>0.0044086571428571452</v>
       </c>
       <c r="D74" s="0">
-        <v>4.0917673408688209e-05</v>
+        <v>4.0857428616815846e-05</v>
       </c>
       <c r="E74" s="0">
-        <v>9.7740847544907652e-05</v>
+        <v>9.7740846482694373e-05</v>
       </c>
       <c r="F74" s="0">
-        <v>-5.1404270661395488e-05</v>
+        <v>-5.1455745070279387e-05</v>
       </c>
       <c r="G74" s="0">
-        <v>6.8348593946136119e-07</v>
+        <v>6.7351798625249789e-07</v>
       </c>
       <c r="H74" s="0">
-        <v>5.2300437052116375e-06</v>
+        <v>5.0890212438089656e-06</v>
       </c>
       <c r="I74" s="0">
-        <v>-1.1338289510642592e-05</v>
+        <v>-1.1196164240331336e-05</v>
       </c>
       <c r="J74" s="0">
-        <v>5.8563911456398096e-09</v>
+        <v>5.9522146707307764e-09</v>
       </c>
       <c r="K74" s="0">
         <v>0</v>
@@ -10222,31 +10222,31 @@
         <v>813</v>
       </c>
       <c r="B75" s="0">
-        <v>0.92231284420417559</v>
+        <v>0.92231284426437354</v>
       </c>
       <c r="C75" s="0">
         <v>0.0026681046153846167</v>
       </c>
       <c r="D75" s="0">
-        <v>7.1541375252463189e-05</v>
+        <v>7.1262385636083772e-05</v>
       </c>
       <c r="E75" s="0">
         <v>0</v>
       </c>
       <c r="F75" s="0">
-        <v>5.277285863887112e-05</v>
+        <v>5.2888458506660196e-05</v>
       </c>
       <c r="G75" s="0">
-        <v>3.9623589947749747e-07</v>
+        <v>3.9050918094799463e-07</v>
       </c>
       <c r="H75" s="0">
-        <v>1.7946200550783385e-05</v>
+        <v>1.746849385234044e-05</v>
       </c>
       <c r="I75" s="0">
-        <v>4.2599867961370857e-07</v>
+        <v>5.1489371554170934e-07</v>
       </c>
       <c r="J75" s="0">
-        <v>8.1483717477263781e-11</v>
+        <v>3.0380593433171768e-11</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
@@ -10266,31 +10266,31 @@
         <v>814</v>
       </c>
       <c r="B76" s="0">
-        <v>0.84619531662321068</v>
+        <v>0.84619531649712187</v>
       </c>
       <c r="C76" s="0">
         <v>0.00020541626373626369</v>
       </c>
       <c r="D76" s="0">
-        <v>1.005953629018491e-05</v>
+        <v>1.0114297341952147e-05</v>
       </c>
       <c r="E76" s="0">
         <v>0</v>
       </c>
       <c r="F76" s="0">
-        <v>3.7164347555878177e-06</v>
+        <v>3.5839216190300268e-06</v>
       </c>
       <c r="G76" s="0">
-        <v>1.7312912383737871e-07</v>
+        <v>1.7050359855926123e-07</v>
       </c>
       <c r="H76" s="0">
-        <v>3.7214406238295641e-05</v>
+        <v>3.7460308841439324e-05</v>
       </c>
       <c r="I76" s="0">
-        <v>-3.1047672697552565e-05</v>
+        <v>-3.1103673871188875e-05</v>
       </c>
       <c r="J76" s="0">
-        <v>3.2388700166348784e-09</v>
+        <v>3.2371541124081747e-09</v>
       </c>
       <c r="K76" s="0">
         <v>0</v>
@@ -10310,31 +10310,31 @@
         <v>815</v>
       </c>
       <c r="B77" s="0">
-        <v>0.85670698494413822</v>
+        <v>0.85670698539497991</v>
       </c>
       <c r="C77" s="0">
         <v>0.0016430985714285722</v>
       </c>
       <c r="D77" s="0">
-        <v>7.81027332344626e-05</v>
+        <v>7.7815053734453383e-05</v>
       </c>
       <c r="E77" s="0">
         <v>0</v>
       </c>
       <c r="F77" s="0">
-        <v>7.5732444788575694e-05</v>
+        <v>7.5908957145121332e-05</v>
       </c>
       <c r="G77" s="0">
-        <v>5.1406648671818469e-07</v>
+        <v>5.0733597740616506e-07</v>
       </c>
       <c r="H77" s="0">
-        <v>6.1532671166040747e-05</v>
+        <v>6.0831758213480235e-05</v>
       </c>
       <c r="I77" s="0">
-        <v>-5.9681541093294018e-05</v>
+        <v>-5.9437344844639599e-05</v>
       </c>
       <c r="J77" s="0">
-        <v>5.0918864219915631e-09</v>
+        <v>4.3472430852467331e-09</v>
       </c>
       <c r="K77" s="0">
         <v>0</v>
@@ -10354,31 +10354,31 @@
         <v>816</v>
       </c>
       <c r="B78" s="0">
-        <v>0.69782870911019923</v>
+        <v>0.69782870947831466</v>
       </c>
       <c r="C78" s="0">
         <v>0.0025547289010989008</v>
       </c>
       <c r="D78" s="0">
-        <v>3.4242060308439566e-05</v>
+        <v>3.3958558781795292e-05</v>
       </c>
       <c r="E78" s="0">
         <v>0</v>
       </c>
       <c r="F78" s="0">
-        <v>5.830768862123326e-05</v>
+        <v>5.8454168255362598e-05</v>
       </c>
       <c r="G78" s="0">
-        <v>3.7613020865723079e-07</v>
+        <v>3.7195954866675713e-07</v>
       </c>
       <c r="H78" s="0">
-        <v>4.89422932478504e-05</v>
+        <v>4.8426307696167401e-05</v>
       </c>
       <c r="I78" s="0">
-        <v>-7.3389794427601433e-05</v>
+        <v>-7.3299408987737805e-05</v>
       </c>
       <c r="J78" s="0">
-        <v>5.742658300102242e-09</v>
+        <v>5.5322693363375622e-09</v>
       </c>
       <c r="K78" s="0">
         <v>0</v>
@@ -10398,31 +10398,31 @@
         <v>817</v>
       </c>
       <c r="B79" s="0">
-        <v>0.52873362439085847</v>
+        <v>0.52873362436339544</v>
       </c>
       <c r="C79" s="0">
         <v>0.022898872857142857</v>
       </c>
       <c r="D79" s="0">
-        <v>7.6179629504201062e-05</v>
+        <v>7.604679147105197e-05</v>
       </c>
       <c r="E79" s="0">
-        <v>0.00020412115983555821</v>
+        <v>0.00020412115983708975</v>
       </c>
       <c r="F79" s="0">
-        <v>-0.00011929861943433634</v>
+        <v>-0.00011944818699451777</v>
       </c>
       <c r="G79" s="0">
-        <v>1.1209041326369784e-06</v>
+        <v>1.1036000920553708e-06</v>
       </c>
       <c r="H79" s="0">
-        <v>8.2406638562416194e-06</v>
+        <v>7.8967300047613862e-06</v>
       </c>
       <c r="I79" s="0">
-        <v>-1.8016933457667918e-05</v>
+        <v>-1.7639197383550607e-05</v>
       </c>
       <c r="J79" s="0">
-        <v>1.245457176852818e-08</v>
+        <v>1.2685915213837433e-08</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
@@ -10442,31 +10442,31 @@
         <v>818</v>
       </c>
       <c r="B80" s="0">
-        <v>0.6011653774154383</v>
+        <v>0.60116537740370646</v>
       </c>
       <c r="C80" s="0">
         <v>0.014392112197802193</v>
       </c>
       <c r="D80" s="0">
-        <v>2.6901026456231989e-05</v>
+        <v>2.6958217068215001e-05</v>
       </c>
       <c r="E80" s="0">
-        <v>5.5270698998745419e-05</v>
+        <v>5.5270698968437008e-05</v>
       </c>
       <c r="F80" s="0">
-        <v>-2.6512059433525348e-05</v>
+        <v>-2.6608823447400971e-05</v>
       </c>
       <c r="G80" s="0">
-        <v>2.7140526184847119e-07</v>
+        <v>2.6791277200703214e-07</v>
       </c>
       <c r="H80" s="0">
-        <v>-6.1164074905926447e-06</v>
+        <v>-6.3414944964665183e-06</v>
       </c>
       <c r="I80" s="0">
-        <v>3.9846498837209095e-06</v>
+        <v>4.3671154865847591e-06</v>
       </c>
       <c r="J80" s="0">
-        <v>2.7392360351828019e-09</v>
+        <v>2.8077850536908463e-09</v>
       </c>
       <c r="K80" s="0">
         <v>1</v>
@@ -10486,31 +10486,31 @@
         <v>819</v>
       </c>
       <c r="B81" s="0">
-        <v>0.65996554817703512</v>
+        <v>0.65996554819550346</v>
       </c>
       <c r="C81" s="0">
         <v>0.02460239230769231</v>
       </c>
       <c r="D81" s="0">
-        <v>3.5876094479627999e-05</v>
+        <v>3.5990600036064773e-05</v>
       </c>
       <c r="E81" s="0">
-        <v>3.3125075013744299e-05</v>
+        <v>3.312507502910821e-05</v>
       </c>
       <c r="F81" s="0">
-        <v>-1.3068116358433669e-06</v>
+        <v>-1.2748381559743899e-06</v>
       </c>
       <c r="G81" s="0">
-        <v>2.0402715225749079e-07</v>
+        <v>2.0183699655671701e-07</v>
       </c>
       <c r="H81" s="0">
-        <v>-8.7600143695104296e-06</v>
+        <v>-9.059967099711854e-06</v>
       </c>
       <c r="I81" s="0">
-        <v>1.2611000478313722e-05</v>
+        <v>1.299561078034419e-05</v>
       </c>
       <c r="J81" s="0">
-        <v>2.8178406662825959e-09</v>
+        <v>2.8824857418995335e-09</v>
       </c>
       <c r="K81" s="0">
         <v>1</v>
@@ -10530,31 +10530,31 @@
         <v>820</v>
       </c>
       <c r="B82" s="0">
-        <v>0.6564328276626773</v>
+        <v>0.65643281439591683</v>
       </c>
       <c r="C82" s="0">
         <v>0.0010859034065934066</v>
       </c>
       <c r="D82" s="0">
-        <v>4.4657521099692107e-05</v>
+        <v>4.4409750241515459e-05</v>
       </c>
       <c r="E82" s="0">
         <v>0</v>
       </c>
       <c r="F82" s="0">
-        <v>5.5991968219524087e-05</v>
+        <v>5.5997645855619324e-05</v>
       </c>
       <c r="G82" s="0">
-        <v>8.4355247531087884e-08</v>
+        <v>8.246817942069667e-08</v>
       </c>
       <c r="H82" s="0">
-        <v>8.998875728847106e-05</v>
+        <v>9.0219287913320204e-05</v>
       </c>
       <c r="I82" s="0">
-        <v>-0.00010140989569153486</v>
+        <v>-0.00010189202716937164</v>
       </c>
       <c r="J82" s="0">
-        <v>2.3360357007346042e-09</v>
+        <v>2.3754625268776822e-09</v>
       </c>
       <c r="K82" s="0">
         <v>0</v>
@@ -10574,31 +10574,31 @@
         <v>821</v>
       </c>
       <c r="B83" s="0">
-        <v>0.82966745179053092</v>
+        <v>0.82966745177947376</v>
       </c>
       <c r="C83" s="0">
         <v>0.0012608371428571427</v>
       </c>
       <c r="D83" s="0">
-        <v>6.2218930111475448e-05</v>
+        <v>6.1913334639215984e-05</v>
       </c>
       <c r="E83" s="0">
         <v>0</v>
       </c>
       <c r="F83" s="0">
-        <v>6.3845947164970325e-05</v>
+        <v>6.4029614952876727e-05</v>
       </c>
       <c r="G83" s="0">
-        <v>2.6359808880274398e-07</v>
+        <v>2.5894986786707763e-07</v>
       </c>
       <c r="H83" s="0">
-        <v>5.0179158437234207e-05</v>
+        <v>4.976685635841062e-05</v>
       </c>
       <c r="I83" s="0">
-        <v>-5.2070786147236991e-05</v>
+        <v>-5.2142989731385698e-05</v>
       </c>
       <c r="J83" s="0">
-        <v>1.012567705165968e-09</v>
+        <v>9.0319144725763871e-10</v>
       </c>
       <c r="K83" s="0">
         <v>0</v>
@@ -10618,31 +10618,31 @@
         <v>822</v>
       </c>
       <c r="B84" s="0">
-        <v>0.63129349229229825</v>
+        <v>0.63129349251822553</v>
       </c>
       <c r="C84" s="0">
         <v>0.0042829491208791195</v>
       </c>
       <c r="D84" s="0">
-        <v>-3.3492089978913376e-05</v>
+        <v>-3.3733619116666934e-05</v>
       </c>
       <c r="E84" s="0">
         <v>0</v>
       </c>
       <c r="F84" s="0">
-        <v>7.5041589767920524e-07</v>
+        <v>8.4915440385766844e-07</v>
       </c>
       <c r="G84" s="0">
-        <v>5.8350167277395151e-07</v>
+        <v>5.7961599194062216e-07</v>
       </c>
       <c r="H84" s="0">
-        <v>-1.0620220096394289e-05</v>
+        <v>-1.0508442004301791e-05</v>
       </c>
       <c r="I84" s="0">
-        <v>-2.4209057808810668e-05</v>
+        <v>-2.4657320142372127e-05</v>
       </c>
       <c r="J84" s="0">
-        <v>3.2703558384209179e-09</v>
+        <v>3.3726342086965128e-09</v>
       </c>
       <c r="K84" s="0">
         <v>0</v>
@@ -10662,31 +10662,31 @@
         <v>823</v>
       </c>
       <c r="B85" s="0">
-        <v>0.83165885430487985</v>
+        <v>0.83165885403716344</v>
       </c>
       <c r="C85" s="0">
         <v>0.0021703880219780219</v>
       </c>
       <c r="D85" s="0">
-        <v>-7.2867117048346613e-06</v>
+        <v>-7.4335046167103234e-06</v>
       </c>
       <c r="E85" s="0">
         <v>0</v>
       </c>
       <c r="F85" s="0">
-        <v>2.9500841706967887e-06</v>
+        <v>3.0404969934543226e-06</v>
       </c>
       <c r="G85" s="0">
-        <v>8.3130291717224355e-08</v>
+        <v>8.2649395109627733e-08</v>
       </c>
       <c r="H85" s="0">
-        <v>-7.466665996978273e-06</v>
+        <v>-7.3420507125797969e-06</v>
       </c>
       <c r="I85" s="0">
-        <v>-2.856529259039241e-06</v>
+        <v>-3.2179174630963403e-06</v>
       </c>
       <c r="J85" s="0">
-        <v>3.2690887688388122e-09</v>
+        <v>3.3171704018619279e-09</v>
       </c>
       <c r="K85" s="0">
         <v>1</v>
@@ -10706,31 +10706,31 @@
         <v>824</v>
       </c>
       <c r="B86" s="0">
-        <v>0.75541996285776414</v>
+        <v>0.75541996278938972</v>
       </c>
       <c r="C86" s="0">
         <v>0.00082946340659340641</v>
       </c>
       <c r="D86" s="0">
-        <v>4.4586664363145128e-05</v>
+        <v>4.4507130662079436e-05</v>
       </c>
       <c r="E86" s="0">
         <v>0</v>
       </c>
       <c r="F86" s="0">
-        <v>4.468643231770644e-05</v>
+        <v>4.463579354779549e-05</v>
       </c>
       <c r="G86" s="0">
-        <v>3.2403137741268604e-07</v>
+        <v>3.1978615681347346e-07</v>
       </c>
       <c r="H86" s="0">
-        <v>7.6765458176721187e-05</v>
+        <v>7.6802018409641366e-05</v>
       </c>
       <c r="I86" s="0">
-        <v>-7.7194147113232884e-05</v>
+        <v>-7.7255005923690864e-05</v>
       </c>
       <c r="J86" s="0">
-        <v>4.8896045376945352e-09</v>
+        <v>4.5384715199723756e-09</v>
       </c>
       <c r="K86" s="0">
         <v>0</v>
@@ -10750,31 +10750,31 @@
         <v>825</v>
       </c>
       <c r="B87" s="0">
-        <v>0.88569374047079452</v>
+        <v>0.88569374065541928</v>
       </c>
       <c r="C87" s="0">
         <v>0.00041692989010989011</v>
       </c>
       <c r="D87" s="0">
-        <v>7.0388055137382496e-06</v>
+        <v>7.0239433190711346e-06</v>
       </c>
       <c r="E87" s="0">
         <v>0</v>
       </c>
       <c r="F87" s="0">
-        <v>7.4151108413050066e-06</v>
+        <v>7.3449925733435507e-06</v>
       </c>
       <c r="G87" s="0">
-        <v>1.3346296800142177e-07</v>
+        <v>1.3187907111819559e-07</v>
       </c>
       <c r="H87" s="0">
-        <v>3.8278027451545284e-05</v>
+        <v>3.8405493132132042e-05</v>
       </c>
       <c r="I87" s="0">
-        <v>-3.8789778860042376e-05</v>
+        <v>-3.8860289860333731e-05</v>
       </c>
       <c r="J87" s="0">
-        <v>1.9831129289104156e-09</v>
+        <v>1.8684028110749987e-09</v>
       </c>
       <c r="K87" s="0">
         <v>0</v>
@@ -10794,31 +10794,31 @@
         <v>826</v>
       </c>
       <c r="B88" s="0">
-        <v>0.86346120501878576</v>
+        <v>0.86346120492175782</v>
       </c>
       <c r="C88" s="0">
         <v>0.0015838630769230773</v>
       </c>
       <c r="D88" s="0">
-        <v>2.6682788217192531e-05</v>
+        <v>2.6535415842857527e-05</v>
       </c>
       <c r="E88" s="0">
         <v>0</v>
       </c>
       <c r="F88" s="0">
-        <v>3.293704396065532e-05</v>
+        <v>3.3059717008117047e-05</v>
       </c>
       <c r="G88" s="0">
-        <v>2.8089181638418751e-07</v>
+        <v>2.779283496659814e-07</v>
       </c>
       <c r="H88" s="0">
-        <v>3.0716632751054517e-05</v>
+        <v>3.0408101105906732e-05</v>
       </c>
       <c r="I88" s="0">
-        <v>-3.7254581155552453e-05</v>
+        <v>-3.7212775511748205e-05</v>
       </c>
       <c r="J88" s="0">
-        <v>2.8008446509612209e-09</v>
+        <v>2.4448909159748293e-09</v>
       </c>
       <c r="K88" s="0">
         <v>0</v>
@@ -10838,31 +10838,31 @@
         <v>827</v>
       </c>
       <c r="B89" s="0">
-        <v>0.90768418745615853</v>
+        <v>0.90768418745384349</v>
       </c>
       <c r="C89" s="0">
         <v>0.014315898461538461</v>
       </c>
       <c r="D89" s="0">
-        <v>-1.519016321799093e-06</v>
+        <v>-1.6491304487690754e-06</v>
       </c>
       <c r="E89" s="0">
-        <v>8.7046594441094601e-06</v>
+        <v>8.7046594480190321e-06</v>
       </c>
       <c r="F89" s="0">
-        <v>-3.5495980583653878e-06</v>
+        <v>-3.4727245690831141e-06</v>
       </c>
       <c r="G89" s="0">
-        <v>1.4587720728110973e-07</v>
+        <v>1.4538407141253752e-07</v>
       </c>
       <c r="H89" s="0">
-        <v>-1.5498550658778291e-06</v>
+        <v>-1.611853760422543e-06</v>
       </c>
       <c r="I89" s="0">
-        <v>-5.2709520306546056e-06</v>
+        <v>-5.4154825123496232e-06</v>
       </c>
       <c r="J89" s="0">
-        <v>8.5218170816055361e-10</v>
+        <v>8.8687365463575526e-10</v>
       </c>
       <c r="K89" s="0">
         <v>1</v>
@@ -10882,31 +10882,31 @@
         <v>828</v>
       </c>
       <c r="B90" s="0">
-        <v>0.87660295419990319</v>
+        <v>0.8766029539329564</v>
       </c>
       <c r="C90" s="0">
         <v>0.00065676263736263757</v>
       </c>
       <c r="D90" s="0">
-        <v>7.6977084016124981e-05</v>
+        <v>7.7180103879216999e-05</v>
       </c>
       <c r="E90" s="0">
         <v>0</v>
       </c>
       <c r="F90" s="0">
-        <v>3.8893976415846074e-05</v>
+        <v>3.8983280938844626e-05</v>
       </c>
       <c r="G90" s="0">
-        <v>3.377673222712171e-07</v>
+        <v>3.3392385087889097e-07</v>
       </c>
       <c r="H90" s="0">
-        <v>9.1434614593232527e-05</v>
+        <v>9.1841788151742496e-05</v>
       </c>
       <c r="I90" s="0">
-        <v>-5.3692617030743252e-05</v>
+        <v>-5.3981797598981108e-05</v>
       </c>
       <c r="J90" s="0">
-        <v>3.3427155184126227e-09</v>
+        <v>2.908536732091477e-09</v>
       </c>
       <c r="K90" s="0">
         <v>0</v>
@@ -10926,31 +10926,31 @@
         <v>829</v>
       </c>
       <c r="B91" s="0">
-        <v>0.84086726070600193</v>
+        <v>0.84086726068591122</v>
       </c>
       <c r="C91" s="0">
         <v>0.0016166171428571427</v>
       </c>
       <c r="D91" s="0">
-        <v>2.1176440141906153e-05</v>
+        <v>2.0933178879853808e-05</v>
       </c>
       <c r="E91" s="0">
         <v>0</v>
       </c>
       <c r="F91" s="0">
-        <v>3.2055158894692607e-05</v>
+        <v>3.2210358470521413e-05</v>
       </c>
       <c r="G91" s="0">
-        <v>1.5842632742626993e-07</v>
+        <v>1.5650865176204608e-07</v>
       </c>
       <c r="H91" s="0">
-        <v>-1.1445097024407509e-05</v>
+        <v>-1.1796722169019513e-05</v>
       </c>
       <c r="I91" s="0">
-        <v>4.0673641782782444e-07</v>
+        <v>3.6181528940565991e-07</v>
       </c>
       <c r="J91" s="0">
-        <v>1.2155263669587373e-09</v>
+        <v>1.2186371842030235e-09</v>
       </c>
       <c r="K91" s="0">
         <v>0</v>
@@ -10970,31 +10970,31 @@
         <v>830</v>
       </c>
       <c r="B92" s="0">
-        <v>0.88573320794875554</v>
+        <v>0.88573320339523642</v>
       </c>
       <c r="C92" s="0">
         <v>0.0004673857142857143</v>
       </c>
       <c r="D92" s="0">
-        <v>5.8700292941223949e-05</v>
+        <v>5.8806664678860595e-05</v>
       </c>
       <c r="E92" s="0">
         <v>0</v>
       </c>
       <c r="F92" s="0">
-        <v>2.5491048483959452e-05</v>
+        <v>2.5449472923731981e-05</v>
       </c>
       <c r="G92" s="0">
-        <v>1.4166351369050028e-07</v>
+        <v>1.3945564402263627e-07</v>
       </c>
       <c r="H92" s="0">
-        <v>8.7865807495124342e-05</v>
+        <v>8.8185392050372442e-05</v>
       </c>
       <c r="I92" s="0">
-        <v>-5.4799079468022821e-05</v>
+        <v>-5.4968396448702513e-05</v>
       </c>
       <c r="J92" s="0">
-        <v>8.5291647247513758e-10</v>
+        <v>7.4050943605101158e-10</v>
       </c>
       <c r="K92" s="0">
         <v>0</v>
